--- a/jogos_2026-09-16.xlsx
+++ b/jogos_2026-09-16.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU3"/>
+  <dimension ref="A1:AU56"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -751,158 +751,8797 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Russia FNL</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Yenisey</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Arsenal Tula</t>
+        </is>
+      </c>
+      <c r="G3">
+        <v>0</v>
+      </c>
+      <c r="H3">
+        <v>0</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>0</v>
+      </c>
+      <c r="K3">
+        <v>0</v>
+      </c>
+      <c r="L3">
+        <v>0</v>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N3">
+        <v>0</v>
+      </c>
+      <c r="O3">
+        <v>0</v>
+      </c>
+      <c r="P3">
+        <v>0</v>
+      </c>
+      <c r="Q3">
+        <v>0</v>
+      </c>
+      <c r="R3">
+        <v>0</v>
+      </c>
+      <c r="S3">
+        <v>0</v>
+      </c>
+      <c r="T3">
+        <v>0</v>
+      </c>
+      <c r="U3">
+        <v>0</v>
+      </c>
+      <c r="V3">
+        <v>0</v>
+      </c>
+      <c r="W3">
+        <v>0</v>
+      </c>
+      <c r="X3">
+        <v>0</v>
+      </c>
+      <c r="Y3">
+        <v>0</v>
+      </c>
+      <c r="Z3">
+        <v>0</v>
+      </c>
+      <c r="AA3">
+        <v>0</v>
+      </c>
+      <c r="AB3">
+        <v>0</v>
+      </c>
+      <c r="AC3">
+        <v>0</v>
+      </c>
+      <c r="AD3">
+        <v>0</v>
+      </c>
+      <c r="AE3">
+        <v>0</v>
+      </c>
+      <c r="AF3">
+        <v>0</v>
+      </c>
+      <c r="AG3">
+        <v>0</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ3">
+        <v>0</v>
+      </c>
+      <c r="AK3">
+        <v>0</v>
+      </c>
+      <c r="AL3">
+        <v>0</v>
+      </c>
+      <c r="AM3">
+        <v>-1</v>
+      </c>
+      <c r="AN3">
+        <v>-1</v>
+      </c>
+      <c r="AO3">
+        <v>-1</v>
+      </c>
+      <c r="AP3">
+        <v>-1</v>
+      </c>
+      <c r="AQ3">
+        <v>0</v>
+      </c>
+      <c r="AR3">
+        <v>0</v>
+      </c>
+      <c r="AS3">
+        <v>0</v>
+      </c>
+      <c r="AT3">
+        <v>0</v>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>2026-09-16 09:30:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Egypt Egyptian Premier League</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>El Gounah</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Petrojet</t>
+        </is>
+      </c>
+      <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="H4">
+        <v>0</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>0</v>
+      </c>
+      <c r="K4">
+        <v>0</v>
+      </c>
+      <c r="L4">
+        <v>0</v>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N4">
+        <v>0</v>
+      </c>
+      <c r="O4">
+        <v>0</v>
+      </c>
+      <c r="P4">
+        <v>0</v>
+      </c>
+      <c r="Q4">
+        <v>0</v>
+      </c>
+      <c r="R4">
+        <v>0</v>
+      </c>
+      <c r="S4">
+        <v>0</v>
+      </c>
+      <c r="T4">
+        <v>0</v>
+      </c>
+      <c r="U4">
+        <v>0</v>
+      </c>
+      <c r="V4">
+        <v>0</v>
+      </c>
+      <c r="W4">
+        <v>0</v>
+      </c>
+      <c r="X4">
+        <v>0</v>
+      </c>
+      <c r="Y4">
+        <v>0</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+      <c r="AA4">
+        <v>0</v>
+      </c>
+      <c r="AB4">
+        <v>0</v>
+      </c>
+      <c r="AC4">
+        <v>0</v>
+      </c>
+      <c r="AD4">
+        <v>0</v>
+      </c>
+      <c r="AE4">
+        <v>0</v>
+      </c>
+      <c r="AF4">
+        <v>0</v>
+      </c>
+      <c r="AG4">
+        <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ4">
+        <v>0</v>
+      </c>
+      <c r="AK4">
+        <v>0</v>
+      </c>
+      <c r="AL4">
+        <v>0</v>
+      </c>
+      <c r="AM4">
+        <v>-1</v>
+      </c>
+      <c r="AN4">
+        <v>-1</v>
+      </c>
+      <c r="AO4">
+        <v>-1</v>
+      </c>
+      <c r="AP4">
+        <v>-1</v>
+      </c>
+      <c r="AQ4">
+        <v>0</v>
+      </c>
+      <c r="AR4">
+        <v>0</v>
+      </c>
+      <c r="AS4">
+        <v>0</v>
+      </c>
+      <c r="AT4">
+        <v>0</v>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
+          <t>2026-09-16 11:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Tunisia Ligue 1</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Ben Guerdane</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>CS Sfaxien</t>
+        </is>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5">
+        <v>0</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>0</v>
+      </c>
+      <c r="K5">
+        <v>0</v>
+      </c>
+      <c r="L5">
+        <v>0</v>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N5">
+        <v>0</v>
+      </c>
+      <c r="O5">
+        <v>0</v>
+      </c>
+      <c r="P5">
+        <v>0</v>
+      </c>
+      <c r="Q5">
+        <v>0</v>
+      </c>
+      <c r="R5">
+        <v>0</v>
+      </c>
+      <c r="S5">
+        <v>0</v>
+      </c>
+      <c r="T5">
+        <v>0</v>
+      </c>
+      <c r="U5">
+        <v>0</v>
+      </c>
+      <c r="V5">
+        <v>0</v>
+      </c>
+      <c r="W5">
+        <v>0</v>
+      </c>
+      <c r="X5">
+        <v>0</v>
+      </c>
+      <c r="Y5">
+        <v>0</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+      <c r="AA5">
+        <v>0</v>
+      </c>
+      <c r="AB5">
+        <v>0</v>
+      </c>
+      <c r="AC5">
+        <v>0</v>
+      </c>
+      <c r="AD5">
+        <v>0</v>
+      </c>
+      <c r="AE5">
+        <v>0</v>
+      </c>
+      <c r="AF5">
+        <v>0</v>
+      </c>
+      <c r="AG5">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ5">
+        <v>0</v>
+      </c>
+      <c r="AK5">
+        <v>0</v>
+      </c>
+      <c r="AL5">
+        <v>0</v>
+      </c>
+      <c r="AM5">
+        <v>-1</v>
+      </c>
+      <c r="AN5">
+        <v>-1</v>
+      </c>
+      <c r="AO5">
+        <v>-1</v>
+      </c>
+      <c r="AP5">
+        <v>-1</v>
+      </c>
+      <c r="AQ5">
+        <v>0</v>
+      </c>
+      <c r="AR5">
+        <v>0</v>
+      </c>
+      <c r="AS5">
+        <v>0</v>
+      </c>
+      <c r="AT5">
+        <v>0</v>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
+          <t>2026-09-16 12:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Russia Russian Premier League</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Spartak Moskva</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Fakel</t>
+        </is>
+      </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>0</v>
+      </c>
+      <c r="K6">
+        <v>0</v>
+      </c>
+      <c r="L6">
+        <v>0</v>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N6">
+        <v>0</v>
+      </c>
+      <c r="O6">
+        <v>0</v>
+      </c>
+      <c r="P6">
+        <v>0</v>
+      </c>
+      <c r="Q6">
+        <v>0</v>
+      </c>
+      <c r="R6">
+        <v>0</v>
+      </c>
+      <c r="S6">
+        <v>0</v>
+      </c>
+      <c r="T6">
+        <v>0</v>
+      </c>
+      <c r="U6">
+        <v>0</v>
+      </c>
+      <c r="V6">
+        <v>0</v>
+      </c>
+      <c r="W6">
+        <v>0</v>
+      </c>
+      <c r="X6">
+        <v>0</v>
+      </c>
+      <c r="Y6">
+        <v>0</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+      <c r="AA6">
+        <v>0</v>
+      </c>
+      <c r="AB6">
+        <v>0</v>
+      </c>
+      <c r="AC6">
+        <v>0</v>
+      </c>
+      <c r="AD6">
+        <v>0</v>
+      </c>
+      <c r="AE6">
+        <v>0</v>
+      </c>
+      <c r="AF6">
+        <v>0</v>
+      </c>
+      <c r="AG6">
+        <v>0</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ6">
+        <v>0</v>
+      </c>
+      <c r="AK6">
+        <v>0</v>
+      </c>
+      <c r="AL6">
+        <v>0</v>
+      </c>
+      <c r="AM6">
+        <v>-1</v>
+      </c>
+      <c r="AN6">
+        <v>-1</v>
+      </c>
+      <c r="AO6">
+        <v>-1</v>
+      </c>
+      <c r="AP6">
+        <v>-1</v>
+      </c>
+      <c r="AQ6">
+        <v>0</v>
+      </c>
+      <c r="AR6">
+        <v>0</v>
+      </c>
+      <c r="AS6">
+        <v>0</v>
+      </c>
+      <c r="AT6">
+        <v>0</v>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>2026-09-16 12:30:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Russia Russian Premier League</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Rodina Moskva</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Rubin Kazan</t>
+        </is>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7">
+        <v>0</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>0</v>
+      </c>
+      <c r="K7">
+        <v>0</v>
+      </c>
+      <c r="L7">
+        <v>0</v>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N7">
+        <v>0</v>
+      </c>
+      <c r="O7">
+        <v>0</v>
+      </c>
+      <c r="P7">
+        <v>0</v>
+      </c>
+      <c r="Q7">
+        <v>0</v>
+      </c>
+      <c r="R7">
+        <v>0</v>
+      </c>
+      <c r="S7">
+        <v>0</v>
+      </c>
+      <c r="T7">
+        <v>0</v>
+      </c>
+      <c r="U7">
+        <v>0</v>
+      </c>
+      <c r="V7">
+        <v>0</v>
+      </c>
+      <c r="W7">
+        <v>0</v>
+      </c>
+      <c r="X7">
+        <v>0</v>
+      </c>
+      <c r="Y7">
+        <v>0</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+      <c r="AA7">
+        <v>0</v>
+      </c>
+      <c r="AB7">
+        <v>0</v>
+      </c>
+      <c r="AC7">
+        <v>0</v>
+      </c>
+      <c r="AD7">
+        <v>0</v>
+      </c>
+      <c r="AE7">
+        <v>0</v>
+      </c>
+      <c r="AF7">
+        <v>0</v>
+      </c>
+      <c r="AG7">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ7">
+        <v>0</v>
+      </c>
+      <c r="AK7">
+        <v>0</v>
+      </c>
+      <c r="AL7">
+        <v>0</v>
+      </c>
+      <c r="AM7">
+        <v>-1</v>
+      </c>
+      <c r="AN7">
+        <v>-1</v>
+      </c>
+      <c r="AO7">
+        <v>-1</v>
+      </c>
+      <c r="AP7">
+        <v>-1</v>
+      </c>
+      <c r="AQ7">
+        <v>0</v>
+      </c>
+      <c r="AR7">
+        <v>0</v>
+      </c>
+      <c r="AS7">
+        <v>0</v>
+      </c>
+      <c r="AT7">
+        <v>0</v>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
+          <t>2026-09-16 12:30:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Lithuania A Lyga</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Žalgiris</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Kauno Žalgiris</t>
+        </is>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8">
+        <v>0</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>0</v>
+      </c>
+      <c r="K8">
+        <v>0</v>
+      </c>
+      <c r="L8">
+        <v>0</v>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N8">
+        <v>2.88</v>
+      </c>
+      <c r="O8">
+        <v>3.35</v>
+      </c>
+      <c r="P8">
+        <v>2.25</v>
+      </c>
+      <c r="Q8">
+        <v>0</v>
+      </c>
+      <c r="R8">
+        <v>0</v>
+      </c>
+      <c r="S8">
+        <v>0</v>
+      </c>
+      <c r="T8">
+        <v>0</v>
+      </c>
+      <c r="U8">
+        <v>0</v>
+      </c>
+      <c r="V8">
+        <v>0</v>
+      </c>
+      <c r="W8">
+        <v>0</v>
+      </c>
+      <c r="X8">
+        <v>0</v>
+      </c>
+      <c r="Y8">
+        <v>0</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+      <c r="AA8">
+        <v>0</v>
+      </c>
+      <c r="AB8">
+        <v>0</v>
+      </c>
+      <c r="AC8">
+        <v>0</v>
+      </c>
+      <c r="AD8">
+        <v>0</v>
+      </c>
+      <c r="AE8">
+        <v>0</v>
+      </c>
+      <c r="AF8">
+        <v>0</v>
+      </c>
+      <c r="AG8">
+        <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ8">
+        <v>0</v>
+      </c>
+      <c r="AK8">
+        <v>0</v>
+      </c>
+      <c r="AL8">
+        <v>0</v>
+      </c>
+      <c r="AM8">
+        <v>-1</v>
+      </c>
+      <c r="AN8">
+        <v>-1</v>
+      </c>
+      <c r="AO8">
+        <v>-1</v>
+      </c>
+      <c r="AP8">
+        <v>-1</v>
+      </c>
+      <c r="AQ8">
+        <v>0</v>
+      </c>
+      <c r="AR8">
+        <v>0</v>
+      </c>
+      <c r="AS8">
+        <v>0</v>
+      </c>
+      <c r="AT8">
+        <v>0</v>
+      </c>
+      <c r="AU8" t="inlineStr">
+        <is>
+          <t>2026-09-16 12:45:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
           <t>13:00</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Estonia Meistriliiga</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Paide</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Vaprus</t>
+        </is>
+      </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9">
+        <v>0</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>0</v>
+      </c>
+      <c r="K9">
+        <v>0</v>
+      </c>
+      <c r="L9">
+        <v>0</v>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N9">
+        <v>0</v>
+      </c>
+      <c r="O9">
+        <v>0</v>
+      </c>
+      <c r="P9">
+        <v>0</v>
+      </c>
+      <c r="Q9">
+        <v>0</v>
+      </c>
+      <c r="R9">
+        <v>0</v>
+      </c>
+      <c r="S9">
+        <v>0</v>
+      </c>
+      <c r="T9">
+        <v>0</v>
+      </c>
+      <c r="U9">
+        <v>0</v>
+      </c>
+      <c r="V9">
+        <v>0</v>
+      </c>
+      <c r="W9">
+        <v>0</v>
+      </c>
+      <c r="X9">
+        <v>0</v>
+      </c>
+      <c r="Y9">
+        <v>0</v>
+      </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+      <c r="AA9">
+        <v>0</v>
+      </c>
+      <c r="AB9">
+        <v>0</v>
+      </c>
+      <c r="AC9">
+        <v>0</v>
+      </c>
+      <c r="AD9">
+        <v>0</v>
+      </c>
+      <c r="AE9">
+        <v>0</v>
+      </c>
+      <c r="AF9">
+        <v>0</v>
+      </c>
+      <c r="AG9">
+        <v>0</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ9">
+        <v>0</v>
+      </c>
+      <c r="AK9">
+        <v>0</v>
+      </c>
+      <c r="AL9">
+        <v>0</v>
+      </c>
+      <c r="AM9">
+        <v>-1</v>
+      </c>
+      <c r="AN9">
+        <v>-1</v>
+      </c>
+      <c r="AO9">
+        <v>-1</v>
+      </c>
+      <c r="AP9">
+        <v>-1</v>
+      </c>
+      <c r="AQ9">
+        <v>0</v>
+      </c>
+      <c r="AR9">
+        <v>0</v>
+      </c>
+      <c r="AS9">
+        <v>0</v>
+      </c>
+      <c r="AT9">
+        <v>0</v>
+      </c>
+      <c r="AU9" t="inlineStr">
+        <is>
+          <t>2026-09-16 13:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Latvia Virsliga</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Auda</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Ogre United</t>
+        </is>
+      </c>
+      <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="H10">
+        <v>0</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>0</v>
+      </c>
+      <c r="K10">
+        <v>0</v>
+      </c>
+      <c r="L10">
+        <v>0</v>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>suspended</t>
+        </is>
+      </c>
+      <c r="N10">
+        <v>1.23</v>
+      </c>
+      <c r="O10">
+        <v>5.5</v>
+      </c>
+      <c r="P10">
+        <v>8.5</v>
+      </c>
+      <c r="Q10">
+        <v>1.62</v>
+      </c>
+      <c r="R10">
+        <v>2.95</v>
+      </c>
+      <c r="S10">
+        <v>1.2</v>
+      </c>
+      <c r="T10">
+        <v>4</v>
+      </c>
+      <c r="U10">
+        <v>2.1</v>
+      </c>
+      <c r="V10">
+        <v>1.68</v>
+      </c>
+      <c r="W10">
+        <v>1.17</v>
+      </c>
+      <c r="X10">
+        <v>1.02</v>
+      </c>
+      <c r="Y10">
+        <v>1.08</v>
+      </c>
+      <c r="Z10">
+        <v>5.75</v>
+      </c>
+      <c r="AA10">
+        <v>1.43</v>
+      </c>
+      <c r="AB10">
+        <v>2.75</v>
+      </c>
+      <c r="AC10">
+        <v>2</v>
+      </c>
+      <c r="AD10">
+        <v>1.61</v>
+      </c>
+      <c r="AE10">
+        <v>1.27</v>
+      </c>
+      <c r="AF10">
+        <v>1.72</v>
+      </c>
+      <c r="AG10">
+        <v>1.97</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ10">
+        <v>1.08</v>
+      </c>
+      <c r="AK10">
+        <v>3.42</v>
+      </c>
+      <c r="AL10">
+        <v>0</v>
+      </c>
+      <c r="AM10">
+        <v>-1</v>
+      </c>
+      <c r="AN10">
+        <v>-1</v>
+      </c>
+      <c r="AO10">
+        <v>-1</v>
+      </c>
+      <c r="AP10">
+        <v>-1</v>
+      </c>
+      <c r="AQ10">
+        <v>0</v>
+      </c>
+      <c r="AR10">
+        <v>0</v>
+      </c>
+      <c r="AS10">
+        <v>0</v>
+      </c>
+      <c r="AT10">
+        <v>0</v>
+      </c>
+      <c r="AU10" t="inlineStr">
+        <is>
+          <t>2026-09-16 13:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
         <is>
           <t>Bulgaria First League</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>2026/2027</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>CSKA Sofia</t>
         </is>
       </c>
-      <c r="G3">
-        <v>0</v>
-      </c>
-      <c r="H3">
-        <v>0</v>
-      </c>
-      <c r="I3">
-        <v>0</v>
-      </c>
-      <c r="J3">
-        <v>0</v>
-      </c>
-      <c r="K3">
-        <v>0</v>
-      </c>
-      <c r="L3">
-        <v>0</v>
-      </c>
-      <c r="M3" t="inlineStr">
+      <c r="G11">
+        <v>0</v>
+      </c>
+      <c r="H11">
+        <v>0</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>0</v>
+      </c>
+      <c r="K11">
+        <v>0</v>
+      </c>
+      <c r="L11">
+        <v>0</v>
+      </c>
+      <c r="M11" t="inlineStr">
         <is>
           <t>suspended</t>
         </is>
       </c>
-      <c r="N3">
+      <c r="N11">
         <v>4.6</v>
       </c>
-      <c r="O3">
+      <c r="O11">
         <v>3.9</v>
       </c>
-      <c r="P3">
+      <c r="P11">
         <v>1.55</v>
       </c>
-      <c r="Q3">
+      <c r="Q11">
         <v>5.07</v>
       </c>
-      <c r="R3">
+      <c r="R11">
         <v>2.43</v>
       </c>
-      <c r="S3">
+      <c r="S11">
         <v>1.3</v>
       </c>
-      <c r="T3">
+      <c r="T11">
         <v>3.1</v>
       </c>
-      <c r="U3">
+      <c r="U11">
         <v>2.63</v>
       </c>
-      <c r="V3">
+      <c r="V11">
         <v>1.47</v>
       </c>
-      <c r="W3">
+      <c r="W11">
         <v>1.08</v>
       </c>
-      <c r="X3">
+      <c r="X11">
         <v>1.04</v>
       </c>
-      <c r="Y3">
+      <c r="Y11">
         <v>1.24</v>
       </c>
-      <c r="Z3">
+      <c r="Z11">
         <v>3.72</v>
       </c>
-      <c r="AA3">
+      <c r="AA11">
         <v>1.75</v>
       </c>
-      <c r="AB3">
+      <c r="AB11">
         <v>2.05</v>
       </c>
-      <c r="AC3">
+      <c r="AC11">
         <v>2.75</v>
       </c>
-      <c r="AD3">
+      <c r="AD11">
         <v>1.4</v>
       </c>
-      <c r="AE3">
+      <c r="AE11">
         <v>1.15</v>
       </c>
-      <c r="AF3">
+      <c r="AF11">
         <v>1.74</v>
       </c>
-      <c r="AG3">
+      <c r="AG11">
         <v>1.95</v>
       </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ3">
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ11">
         <v>1.25</v>
       </c>
-      <c r="AK3">
+      <c r="AK11">
         <v>1.17</v>
       </c>
-      <c r="AL3">
-        <v>0</v>
-      </c>
-      <c r="AM3">
-        <v>-1</v>
-      </c>
-      <c r="AN3">
-        <v>-1</v>
-      </c>
-      <c r="AO3">
-        <v>-1</v>
-      </c>
-      <c r="AP3">
-        <v>-1</v>
-      </c>
-      <c r="AQ3">
-        <v>0</v>
-      </c>
-      <c r="AR3">
-        <v>0</v>
-      </c>
-      <c r="AS3">
-        <v>0</v>
-      </c>
-      <c r="AT3">
-        <v>0</v>
-      </c>
-      <c r="AU3" t="inlineStr">
+      <c r="AL11">
+        <v>0</v>
+      </c>
+      <c r="AM11">
+        <v>-1</v>
+      </c>
+      <c r="AN11">
+        <v>-1</v>
+      </c>
+      <c r="AO11">
+        <v>-1</v>
+      </c>
+      <c r="AP11">
+        <v>-1</v>
+      </c>
+      <c r="AQ11">
+        <v>0</v>
+      </c>
+      <c r="AR11">
+        <v>0</v>
+      </c>
+      <c r="AS11">
+        <v>0</v>
+      </c>
+      <c r="AT11">
+        <v>0</v>
+      </c>
+      <c r="AU11" t="inlineStr">
         <is>
           <t>2026-09-16 13:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Italy Serie C Group B</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Latina</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Nuova Monterosi</t>
+        </is>
+      </c>
+      <c r="G12">
+        <v>0</v>
+      </c>
+      <c r="H12">
+        <v>0</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>0</v>
+      </c>
+      <c r="K12">
+        <v>0</v>
+      </c>
+      <c r="L12">
+        <v>0</v>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N12">
+        <v>0</v>
+      </c>
+      <c r="O12">
+        <v>0</v>
+      </c>
+      <c r="P12">
+        <v>0</v>
+      </c>
+      <c r="Q12">
+        <v>0</v>
+      </c>
+      <c r="R12">
+        <v>0</v>
+      </c>
+      <c r="S12">
+        <v>0</v>
+      </c>
+      <c r="T12">
+        <v>0</v>
+      </c>
+      <c r="U12">
+        <v>0</v>
+      </c>
+      <c r="V12">
+        <v>0</v>
+      </c>
+      <c r="W12">
+        <v>0</v>
+      </c>
+      <c r="X12">
+        <v>0</v>
+      </c>
+      <c r="Y12">
+        <v>0</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+      <c r="AA12">
+        <v>0</v>
+      </c>
+      <c r="AB12">
+        <v>0</v>
+      </c>
+      <c r="AC12">
+        <v>0</v>
+      </c>
+      <c r="AD12">
+        <v>0</v>
+      </c>
+      <c r="AE12">
+        <v>0</v>
+      </c>
+      <c r="AF12">
+        <v>0</v>
+      </c>
+      <c r="AG12">
+        <v>0</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ12">
+        <v>0</v>
+      </c>
+      <c r="AK12">
+        <v>0</v>
+      </c>
+      <c r="AL12">
+        <v>0</v>
+      </c>
+      <c r="AM12">
+        <v>-1</v>
+      </c>
+      <c r="AN12">
+        <v>-1</v>
+      </c>
+      <c r="AO12">
+        <v>-1</v>
+      </c>
+      <c r="AP12">
+        <v>-1</v>
+      </c>
+      <c r="AQ12">
+        <v>0</v>
+      </c>
+      <c r="AR12">
+        <v>0</v>
+      </c>
+      <c r="AS12">
+        <v>0</v>
+      </c>
+      <c r="AT12">
+        <v>0</v>
+      </c>
+      <c r="AU12" t="inlineStr">
+        <is>
+          <t>2026-09-16 13:30:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Italy Serie C Group B</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Ostia Mare Lidocalcio</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Ravenna</t>
+        </is>
+      </c>
+      <c r="G13">
+        <v>0</v>
+      </c>
+      <c r="H13">
+        <v>0</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>0</v>
+      </c>
+      <c r="K13">
+        <v>0</v>
+      </c>
+      <c r="L13">
+        <v>0</v>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N13">
+        <v>0</v>
+      </c>
+      <c r="O13">
+        <v>0</v>
+      </c>
+      <c r="P13">
+        <v>0</v>
+      </c>
+      <c r="Q13">
+        <v>0</v>
+      </c>
+      <c r="R13">
+        <v>0</v>
+      </c>
+      <c r="S13">
+        <v>0</v>
+      </c>
+      <c r="T13">
+        <v>0</v>
+      </c>
+      <c r="U13">
+        <v>0</v>
+      </c>
+      <c r="V13">
+        <v>0</v>
+      </c>
+      <c r="W13">
+        <v>0</v>
+      </c>
+      <c r="X13">
+        <v>0</v>
+      </c>
+      <c r="Y13">
+        <v>0</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+      <c r="AA13">
+        <v>0</v>
+      </c>
+      <c r="AB13">
+        <v>0</v>
+      </c>
+      <c r="AC13">
+        <v>0</v>
+      </c>
+      <c r="AD13">
+        <v>0</v>
+      </c>
+      <c r="AE13">
+        <v>0</v>
+      </c>
+      <c r="AF13">
+        <v>0</v>
+      </c>
+      <c r="AG13">
+        <v>0</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ13">
+        <v>0</v>
+      </c>
+      <c r="AK13">
+        <v>0</v>
+      </c>
+      <c r="AL13">
+        <v>0</v>
+      </c>
+      <c r="AM13">
+        <v>-1</v>
+      </c>
+      <c r="AN13">
+        <v>-1</v>
+      </c>
+      <c r="AO13">
+        <v>-1</v>
+      </c>
+      <c r="AP13">
+        <v>-1</v>
+      </c>
+      <c r="AQ13">
+        <v>0</v>
+      </c>
+      <c r="AR13">
+        <v>0</v>
+      </c>
+      <c r="AS13">
+        <v>0</v>
+      </c>
+      <c r="AT13">
+        <v>0</v>
+      </c>
+      <c r="AU13" t="inlineStr">
+        <is>
+          <t>2026-09-16 13:30:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Italy Serie C Group B</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Sambenedettese</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Atalanta II</t>
+        </is>
+      </c>
+      <c r="G14">
+        <v>0</v>
+      </c>
+      <c r="H14">
+        <v>0</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>0</v>
+      </c>
+      <c r="K14">
+        <v>0</v>
+      </c>
+      <c r="L14">
+        <v>0</v>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N14">
+        <v>0</v>
+      </c>
+      <c r="O14">
+        <v>0</v>
+      </c>
+      <c r="P14">
+        <v>0</v>
+      </c>
+      <c r="Q14">
+        <v>0</v>
+      </c>
+      <c r="R14">
+        <v>0</v>
+      </c>
+      <c r="S14">
+        <v>0</v>
+      </c>
+      <c r="T14">
+        <v>0</v>
+      </c>
+      <c r="U14">
+        <v>0</v>
+      </c>
+      <c r="V14">
+        <v>0</v>
+      </c>
+      <c r="W14">
+        <v>0</v>
+      </c>
+      <c r="X14">
+        <v>0</v>
+      </c>
+      <c r="Y14">
+        <v>0</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+      <c r="AA14">
+        <v>0</v>
+      </c>
+      <c r="AB14">
+        <v>0</v>
+      </c>
+      <c r="AC14">
+        <v>0</v>
+      </c>
+      <c r="AD14">
+        <v>0</v>
+      </c>
+      <c r="AE14">
+        <v>0</v>
+      </c>
+      <c r="AF14">
+        <v>0</v>
+      </c>
+      <c r="AG14">
+        <v>0</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ14">
+        <v>0</v>
+      </c>
+      <c r="AK14">
+        <v>0</v>
+      </c>
+      <c r="AL14">
+        <v>0</v>
+      </c>
+      <c r="AM14">
+        <v>-1</v>
+      </c>
+      <c r="AN14">
+        <v>-1</v>
+      </c>
+      <c r="AO14">
+        <v>-1</v>
+      </c>
+      <c r="AP14">
+        <v>-1</v>
+      </c>
+      <c r="AQ14">
+        <v>0</v>
+      </c>
+      <c r="AR14">
+        <v>0</v>
+      </c>
+      <c r="AS14">
+        <v>0</v>
+      </c>
+      <c r="AT14">
+        <v>0</v>
+      </c>
+      <c r="AU14" t="inlineStr">
+        <is>
+          <t>2026-09-16 13:30:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Italy Serie C Group B</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Pineto</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Forlì</t>
+        </is>
+      </c>
+      <c r="G15">
+        <v>0</v>
+      </c>
+      <c r="H15">
+        <v>0</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>0</v>
+      </c>
+      <c r="K15">
+        <v>0</v>
+      </c>
+      <c r="L15">
+        <v>0</v>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N15">
+        <v>0</v>
+      </c>
+      <c r="O15">
+        <v>0</v>
+      </c>
+      <c r="P15">
+        <v>0</v>
+      </c>
+      <c r="Q15">
+        <v>0</v>
+      </c>
+      <c r="R15">
+        <v>0</v>
+      </c>
+      <c r="S15">
+        <v>0</v>
+      </c>
+      <c r="T15">
+        <v>0</v>
+      </c>
+      <c r="U15">
+        <v>0</v>
+      </c>
+      <c r="V15">
+        <v>0</v>
+      </c>
+      <c r="W15">
+        <v>0</v>
+      </c>
+      <c r="X15">
+        <v>0</v>
+      </c>
+      <c r="Y15">
+        <v>0</v>
+      </c>
+      <c r="Z15">
+        <v>0</v>
+      </c>
+      <c r="AA15">
+        <v>0</v>
+      </c>
+      <c r="AB15">
+        <v>0</v>
+      </c>
+      <c r="AC15">
+        <v>0</v>
+      </c>
+      <c r="AD15">
+        <v>0</v>
+      </c>
+      <c r="AE15">
+        <v>0</v>
+      </c>
+      <c r="AF15">
+        <v>0</v>
+      </c>
+      <c r="AG15">
+        <v>0</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ15">
+        <v>0</v>
+      </c>
+      <c r="AK15">
+        <v>0</v>
+      </c>
+      <c r="AL15">
+        <v>0</v>
+      </c>
+      <c r="AM15">
+        <v>-1</v>
+      </c>
+      <c r="AN15">
+        <v>-1</v>
+      </c>
+      <c r="AO15">
+        <v>-1</v>
+      </c>
+      <c r="AP15">
+        <v>-1</v>
+      </c>
+      <c r="AQ15">
+        <v>0</v>
+      </c>
+      <c r="AR15">
+        <v>0</v>
+      </c>
+      <c r="AS15">
+        <v>0</v>
+      </c>
+      <c r="AT15">
+        <v>0</v>
+      </c>
+      <c r="AU15" t="inlineStr">
+        <is>
+          <t>2026-09-16 13:30:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Italy Serie C Group B</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Grosseto</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Città di Campobasso</t>
+        </is>
+      </c>
+      <c r="G16">
+        <v>0</v>
+      </c>
+      <c r="H16">
+        <v>0</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>0</v>
+      </c>
+      <c r="K16">
+        <v>0</v>
+      </c>
+      <c r="L16">
+        <v>0</v>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N16">
+        <v>0</v>
+      </c>
+      <c r="O16">
+        <v>0</v>
+      </c>
+      <c r="P16">
+        <v>0</v>
+      </c>
+      <c r="Q16">
+        <v>0</v>
+      </c>
+      <c r="R16">
+        <v>0</v>
+      </c>
+      <c r="S16">
+        <v>0</v>
+      </c>
+      <c r="T16">
+        <v>0</v>
+      </c>
+      <c r="U16">
+        <v>0</v>
+      </c>
+      <c r="V16">
+        <v>0</v>
+      </c>
+      <c r="W16">
+        <v>0</v>
+      </c>
+      <c r="X16">
+        <v>0</v>
+      </c>
+      <c r="Y16">
+        <v>0</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+      <c r="AA16">
+        <v>0</v>
+      </c>
+      <c r="AB16">
+        <v>0</v>
+      </c>
+      <c r="AC16">
+        <v>0</v>
+      </c>
+      <c r="AD16">
+        <v>0</v>
+      </c>
+      <c r="AE16">
+        <v>0</v>
+      </c>
+      <c r="AF16">
+        <v>0</v>
+      </c>
+      <c r="AG16">
+        <v>0</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ16">
+        <v>0</v>
+      </c>
+      <c r="AK16">
+        <v>0</v>
+      </c>
+      <c r="AL16">
+        <v>0</v>
+      </c>
+      <c r="AM16">
+        <v>-1</v>
+      </c>
+      <c r="AN16">
+        <v>-1</v>
+      </c>
+      <c r="AO16">
+        <v>-1</v>
+      </c>
+      <c r="AP16">
+        <v>-1</v>
+      </c>
+      <c r="AQ16">
+        <v>0</v>
+      </c>
+      <c r="AR16">
+        <v>0</v>
+      </c>
+      <c r="AS16">
+        <v>0</v>
+      </c>
+      <c r="AT16">
+        <v>0</v>
+      </c>
+      <c r="AU16" t="inlineStr">
+        <is>
+          <t>2026-09-16 13:30:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Italy Serie C Group B</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Sassari Torres</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Pianese</t>
+        </is>
+      </c>
+      <c r="G17">
+        <v>0</v>
+      </c>
+      <c r="H17">
+        <v>0</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>0</v>
+      </c>
+      <c r="K17">
+        <v>0</v>
+      </c>
+      <c r="L17">
+        <v>0</v>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N17">
+        <v>0</v>
+      </c>
+      <c r="O17">
+        <v>0</v>
+      </c>
+      <c r="P17">
+        <v>0</v>
+      </c>
+      <c r="Q17">
+        <v>0</v>
+      </c>
+      <c r="R17">
+        <v>0</v>
+      </c>
+      <c r="S17">
+        <v>0</v>
+      </c>
+      <c r="T17">
+        <v>0</v>
+      </c>
+      <c r="U17">
+        <v>0</v>
+      </c>
+      <c r="V17">
+        <v>0</v>
+      </c>
+      <c r="W17">
+        <v>0</v>
+      </c>
+      <c r="X17">
+        <v>0</v>
+      </c>
+      <c r="Y17">
+        <v>0</v>
+      </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+      <c r="AA17">
+        <v>0</v>
+      </c>
+      <c r="AB17">
+        <v>0</v>
+      </c>
+      <c r="AC17">
+        <v>0</v>
+      </c>
+      <c r="AD17">
+        <v>0</v>
+      </c>
+      <c r="AE17">
+        <v>0</v>
+      </c>
+      <c r="AF17">
+        <v>0</v>
+      </c>
+      <c r="AG17">
+        <v>0</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ17">
+        <v>0</v>
+      </c>
+      <c r="AK17">
+        <v>0</v>
+      </c>
+      <c r="AL17">
+        <v>0</v>
+      </c>
+      <c r="AM17">
+        <v>-1</v>
+      </c>
+      <c r="AN17">
+        <v>-1</v>
+      </c>
+      <c r="AO17">
+        <v>-1</v>
+      </c>
+      <c r="AP17">
+        <v>-1</v>
+      </c>
+      <c r="AQ17">
+        <v>0</v>
+      </c>
+      <c r="AR17">
+        <v>0</v>
+      </c>
+      <c r="AS17">
+        <v>0</v>
+      </c>
+      <c r="AT17">
+        <v>0</v>
+      </c>
+      <c r="AU17" t="inlineStr">
+        <is>
+          <t>2026-09-16 13:30:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Egypt Egyptian Premier League</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Ghazl El Mehalla</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Zamalek</t>
+        </is>
+      </c>
+      <c r="G18">
+        <v>0</v>
+      </c>
+      <c r="H18">
+        <v>0</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>0</v>
+      </c>
+      <c r="K18">
+        <v>0</v>
+      </c>
+      <c r="L18">
+        <v>0</v>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N18">
+        <v>0</v>
+      </c>
+      <c r="O18">
+        <v>0</v>
+      </c>
+      <c r="P18">
+        <v>0</v>
+      </c>
+      <c r="Q18">
+        <v>0</v>
+      </c>
+      <c r="R18">
+        <v>0</v>
+      </c>
+      <c r="S18">
+        <v>0</v>
+      </c>
+      <c r="T18">
+        <v>0</v>
+      </c>
+      <c r="U18">
+        <v>0</v>
+      </c>
+      <c r="V18">
+        <v>0</v>
+      </c>
+      <c r="W18">
+        <v>0</v>
+      </c>
+      <c r="X18">
+        <v>0</v>
+      </c>
+      <c r="Y18">
+        <v>0</v>
+      </c>
+      <c r="Z18">
+        <v>0</v>
+      </c>
+      <c r="AA18">
+        <v>0</v>
+      </c>
+      <c r="AB18">
+        <v>0</v>
+      </c>
+      <c r="AC18">
+        <v>0</v>
+      </c>
+      <c r="AD18">
+        <v>0</v>
+      </c>
+      <c r="AE18">
+        <v>0</v>
+      </c>
+      <c r="AF18">
+        <v>0</v>
+      </c>
+      <c r="AG18">
+        <v>0</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ18">
+        <v>0</v>
+      </c>
+      <c r="AK18">
+        <v>0</v>
+      </c>
+      <c r="AL18">
+        <v>0</v>
+      </c>
+      <c r="AM18">
+        <v>-1</v>
+      </c>
+      <c r="AN18">
+        <v>-1</v>
+      </c>
+      <c r="AO18">
+        <v>-1</v>
+      </c>
+      <c r="AP18">
+        <v>-1</v>
+      </c>
+      <c r="AQ18">
+        <v>0</v>
+      </c>
+      <c r="AR18">
+        <v>0</v>
+      </c>
+      <c r="AS18">
+        <v>0</v>
+      </c>
+      <c r="AT18">
+        <v>0</v>
+      </c>
+      <c r="AU18" t="inlineStr">
+        <is>
+          <t>2026-09-16 14:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Egypt Egyptian Premier League</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>ENPPI</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Pyramids FC</t>
+        </is>
+      </c>
+      <c r="G19">
+        <v>0</v>
+      </c>
+      <c r="H19">
+        <v>0</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>0</v>
+      </c>
+      <c r="K19">
+        <v>0</v>
+      </c>
+      <c r="L19">
+        <v>0</v>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N19">
+        <v>0</v>
+      </c>
+      <c r="O19">
+        <v>0</v>
+      </c>
+      <c r="P19">
+        <v>0</v>
+      </c>
+      <c r="Q19">
+        <v>0</v>
+      </c>
+      <c r="R19">
+        <v>0</v>
+      </c>
+      <c r="S19">
+        <v>0</v>
+      </c>
+      <c r="T19">
+        <v>0</v>
+      </c>
+      <c r="U19">
+        <v>0</v>
+      </c>
+      <c r="V19">
+        <v>0</v>
+      </c>
+      <c r="W19">
+        <v>0</v>
+      </c>
+      <c r="X19">
+        <v>0</v>
+      </c>
+      <c r="Y19">
+        <v>0</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+      <c r="AA19">
+        <v>0</v>
+      </c>
+      <c r="AB19">
+        <v>0</v>
+      </c>
+      <c r="AC19">
+        <v>0</v>
+      </c>
+      <c r="AD19">
+        <v>0</v>
+      </c>
+      <c r="AE19">
+        <v>0</v>
+      </c>
+      <c r="AF19">
+        <v>0</v>
+      </c>
+      <c r="AG19">
+        <v>0</v>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ19">
+        <v>0</v>
+      </c>
+      <c r="AK19">
+        <v>0</v>
+      </c>
+      <c r="AL19">
+        <v>0</v>
+      </c>
+      <c r="AM19">
+        <v>-1</v>
+      </c>
+      <c r="AN19">
+        <v>-1</v>
+      </c>
+      <c r="AO19">
+        <v>-1</v>
+      </c>
+      <c r="AP19">
+        <v>-1</v>
+      </c>
+      <c r="AQ19">
+        <v>0</v>
+      </c>
+      <c r="AR19">
+        <v>0</v>
+      </c>
+      <c r="AS19">
+        <v>0</v>
+      </c>
+      <c r="AT19">
+        <v>0</v>
+      </c>
+      <c r="AU19" t="inlineStr">
+        <is>
+          <t>2026-09-16 14:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Switzerland Super League</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Lugano</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>St. Gallen</t>
+        </is>
+      </c>
+      <c r="G20">
+        <v>0</v>
+      </c>
+      <c r="H20">
+        <v>0</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>0</v>
+      </c>
+      <c r="K20">
+        <v>0</v>
+      </c>
+      <c r="L20">
+        <v>0</v>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>suspended</t>
+        </is>
+      </c>
+      <c r="N20">
+        <v>2.01</v>
+      </c>
+      <c r="O20">
+        <v>3.55</v>
+      </c>
+      <c r="P20">
+        <v>3.52</v>
+      </c>
+      <c r="Q20">
+        <v>2.47</v>
+      </c>
+      <c r="R20">
+        <v>2.4</v>
+      </c>
+      <c r="S20">
+        <v>1.23</v>
+      </c>
+      <c r="T20">
+        <v>3.8</v>
+      </c>
+      <c r="U20">
+        <v>2.16</v>
+      </c>
+      <c r="V20">
+        <v>1.65</v>
+      </c>
+      <c r="W20">
+        <v>1.17</v>
+      </c>
+      <c r="X20">
+        <v>1.02</v>
+      </c>
+      <c r="Y20">
+        <v>1.11</v>
+      </c>
+      <c r="Z20">
+        <v>4.8</v>
+      </c>
+      <c r="AA20">
+        <v>1.46</v>
+      </c>
+      <c r="AB20">
+        <v>2.39</v>
+      </c>
+      <c r="AC20">
+        <v>2.26</v>
+      </c>
+      <c r="AD20">
+        <v>1.62</v>
+      </c>
+      <c r="AE20">
+        <v>1.21</v>
+      </c>
+      <c r="AF20">
+        <v>1.44</v>
+      </c>
+      <c r="AG20">
+        <v>2.55</v>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ20">
+        <v>1.33</v>
+      </c>
+      <c r="AK20">
+        <v>1.74</v>
+      </c>
+      <c r="AL20">
+        <v>0</v>
+      </c>
+      <c r="AM20">
+        <v>-1</v>
+      </c>
+      <c r="AN20">
+        <v>-1</v>
+      </c>
+      <c r="AO20">
+        <v>-1</v>
+      </c>
+      <c r="AP20">
+        <v>-1</v>
+      </c>
+      <c r="AQ20">
+        <v>0</v>
+      </c>
+      <c r="AR20">
+        <v>0</v>
+      </c>
+      <c r="AS20">
+        <v>0</v>
+      </c>
+      <c r="AT20">
+        <v>0</v>
+      </c>
+      <c r="AU20" t="inlineStr">
+        <is>
+          <t>2026-09-16 14:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Switzerland Super League</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Thun</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Servette</t>
+        </is>
+      </c>
+      <c r="G21">
+        <v>0</v>
+      </c>
+      <c r="H21">
+        <v>0</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>0</v>
+      </c>
+      <c r="K21">
+        <v>0</v>
+      </c>
+      <c r="L21">
+        <v>0</v>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>suspended</t>
+        </is>
+      </c>
+      <c r="N21">
+        <v>2.72</v>
+      </c>
+      <c r="O21">
+        <v>3.5</v>
+      </c>
+      <c r="P21">
+        <v>2.2</v>
+      </c>
+      <c r="Q21">
+        <v>3.05</v>
+      </c>
+      <c r="R21">
+        <v>2.29</v>
+      </c>
+      <c r="S21">
+        <v>1.24</v>
+      </c>
+      <c r="T21">
+        <v>3.5</v>
+      </c>
+      <c r="U21">
+        <v>2.1</v>
+      </c>
+      <c r="V21">
+        <v>1.61</v>
+      </c>
+      <c r="W21">
+        <v>1.18</v>
+      </c>
+      <c r="X21">
+        <v>1.02</v>
+      </c>
+      <c r="Y21">
+        <v>1.11</v>
+      </c>
+      <c r="Z21">
+        <v>5</v>
+      </c>
+      <c r="AA21">
+        <v>1.5</v>
+      </c>
+      <c r="AB21">
+        <v>2.53</v>
+      </c>
+      <c r="AC21">
+        <v>2.25</v>
+      </c>
+      <c r="AD21">
+        <v>1.62</v>
+      </c>
+      <c r="AE21">
+        <v>1.22</v>
+      </c>
+      <c r="AF21">
+        <v>1.43</v>
+      </c>
+      <c r="AG21">
+        <v>2.6</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ21">
+        <v>1.57</v>
+      </c>
+      <c r="AK21">
+        <v>1.41</v>
+      </c>
+      <c r="AL21">
+        <v>0</v>
+      </c>
+      <c r="AM21">
+        <v>-1</v>
+      </c>
+      <c r="AN21">
+        <v>-1</v>
+      </c>
+      <c r="AO21">
+        <v>-1</v>
+      </c>
+      <c r="AP21">
+        <v>-1</v>
+      </c>
+      <c r="AQ21">
+        <v>0</v>
+      </c>
+      <c r="AR21">
+        <v>0</v>
+      </c>
+      <c r="AS21">
+        <v>0</v>
+      </c>
+      <c r="AT21">
+        <v>0</v>
+      </c>
+      <c r="AU21" t="inlineStr">
+        <is>
+          <t>2026-09-16 14:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Germany 3. Liga</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Hansa Rostock</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Stuttgart II</t>
+        </is>
+      </c>
+      <c r="G22">
+        <v>0</v>
+      </c>
+      <c r="H22">
+        <v>0</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>0</v>
+      </c>
+      <c r="K22">
+        <v>0</v>
+      </c>
+      <c r="L22">
+        <v>0</v>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N22">
+        <v>0</v>
+      </c>
+      <c r="O22">
+        <v>0</v>
+      </c>
+      <c r="P22">
+        <v>0</v>
+      </c>
+      <c r="Q22">
+        <v>0</v>
+      </c>
+      <c r="R22">
+        <v>0</v>
+      </c>
+      <c r="S22">
+        <v>0</v>
+      </c>
+      <c r="T22">
+        <v>0</v>
+      </c>
+      <c r="U22">
+        <v>0</v>
+      </c>
+      <c r="V22">
+        <v>0</v>
+      </c>
+      <c r="W22">
+        <v>0</v>
+      </c>
+      <c r="X22">
+        <v>0</v>
+      </c>
+      <c r="Y22">
+        <v>0</v>
+      </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
+      <c r="AA22">
+        <v>0</v>
+      </c>
+      <c r="AB22">
+        <v>0</v>
+      </c>
+      <c r="AC22">
+        <v>0</v>
+      </c>
+      <c r="AD22">
+        <v>0</v>
+      </c>
+      <c r="AE22">
+        <v>0</v>
+      </c>
+      <c r="AF22">
+        <v>0</v>
+      </c>
+      <c r="AG22">
+        <v>0</v>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ22">
+        <v>0</v>
+      </c>
+      <c r="AK22">
+        <v>0</v>
+      </c>
+      <c r="AL22">
+        <v>0</v>
+      </c>
+      <c r="AM22">
+        <v>-1</v>
+      </c>
+      <c r="AN22">
+        <v>-1</v>
+      </c>
+      <c r="AO22">
+        <v>-1</v>
+      </c>
+      <c r="AP22">
+        <v>-1</v>
+      </c>
+      <c r="AQ22">
+        <v>0</v>
+      </c>
+      <c r="AR22">
+        <v>0</v>
+      </c>
+      <c r="AS22">
+        <v>0</v>
+      </c>
+      <c r="AT22">
+        <v>0</v>
+      </c>
+      <c r="AU22" t="inlineStr">
+        <is>
+          <t>2026-09-16 14:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Germany 3. Liga</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Preußen Münster</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Saarbrucken</t>
+        </is>
+      </c>
+      <c r="G23">
+        <v>0</v>
+      </c>
+      <c r="H23">
+        <v>0</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>0</v>
+      </c>
+      <c r="K23">
+        <v>0</v>
+      </c>
+      <c r="L23">
+        <v>0</v>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N23">
+        <v>0</v>
+      </c>
+      <c r="O23">
+        <v>0</v>
+      </c>
+      <c r="P23">
+        <v>0</v>
+      </c>
+      <c r="Q23">
+        <v>0</v>
+      </c>
+      <c r="R23">
+        <v>0</v>
+      </c>
+      <c r="S23">
+        <v>0</v>
+      </c>
+      <c r="T23">
+        <v>0</v>
+      </c>
+      <c r="U23">
+        <v>0</v>
+      </c>
+      <c r="V23">
+        <v>0</v>
+      </c>
+      <c r="W23">
+        <v>0</v>
+      </c>
+      <c r="X23">
+        <v>0</v>
+      </c>
+      <c r="Y23">
+        <v>0</v>
+      </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
+      <c r="AA23">
+        <v>0</v>
+      </c>
+      <c r="AB23">
+        <v>0</v>
+      </c>
+      <c r="AC23">
+        <v>0</v>
+      </c>
+      <c r="AD23">
+        <v>0</v>
+      </c>
+      <c r="AE23">
+        <v>0</v>
+      </c>
+      <c r="AF23">
+        <v>0</v>
+      </c>
+      <c r="AG23">
+        <v>0</v>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ23">
+        <v>0</v>
+      </c>
+      <c r="AK23">
+        <v>0</v>
+      </c>
+      <c r="AL23">
+        <v>0</v>
+      </c>
+      <c r="AM23">
+        <v>-1</v>
+      </c>
+      <c r="AN23">
+        <v>-1</v>
+      </c>
+      <c r="AO23">
+        <v>-1</v>
+      </c>
+      <c r="AP23">
+        <v>-1</v>
+      </c>
+      <c r="AQ23">
+        <v>0</v>
+      </c>
+      <c r="AR23">
+        <v>0</v>
+      </c>
+      <c r="AS23">
+        <v>0</v>
+      </c>
+      <c r="AT23">
+        <v>0</v>
+      </c>
+      <c r="AU23" t="inlineStr">
+        <is>
+          <t>2026-09-16 14:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Germany 3. Liga</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Fortuna Köln</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Wehen Wiesbaden</t>
+        </is>
+      </c>
+      <c r="G24">
+        <v>0</v>
+      </c>
+      <c r="H24">
+        <v>0</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>0</v>
+      </c>
+      <c r="K24">
+        <v>0</v>
+      </c>
+      <c r="L24">
+        <v>0</v>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N24">
+        <v>0</v>
+      </c>
+      <c r="O24">
+        <v>0</v>
+      </c>
+      <c r="P24">
+        <v>0</v>
+      </c>
+      <c r="Q24">
+        <v>0</v>
+      </c>
+      <c r="R24">
+        <v>0</v>
+      </c>
+      <c r="S24">
+        <v>0</v>
+      </c>
+      <c r="T24">
+        <v>0</v>
+      </c>
+      <c r="U24">
+        <v>0</v>
+      </c>
+      <c r="V24">
+        <v>0</v>
+      </c>
+      <c r="W24">
+        <v>0</v>
+      </c>
+      <c r="X24">
+        <v>0</v>
+      </c>
+      <c r="Y24">
+        <v>0</v>
+      </c>
+      <c r="Z24">
+        <v>0</v>
+      </c>
+      <c r="AA24">
+        <v>0</v>
+      </c>
+      <c r="AB24">
+        <v>0</v>
+      </c>
+      <c r="AC24">
+        <v>0</v>
+      </c>
+      <c r="AD24">
+        <v>0</v>
+      </c>
+      <c r="AE24">
+        <v>0</v>
+      </c>
+      <c r="AF24">
+        <v>0</v>
+      </c>
+      <c r="AG24">
+        <v>0</v>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ24">
+        <v>0</v>
+      </c>
+      <c r="AK24">
+        <v>0</v>
+      </c>
+      <c r="AL24">
+        <v>0</v>
+      </c>
+      <c r="AM24">
+        <v>-1</v>
+      </c>
+      <c r="AN24">
+        <v>-1</v>
+      </c>
+      <c r="AO24">
+        <v>-1</v>
+      </c>
+      <c r="AP24">
+        <v>-1</v>
+      </c>
+      <c r="AQ24">
+        <v>0</v>
+      </c>
+      <c r="AR24">
+        <v>0</v>
+      </c>
+      <c r="AS24">
+        <v>0</v>
+      </c>
+      <c r="AT24">
+        <v>0</v>
+      </c>
+      <c r="AU24" t="inlineStr">
+        <is>
+          <t>2026-09-16 14:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Germany 3. Liga</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Ingolstadt</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Hoffenheim II</t>
+        </is>
+      </c>
+      <c r="G25">
+        <v>0</v>
+      </c>
+      <c r="H25">
+        <v>0</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>0</v>
+      </c>
+      <c r="K25">
+        <v>0</v>
+      </c>
+      <c r="L25">
+        <v>0</v>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N25">
+        <v>0</v>
+      </c>
+      <c r="O25">
+        <v>0</v>
+      </c>
+      <c r="P25">
+        <v>0</v>
+      </c>
+      <c r="Q25">
+        <v>0</v>
+      </c>
+      <c r="R25">
+        <v>0</v>
+      </c>
+      <c r="S25">
+        <v>0</v>
+      </c>
+      <c r="T25">
+        <v>0</v>
+      </c>
+      <c r="U25">
+        <v>0</v>
+      </c>
+      <c r="V25">
+        <v>0</v>
+      </c>
+      <c r="W25">
+        <v>0</v>
+      </c>
+      <c r="X25">
+        <v>0</v>
+      </c>
+      <c r="Y25">
+        <v>0</v>
+      </c>
+      <c r="Z25">
+        <v>0</v>
+      </c>
+      <c r="AA25">
+        <v>0</v>
+      </c>
+      <c r="AB25">
+        <v>0</v>
+      </c>
+      <c r="AC25">
+        <v>0</v>
+      </c>
+      <c r="AD25">
+        <v>0</v>
+      </c>
+      <c r="AE25">
+        <v>0</v>
+      </c>
+      <c r="AF25">
+        <v>0</v>
+      </c>
+      <c r="AG25">
+        <v>0</v>
+      </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ25">
+        <v>0</v>
+      </c>
+      <c r="AK25">
+        <v>0</v>
+      </c>
+      <c r="AL25">
+        <v>0</v>
+      </c>
+      <c r="AM25">
+        <v>-1</v>
+      </c>
+      <c r="AN25">
+        <v>-1</v>
+      </c>
+      <c r="AO25">
+        <v>-1</v>
+      </c>
+      <c r="AP25">
+        <v>-1</v>
+      </c>
+      <c r="AQ25">
+        <v>0</v>
+      </c>
+      <c r="AR25">
+        <v>0</v>
+      </c>
+      <c r="AS25">
+        <v>0</v>
+      </c>
+      <c r="AT25">
+        <v>0</v>
+      </c>
+      <c r="AU25" t="inlineStr">
+        <is>
+          <t>2026-09-16 14:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Germany 3. Liga</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Waldhof Mannheim</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Rot-Weiss Essen</t>
+        </is>
+      </c>
+      <c r="G26">
+        <v>0</v>
+      </c>
+      <c r="H26">
+        <v>0</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>0</v>
+      </c>
+      <c r="K26">
+        <v>0</v>
+      </c>
+      <c r="L26">
+        <v>0</v>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N26">
+        <v>0</v>
+      </c>
+      <c r="O26">
+        <v>0</v>
+      </c>
+      <c r="P26">
+        <v>0</v>
+      </c>
+      <c r="Q26">
+        <v>0</v>
+      </c>
+      <c r="R26">
+        <v>0</v>
+      </c>
+      <c r="S26">
+        <v>0</v>
+      </c>
+      <c r="T26">
+        <v>0</v>
+      </c>
+      <c r="U26">
+        <v>0</v>
+      </c>
+      <c r="V26">
+        <v>0</v>
+      </c>
+      <c r="W26">
+        <v>0</v>
+      </c>
+      <c r="X26">
+        <v>0</v>
+      </c>
+      <c r="Y26">
+        <v>0</v>
+      </c>
+      <c r="Z26">
+        <v>0</v>
+      </c>
+      <c r="AA26">
+        <v>0</v>
+      </c>
+      <c r="AB26">
+        <v>0</v>
+      </c>
+      <c r="AC26">
+        <v>0</v>
+      </c>
+      <c r="AD26">
+        <v>0</v>
+      </c>
+      <c r="AE26">
+        <v>0</v>
+      </c>
+      <c r="AF26">
+        <v>0</v>
+      </c>
+      <c r="AG26">
+        <v>0</v>
+      </c>
+      <c r="AH26" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ26">
+        <v>0</v>
+      </c>
+      <c r="AK26">
+        <v>0</v>
+      </c>
+      <c r="AL26">
+        <v>0</v>
+      </c>
+      <c r="AM26">
+        <v>-1</v>
+      </c>
+      <c r="AN26">
+        <v>-1</v>
+      </c>
+      <c r="AO26">
+        <v>-1</v>
+      </c>
+      <c r="AP26">
+        <v>-1</v>
+      </c>
+      <c r="AQ26">
+        <v>0</v>
+      </c>
+      <c r="AR26">
+        <v>0</v>
+      </c>
+      <c r="AS26">
+        <v>0</v>
+      </c>
+      <c r="AT26">
+        <v>0</v>
+      </c>
+      <c r="AU26" t="inlineStr">
+        <is>
+          <t>2026-09-16 14:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Spain La Liga</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Atlético Madrid</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>CA Osasuna</t>
+        </is>
+      </c>
+      <c r="G27">
+        <v>0</v>
+      </c>
+      <c r="H27">
+        <v>0</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>0</v>
+      </c>
+      <c r="K27">
+        <v>0</v>
+      </c>
+      <c r="L27">
+        <v>0</v>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N27">
+        <v>0</v>
+      </c>
+      <c r="O27">
+        <v>0</v>
+      </c>
+      <c r="P27">
+        <v>0</v>
+      </c>
+      <c r="Q27">
+        <v>0</v>
+      </c>
+      <c r="R27">
+        <v>0</v>
+      </c>
+      <c r="S27">
+        <v>0</v>
+      </c>
+      <c r="T27">
+        <v>0</v>
+      </c>
+      <c r="U27">
+        <v>0</v>
+      </c>
+      <c r="V27">
+        <v>0</v>
+      </c>
+      <c r="W27">
+        <v>0</v>
+      </c>
+      <c r="X27">
+        <v>0</v>
+      </c>
+      <c r="Y27">
+        <v>0</v>
+      </c>
+      <c r="Z27">
+        <v>0</v>
+      </c>
+      <c r="AA27">
+        <v>0</v>
+      </c>
+      <c r="AB27">
+        <v>0</v>
+      </c>
+      <c r="AC27">
+        <v>0</v>
+      </c>
+      <c r="AD27">
+        <v>0</v>
+      </c>
+      <c r="AE27">
+        <v>0</v>
+      </c>
+      <c r="AF27">
+        <v>0</v>
+      </c>
+      <c r="AG27">
+        <v>0</v>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ27">
+        <v>0</v>
+      </c>
+      <c r="AK27">
+        <v>0</v>
+      </c>
+      <c r="AL27">
+        <v>0</v>
+      </c>
+      <c r="AM27">
+        <v>-1</v>
+      </c>
+      <c r="AN27">
+        <v>-1</v>
+      </c>
+      <c r="AO27">
+        <v>-1</v>
+      </c>
+      <c r="AP27">
+        <v>-1</v>
+      </c>
+      <c r="AQ27">
+        <v>0</v>
+      </c>
+      <c r="AR27">
+        <v>0</v>
+      </c>
+      <c r="AS27">
+        <v>0</v>
+      </c>
+      <c r="AT27">
+        <v>0</v>
+      </c>
+      <c r="AU27" t="inlineStr">
+        <is>
+          <t>2026-09-16 14:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Spain La Liga</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Deportivo La Coruña</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Sevilla FC</t>
+        </is>
+      </c>
+      <c r="G28">
+        <v>0</v>
+      </c>
+      <c r="H28">
+        <v>0</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>0</v>
+      </c>
+      <c r="K28">
+        <v>0</v>
+      </c>
+      <c r="L28">
+        <v>0</v>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N28">
+        <v>0</v>
+      </c>
+      <c r="O28">
+        <v>0</v>
+      </c>
+      <c r="P28">
+        <v>0</v>
+      </c>
+      <c r="Q28">
+        <v>0</v>
+      </c>
+      <c r="R28">
+        <v>0</v>
+      </c>
+      <c r="S28">
+        <v>0</v>
+      </c>
+      <c r="T28">
+        <v>0</v>
+      </c>
+      <c r="U28">
+        <v>0</v>
+      </c>
+      <c r="V28">
+        <v>0</v>
+      </c>
+      <c r="W28">
+        <v>0</v>
+      </c>
+      <c r="X28">
+        <v>0</v>
+      </c>
+      <c r="Y28">
+        <v>0</v>
+      </c>
+      <c r="Z28">
+        <v>0</v>
+      </c>
+      <c r="AA28">
+        <v>0</v>
+      </c>
+      <c r="AB28">
+        <v>0</v>
+      </c>
+      <c r="AC28">
+        <v>0</v>
+      </c>
+      <c r="AD28">
+        <v>0</v>
+      </c>
+      <c r="AE28">
+        <v>0</v>
+      </c>
+      <c r="AF28">
+        <v>0</v>
+      </c>
+      <c r="AG28">
+        <v>0</v>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI28" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ28">
+        <v>0</v>
+      </c>
+      <c r="AK28">
+        <v>0</v>
+      </c>
+      <c r="AL28">
+        <v>0</v>
+      </c>
+      <c r="AM28">
+        <v>-1</v>
+      </c>
+      <c r="AN28">
+        <v>-1</v>
+      </c>
+      <c r="AO28">
+        <v>-1</v>
+      </c>
+      <c r="AP28">
+        <v>-1</v>
+      </c>
+      <c r="AQ28">
+        <v>0</v>
+      </c>
+      <c r="AR28">
+        <v>0</v>
+      </c>
+      <c r="AS28">
+        <v>0</v>
+      </c>
+      <c r="AT28">
+        <v>0</v>
+      </c>
+      <c r="AU28" t="inlineStr">
+        <is>
+          <t>2026-09-16 14:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Sweden Allsvenskan</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>AIK</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Mjällby</t>
+        </is>
+      </c>
+      <c r="G29">
+        <v>0</v>
+      </c>
+      <c r="H29">
+        <v>0</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>0</v>
+      </c>
+      <c r="K29">
+        <v>0</v>
+      </c>
+      <c r="L29">
+        <v>0</v>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N29">
+        <v>0</v>
+      </c>
+      <c r="O29">
+        <v>0</v>
+      </c>
+      <c r="P29">
+        <v>0</v>
+      </c>
+      <c r="Q29">
+        <v>0</v>
+      </c>
+      <c r="R29">
+        <v>0</v>
+      </c>
+      <c r="S29">
+        <v>0</v>
+      </c>
+      <c r="T29">
+        <v>0</v>
+      </c>
+      <c r="U29">
+        <v>0</v>
+      </c>
+      <c r="V29">
+        <v>0</v>
+      </c>
+      <c r="W29">
+        <v>0</v>
+      </c>
+      <c r="X29">
+        <v>0</v>
+      </c>
+      <c r="Y29">
+        <v>0</v>
+      </c>
+      <c r="Z29">
+        <v>0</v>
+      </c>
+      <c r="AA29">
+        <v>0</v>
+      </c>
+      <c r="AB29">
+        <v>0</v>
+      </c>
+      <c r="AC29">
+        <v>0</v>
+      </c>
+      <c r="AD29">
+        <v>0</v>
+      </c>
+      <c r="AE29">
+        <v>0</v>
+      </c>
+      <c r="AF29">
+        <v>0</v>
+      </c>
+      <c r="AG29">
+        <v>0</v>
+      </c>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI29" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ29">
+        <v>0</v>
+      </c>
+      <c r="AK29">
+        <v>0</v>
+      </c>
+      <c r="AL29">
+        <v>0</v>
+      </c>
+      <c r="AM29">
+        <v>-1</v>
+      </c>
+      <c r="AN29">
+        <v>-1</v>
+      </c>
+      <c r="AO29">
+        <v>-1</v>
+      </c>
+      <c r="AP29">
+        <v>-1</v>
+      </c>
+      <c r="AQ29">
+        <v>0</v>
+      </c>
+      <c r="AR29">
+        <v>0</v>
+      </c>
+      <c r="AS29">
+        <v>0</v>
+      </c>
+      <c r="AT29">
+        <v>0</v>
+      </c>
+      <c r="AU29" t="inlineStr">
+        <is>
+          <t>2026-09-16 14:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Russia Russian Premier League</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Baltika</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Zenit</t>
+        </is>
+      </c>
+      <c r="G30">
+        <v>0</v>
+      </c>
+      <c r="H30">
+        <v>0</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>0</v>
+      </c>
+      <c r="K30">
+        <v>0</v>
+      </c>
+      <c r="L30">
+        <v>0</v>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N30">
+        <v>0</v>
+      </c>
+      <c r="O30">
+        <v>0</v>
+      </c>
+      <c r="P30">
+        <v>0</v>
+      </c>
+      <c r="Q30">
+        <v>0</v>
+      </c>
+      <c r="R30">
+        <v>0</v>
+      </c>
+      <c r="S30">
+        <v>0</v>
+      </c>
+      <c r="T30">
+        <v>0</v>
+      </c>
+      <c r="U30">
+        <v>0</v>
+      </c>
+      <c r="V30">
+        <v>0</v>
+      </c>
+      <c r="W30">
+        <v>0</v>
+      </c>
+      <c r="X30">
+        <v>0</v>
+      </c>
+      <c r="Y30">
+        <v>0</v>
+      </c>
+      <c r="Z30">
+        <v>0</v>
+      </c>
+      <c r="AA30">
+        <v>0</v>
+      </c>
+      <c r="AB30">
+        <v>0</v>
+      </c>
+      <c r="AC30">
+        <v>0</v>
+      </c>
+      <c r="AD30">
+        <v>0</v>
+      </c>
+      <c r="AE30">
+        <v>0</v>
+      </c>
+      <c r="AF30">
+        <v>0</v>
+      </c>
+      <c r="AG30">
+        <v>0</v>
+      </c>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI30" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ30">
+        <v>0</v>
+      </c>
+      <c r="AK30">
+        <v>0</v>
+      </c>
+      <c r="AL30">
+        <v>0</v>
+      </c>
+      <c r="AM30">
+        <v>-1</v>
+      </c>
+      <c r="AN30">
+        <v>-1</v>
+      </c>
+      <c r="AO30">
+        <v>-1</v>
+      </c>
+      <c r="AP30">
+        <v>-1</v>
+      </c>
+      <c r="AQ30">
+        <v>0</v>
+      </c>
+      <c r="AR30">
+        <v>0</v>
+      </c>
+      <c r="AS30">
+        <v>0</v>
+      </c>
+      <c r="AT30">
+        <v>0</v>
+      </c>
+      <c r="AU30" t="inlineStr">
+        <is>
+          <t>2026-09-16 14:45:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Russia Russian Premier League</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Lokomotiv Moskva</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Krylya Sovetov</t>
+        </is>
+      </c>
+      <c r="G31">
+        <v>0</v>
+      </c>
+      <c r="H31">
+        <v>0</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>0</v>
+      </c>
+      <c r="K31">
+        <v>0</v>
+      </c>
+      <c r="L31">
+        <v>0</v>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N31">
+        <v>0</v>
+      </c>
+      <c r="O31">
+        <v>0</v>
+      </c>
+      <c r="P31">
+        <v>0</v>
+      </c>
+      <c r="Q31">
+        <v>0</v>
+      </c>
+      <c r="R31">
+        <v>0</v>
+      </c>
+      <c r="S31">
+        <v>0</v>
+      </c>
+      <c r="T31">
+        <v>0</v>
+      </c>
+      <c r="U31">
+        <v>0</v>
+      </c>
+      <c r="V31">
+        <v>0</v>
+      </c>
+      <c r="W31">
+        <v>0</v>
+      </c>
+      <c r="X31">
+        <v>0</v>
+      </c>
+      <c r="Y31">
+        <v>0</v>
+      </c>
+      <c r="Z31">
+        <v>0</v>
+      </c>
+      <c r="AA31">
+        <v>0</v>
+      </c>
+      <c r="AB31">
+        <v>0</v>
+      </c>
+      <c r="AC31">
+        <v>0</v>
+      </c>
+      <c r="AD31">
+        <v>0</v>
+      </c>
+      <c r="AE31">
+        <v>0</v>
+      </c>
+      <c r="AF31">
+        <v>0</v>
+      </c>
+      <c r="AG31">
+        <v>0</v>
+      </c>
+      <c r="AH31" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ31">
+        <v>0</v>
+      </c>
+      <c r="AK31">
+        <v>0</v>
+      </c>
+      <c r="AL31">
+        <v>0</v>
+      </c>
+      <c r="AM31">
+        <v>-1</v>
+      </c>
+      <c r="AN31">
+        <v>-1</v>
+      </c>
+      <c r="AO31">
+        <v>-1</v>
+      </c>
+      <c r="AP31">
+        <v>-1</v>
+      </c>
+      <c r="AQ31">
+        <v>0</v>
+      </c>
+      <c r="AR31">
+        <v>0</v>
+      </c>
+      <c r="AS31">
+        <v>0</v>
+      </c>
+      <c r="AT31">
+        <v>0</v>
+      </c>
+      <c r="AU31" t="inlineStr">
+        <is>
+          <t>2026-09-16 14:45:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Argentina Prim B Nacional</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>San Martín San Juan</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Tristán Suárez</t>
+        </is>
+      </c>
+      <c r="G32">
+        <v>0</v>
+      </c>
+      <c r="H32">
+        <v>0</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>0</v>
+      </c>
+      <c r="K32">
+        <v>0</v>
+      </c>
+      <c r="L32">
+        <v>0</v>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>suspended</t>
+        </is>
+      </c>
+      <c r="N32">
+        <v>1.79</v>
+      </c>
+      <c r="O32">
+        <v>2.47</v>
+      </c>
+      <c r="P32">
+        <v>4.6</v>
+      </c>
+      <c r="Q32">
+        <v>2.7</v>
+      </c>
+      <c r="R32">
+        <v>1.85</v>
+      </c>
+      <c r="S32">
+        <v>1.62</v>
+      </c>
+      <c r="T32">
+        <v>2.04</v>
+      </c>
+      <c r="U32">
+        <v>4</v>
+      </c>
+      <c r="V32">
+        <v>1.17</v>
+      </c>
+      <c r="W32">
+        <v>1.03</v>
+      </c>
+      <c r="X32">
+        <v>1.15</v>
+      </c>
+      <c r="Y32">
+        <v>1.67</v>
+      </c>
+      <c r="Z32">
+        <v>2.14</v>
+      </c>
+      <c r="AA32">
+        <v>3.1</v>
+      </c>
+      <c r="AB32">
+        <v>1.34</v>
+      </c>
+      <c r="AC32">
+        <v>6.5</v>
+      </c>
+      <c r="AD32">
+        <v>1.05</v>
+      </c>
+      <c r="AE32">
+        <v>1.01</v>
+      </c>
+      <c r="AF32">
+        <v>2.6</v>
+      </c>
+      <c r="AG32">
+        <v>1.44</v>
+      </c>
+      <c r="AH32" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI32" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ32">
+        <v>1.33</v>
+      </c>
+      <c r="AK32">
+        <v>1.76</v>
+      </c>
+      <c r="AL32">
+        <v>0</v>
+      </c>
+      <c r="AM32">
+        <v>-1</v>
+      </c>
+      <c r="AN32">
+        <v>-1</v>
+      </c>
+      <c r="AO32">
+        <v>-1</v>
+      </c>
+      <c r="AP32">
+        <v>-1</v>
+      </c>
+      <c r="AQ32">
+        <v>0</v>
+      </c>
+      <c r="AR32">
+        <v>0</v>
+      </c>
+      <c r="AS32">
+        <v>0</v>
+      </c>
+      <c r="AT32">
+        <v>0</v>
+      </c>
+      <c r="AU32" t="inlineStr">
+        <is>
+          <t>2026-09-16 15:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Italy Serie C Group B</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Livorno</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Vado</t>
+        </is>
+      </c>
+      <c r="G33">
+        <v>0</v>
+      </c>
+      <c r="H33">
+        <v>0</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>0</v>
+      </c>
+      <c r="K33">
+        <v>0</v>
+      </c>
+      <c r="L33">
+        <v>0</v>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N33">
+        <v>0</v>
+      </c>
+      <c r="O33">
+        <v>0</v>
+      </c>
+      <c r="P33">
+        <v>0</v>
+      </c>
+      <c r="Q33">
+        <v>0</v>
+      </c>
+      <c r="R33">
+        <v>0</v>
+      </c>
+      <c r="S33">
+        <v>0</v>
+      </c>
+      <c r="T33">
+        <v>0</v>
+      </c>
+      <c r="U33">
+        <v>0</v>
+      </c>
+      <c r="V33">
+        <v>0</v>
+      </c>
+      <c r="W33">
+        <v>0</v>
+      </c>
+      <c r="X33">
+        <v>0</v>
+      </c>
+      <c r="Y33">
+        <v>0</v>
+      </c>
+      <c r="Z33">
+        <v>0</v>
+      </c>
+      <c r="AA33">
+        <v>0</v>
+      </c>
+      <c r="AB33">
+        <v>0</v>
+      </c>
+      <c r="AC33">
+        <v>0</v>
+      </c>
+      <c r="AD33">
+        <v>0</v>
+      </c>
+      <c r="AE33">
+        <v>0</v>
+      </c>
+      <c r="AF33">
+        <v>0</v>
+      </c>
+      <c r="AG33">
+        <v>0</v>
+      </c>
+      <c r="AH33" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI33" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ33">
+        <v>0</v>
+      </c>
+      <c r="AK33">
+        <v>0</v>
+      </c>
+      <c r="AL33">
+        <v>0</v>
+      </c>
+      <c r="AM33">
+        <v>-1</v>
+      </c>
+      <c r="AN33">
+        <v>-1</v>
+      </c>
+      <c r="AO33">
+        <v>-1</v>
+      </c>
+      <c r="AP33">
+        <v>-1</v>
+      </c>
+      <c r="AQ33">
+        <v>0</v>
+      </c>
+      <c r="AR33">
+        <v>0</v>
+      </c>
+      <c r="AS33">
+        <v>0</v>
+      </c>
+      <c r="AT33">
+        <v>0</v>
+      </c>
+      <c r="AU33" t="inlineStr">
+        <is>
+          <t>2026-09-16 16:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Italy Serie C Group B</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Vis Pesaro</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Reggiana</t>
+        </is>
+      </c>
+      <c r="G34">
+        <v>0</v>
+      </c>
+      <c r="H34">
+        <v>0</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>0</v>
+      </c>
+      <c r="K34">
+        <v>0</v>
+      </c>
+      <c r="L34">
+        <v>0</v>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N34">
+        <v>0</v>
+      </c>
+      <c r="O34">
+        <v>0</v>
+      </c>
+      <c r="P34">
+        <v>0</v>
+      </c>
+      <c r="Q34">
+        <v>0</v>
+      </c>
+      <c r="R34">
+        <v>0</v>
+      </c>
+      <c r="S34">
+        <v>0</v>
+      </c>
+      <c r="T34">
+        <v>0</v>
+      </c>
+      <c r="U34">
+        <v>0</v>
+      </c>
+      <c r="V34">
+        <v>0</v>
+      </c>
+      <c r="W34">
+        <v>0</v>
+      </c>
+      <c r="X34">
+        <v>0</v>
+      </c>
+      <c r="Y34">
+        <v>0</v>
+      </c>
+      <c r="Z34">
+        <v>0</v>
+      </c>
+      <c r="AA34">
+        <v>0</v>
+      </c>
+      <c r="AB34">
+        <v>0</v>
+      </c>
+      <c r="AC34">
+        <v>0</v>
+      </c>
+      <c r="AD34">
+        <v>0</v>
+      </c>
+      <c r="AE34">
+        <v>0</v>
+      </c>
+      <c r="AF34">
+        <v>0</v>
+      </c>
+      <c r="AG34">
+        <v>0</v>
+      </c>
+      <c r="AH34" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI34" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ34">
+        <v>0</v>
+      </c>
+      <c r="AK34">
+        <v>0</v>
+      </c>
+      <c r="AL34">
+        <v>0</v>
+      </c>
+      <c r="AM34">
+        <v>-1</v>
+      </c>
+      <c r="AN34">
+        <v>-1</v>
+      </c>
+      <c r="AO34">
+        <v>-1</v>
+      </c>
+      <c r="AP34">
+        <v>-1</v>
+      </c>
+      <c r="AQ34">
+        <v>0</v>
+      </c>
+      <c r="AR34">
+        <v>0</v>
+      </c>
+      <c r="AS34">
+        <v>0</v>
+      </c>
+      <c r="AT34">
+        <v>0</v>
+      </c>
+      <c r="AU34" t="inlineStr">
+        <is>
+          <t>2026-09-16 16:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Italy Serie C Group B</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Perugia</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Spezia</t>
+        </is>
+      </c>
+      <c r="G35">
+        <v>0</v>
+      </c>
+      <c r="H35">
+        <v>0</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>0</v>
+      </c>
+      <c r="K35">
+        <v>0</v>
+      </c>
+      <c r="L35">
+        <v>0</v>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N35">
+        <v>0</v>
+      </c>
+      <c r="O35">
+        <v>0</v>
+      </c>
+      <c r="P35">
+        <v>0</v>
+      </c>
+      <c r="Q35">
+        <v>0</v>
+      </c>
+      <c r="R35">
+        <v>0</v>
+      </c>
+      <c r="S35">
+        <v>0</v>
+      </c>
+      <c r="T35">
+        <v>0</v>
+      </c>
+      <c r="U35">
+        <v>0</v>
+      </c>
+      <c r="V35">
+        <v>0</v>
+      </c>
+      <c r="W35">
+        <v>0</v>
+      </c>
+      <c r="X35">
+        <v>0</v>
+      </c>
+      <c r="Y35">
+        <v>0</v>
+      </c>
+      <c r="Z35">
+        <v>0</v>
+      </c>
+      <c r="AA35">
+        <v>0</v>
+      </c>
+      <c r="AB35">
+        <v>0</v>
+      </c>
+      <c r="AC35">
+        <v>0</v>
+      </c>
+      <c r="AD35">
+        <v>0</v>
+      </c>
+      <c r="AE35">
+        <v>0</v>
+      </c>
+      <c r="AF35">
+        <v>0</v>
+      </c>
+      <c r="AG35">
+        <v>0</v>
+      </c>
+      <c r="AH35" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI35" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ35">
+        <v>0</v>
+      </c>
+      <c r="AK35">
+        <v>0</v>
+      </c>
+      <c r="AL35">
+        <v>0</v>
+      </c>
+      <c r="AM35">
+        <v>-1</v>
+      </c>
+      <c r="AN35">
+        <v>-1</v>
+      </c>
+      <c r="AO35">
+        <v>-1</v>
+      </c>
+      <c r="AP35">
+        <v>-1</v>
+      </c>
+      <c r="AQ35">
+        <v>0</v>
+      </c>
+      <c r="AR35">
+        <v>0</v>
+      </c>
+      <c r="AS35">
+        <v>0</v>
+      </c>
+      <c r="AT35">
+        <v>0</v>
+      </c>
+      <c r="AU35" t="inlineStr">
+        <is>
+          <t>2026-09-16 16:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Italy Serie C Group B</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Pescara</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Gubbio</t>
+        </is>
+      </c>
+      <c r="G36">
+        <v>0</v>
+      </c>
+      <c r="H36">
+        <v>0</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>0</v>
+      </c>
+      <c r="K36">
+        <v>0</v>
+      </c>
+      <c r="L36">
+        <v>0</v>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N36">
+        <v>0</v>
+      </c>
+      <c r="O36">
+        <v>0</v>
+      </c>
+      <c r="P36">
+        <v>0</v>
+      </c>
+      <c r="Q36">
+        <v>0</v>
+      </c>
+      <c r="R36">
+        <v>0</v>
+      </c>
+      <c r="S36">
+        <v>0</v>
+      </c>
+      <c r="T36">
+        <v>0</v>
+      </c>
+      <c r="U36">
+        <v>0</v>
+      </c>
+      <c r="V36">
+        <v>0</v>
+      </c>
+      <c r="W36">
+        <v>0</v>
+      </c>
+      <c r="X36">
+        <v>0</v>
+      </c>
+      <c r="Y36">
+        <v>0</v>
+      </c>
+      <c r="Z36">
+        <v>0</v>
+      </c>
+      <c r="AA36">
+        <v>0</v>
+      </c>
+      <c r="AB36">
+        <v>0</v>
+      </c>
+      <c r="AC36">
+        <v>0</v>
+      </c>
+      <c r="AD36">
+        <v>0</v>
+      </c>
+      <c r="AE36">
+        <v>0</v>
+      </c>
+      <c r="AF36">
+        <v>0</v>
+      </c>
+      <c r="AG36">
+        <v>0</v>
+      </c>
+      <c r="AH36" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI36" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ36">
+        <v>0</v>
+      </c>
+      <c r="AK36">
+        <v>0</v>
+      </c>
+      <c r="AL36">
+        <v>0</v>
+      </c>
+      <c r="AM36">
+        <v>-1</v>
+      </c>
+      <c r="AN36">
+        <v>-1</v>
+      </c>
+      <c r="AO36">
+        <v>-1</v>
+      </c>
+      <c r="AP36">
+        <v>-1</v>
+      </c>
+      <c r="AQ36">
+        <v>0</v>
+      </c>
+      <c r="AR36">
+        <v>0</v>
+      </c>
+      <c r="AS36">
+        <v>0</v>
+      </c>
+      <c r="AT36">
+        <v>0</v>
+      </c>
+      <c r="AU36" t="inlineStr">
+        <is>
+          <t>2026-09-16 16:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Bolivia LFPB</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Guabirá</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Aurora</t>
+        </is>
+      </c>
+      <c r="G37">
+        <v>0</v>
+      </c>
+      <c r="H37">
+        <v>0</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>0</v>
+      </c>
+      <c r="K37">
+        <v>0</v>
+      </c>
+      <c r="L37">
+        <v>0</v>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N37">
+        <v>0</v>
+      </c>
+      <c r="O37">
+        <v>0</v>
+      </c>
+      <c r="P37">
+        <v>0</v>
+      </c>
+      <c r="Q37">
+        <v>0</v>
+      </c>
+      <c r="R37">
+        <v>0</v>
+      </c>
+      <c r="S37">
+        <v>0</v>
+      </c>
+      <c r="T37">
+        <v>0</v>
+      </c>
+      <c r="U37">
+        <v>0</v>
+      </c>
+      <c r="V37">
+        <v>0</v>
+      </c>
+      <c r="W37">
+        <v>0</v>
+      </c>
+      <c r="X37">
+        <v>0</v>
+      </c>
+      <c r="Y37">
+        <v>0</v>
+      </c>
+      <c r="Z37">
+        <v>0</v>
+      </c>
+      <c r="AA37">
+        <v>0</v>
+      </c>
+      <c r="AB37">
+        <v>0</v>
+      </c>
+      <c r="AC37">
+        <v>0</v>
+      </c>
+      <c r="AD37">
+        <v>0</v>
+      </c>
+      <c r="AE37">
+        <v>0</v>
+      </c>
+      <c r="AF37">
+        <v>0</v>
+      </c>
+      <c r="AG37">
+        <v>0</v>
+      </c>
+      <c r="AH37" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI37" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ37">
+        <v>0</v>
+      </c>
+      <c r="AK37">
+        <v>0</v>
+      </c>
+      <c r="AL37">
+        <v>0</v>
+      </c>
+      <c r="AM37">
+        <v>-1</v>
+      </c>
+      <c r="AN37">
+        <v>-1</v>
+      </c>
+      <c r="AO37">
+        <v>-1</v>
+      </c>
+      <c r="AP37">
+        <v>-1</v>
+      </c>
+      <c r="AQ37">
+        <v>0</v>
+      </c>
+      <c r="AR37">
+        <v>0</v>
+      </c>
+      <c r="AS37">
+        <v>0</v>
+      </c>
+      <c r="AT37">
+        <v>0</v>
+      </c>
+      <c r="AU37" t="inlineStr">
+        <is>
+          <t>2026-09-16 16:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Spain La Liga</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>FC Barcelona</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Racing Santander</t>
+        </is>
+      </c>
+      <c r="G38">
+        <v>0</v>
+      </c>
+      <c r="H38">
+        <v>0</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>0</v>
+      </c>
+      <c r="K38">
+        <v>0</v>
+      </c>
+      <c r="L38">
+        <v>0</v>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N38">
+        <v>0</v>
+      </c>
+      <c r="O38">
+        <v>0</v>
+      </c>
+      <c r="P38">
+        <v>0</v>
+      </c>
+      <c r="Q38">
+        <v>0</v>
+      </c>
+      <c r="R38">
+        <v>0</v>
+      </c>
+      <c r="S38">
+        <v>0</v>
+      </c>
+      <c r="T38">
+        <v>0</v>
+      </c>
+      <c r="U38">
+        <v>0</v>
+      </c>
+      <c r="V38">
+        <v>0</v>
+      </c>
+      <c r="W38">
+        <v>0</v>
+      </c>
+      <c r="X38">
+        <v>0</v>
+      </c>
+      <c r="Y38">
+        <v>0</v>
+      </c>
+      <c r="Z38">
+        <v>0</v>
+      </c>
+      <c r="AA38">
+        <v>0</v>
+      </c>
+      <c r="AB38">
+        <v>0</v>
+      </c>
+      <c r="AC38">
+        <v>0</v>
+      </c>
+      <c r="AD38">
+        <v>0</v>
+      </c>
+      <c r="AE38">
+        <v>0</v>
+      </c>
+      <c r="AF38">
+        <v>0</v>
+      </c>
+      <c r="AG38">
+        <v>0</v>
+      </c>
+      <c r="AH38" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI38" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ38">
+        <v>0</v>
+      </c>
+      <c r="AK38">
+        <v>0</v>
+      </c>
+      <c r="AL38">
+        <v>0</v>
+      </c>
+      <c r="AM38">
+        <v>-1</v>
+      </c>
+      <c r="AN38">
+        <v>-1</v>
+      </c>
+      <c r="AO38">
+        <v>-1</v>
+      </c>
+      <c r="AP38">
+        <v>-1</v>
+      </c>
+      <c r="AQ38">
+        <v>0</v>
+      </c>
+      <c r="AR38">
+        <v>0</v>
+      </c>
+      <c r="AS38">
+        <v>0</v>
+      </c>
+      <c r="AT38">
+        <v>0</v>
+      </c>
+      <c r="AU38" t="inlineStr">
+        <is>
+          <t>2026-09-16 16:30:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Spain La Liga</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Levante UD</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Athletic Club Bilbao</t>
+        </is>
+      </c>
+      <c r="G39">
+        <v>0</v>
+      </c>
+      <c r="H39">
+        <v>0</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>0</v>
+      </c>
+      <c r="K39">
+        <v>0</v>
+      </c>
+      <c r="L39">
+        <v>0</v>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N39">
+        <v>0</v>
+      </c>
+      <c r="O39">
+        <v>0</v>
+      </c>
+      <c r="P39">
+        <v>0</v>
+      </c>
+      <c r="Q39">
+        <v>0</v>
+      </c>
+      <c r="R39">
+        <v>0</v>
+      </c>
+      <c r="S39">
+        <v>0</v>
+      </c>
+      <c r="T39">
+        <v>0</v>
+      </c>
+      <c r="U39">
+        <v>0</v>
+      </c>
+      <c r="V39">
+        <v>0</v>
+      </c>
+      <c r="W39">
+        <v>0</v>
+      </c>
+      <c r="X39">
+        <v>0</v>
+      </c>
+      <c r="Y39">
+        <v>0</v>
+      </c>
+      <c r="Z39">
+        <v>0</v>
+      </c>
+      <c r="AA39">
+        <v>0</v>
+      </c>
+      <c r="AB39">
+        <v>0</v>
+      </c>
+      <c r="AC39">
+        <v>0</v>
+      </c>
+      <c r="AD39">
+        <v>0</v>
+      </c>
+      <c r="AE39">
+        <v>0</v>
+      </c>
+      <c r="AF39">
+        <v>0</v>
+      </c>
+      <c r="AG39">
+        <v>0</v>
+      </c>
+      <c r="AH39" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI39" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ39">
+        <v>0</v>
+      </c>
+      <c r="AK39">
+        <v>0</v>
+      </c>
+      <c r="AL39">
+        <v>0</v>
+      </c>
+      <c r="AM39">
+        <v>-1</v>
+      </c>
+      <c r="AN39">
+        <v>-1</v>
+      </c>
+      <c r="AO39">
+        <v>-1</v>
+      </c>
+      <c r="AP39">
+        <v>-1</v>
+      </c>
+      <c r="AQ39">
+        <v>0</v>
+      </c>
+      <c r="AR39">
+        <v>0</v>
+      </c>
+      <c r="AS39">
+        <v>0</v>
+      </c>
+      <c r="AT39">
+        <v>0</v>
+      </c>
+      <c r="AU39" t="inlineStr">
+        <is>
+          <t>2026-09-16 16:30:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Chile Primera División</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Coquimbo Unido</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Huachipato</t>
+        </is>
+      </c>
+      <c r="G40">
+        <v>0</v>
+      </c>
+      <c r="H40">
+        <v>0</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>0</v>
+      </c>
+      <c r="K40">
+        <v>0</v>
+      </c>
+      <c r="L40">
+        <v>0</v>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N40">
+        <v>1.54</v>
+      </c>
+      <c r="O40">
+        <v>4.2</v>
+      </c>
+      <c r="P40">
+        <v>6.54</v>
+      </c>
+      <c r="Q40">
+        <v>1.9</v>
+      </c>
+      <c r="R40">
+        <v>2.4</v>
+      </c>
+      <c r="S40">
+        <v>1.3</v>
+      </c>
+      <c r="T40">
+        <v>3.2</v>
+      </c>
+      <c r="U40">
+        <v>2.4</v>
+      </c>
+      <c r="V40">
+        <v>1.5</v>
+      </c>
+      <c r="W40">
+        <v>1.11</v>
+      </c>
+      <c r="X40">
+        <v>1.01</v>
+      </c>
+      <c r="Y40">
+        <v>1.2</v>
+      </c>
+      <c r="Z40">
+        <v>4.1</v>
+      </c>
+      <c r="AA40">
+        <v>1.75</v>
+      </c>
+      <c r="AB40">
+        <v>2.01</v>
+      </c>
+      <c r="AC40">
+        <v>2.75</v>
+      </c>
+      <c r="AD40">
+        <v>1.44</v>
+      </c>
+      <c r="AE40">
+        <v>1.12</v>
+      </c>
+      <c r="AF40">
+        <v>1.85</v>
+      </c>
+      <c r="AG40">
+        <v>1.87</v>
+      </c>
+      <c r="AH40" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI40" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ40">
+        <v>1.09</v>
+      </c>
+      <c r="AK40">
+        <v>2.61</v>
+      </c>
+      <c r="AL40">
+        <v>0</v>
+      </c>
+      <c r="AM40">
+        <v>-1</v>
+      </c>
+      <c r="AN40">
+        <v>-1</v>
+      </c>
+      <c r="AO40">
+        <v>-1</v>
+      </c>
+      <c r="AP40">
+        <v>-1</v>
+      </c>
+      <c r="AQ40">
+        <v>0</v>
+      </c>
+      <c r="AR40">
+        <v>0</v>
+      </c>
+      <c r="AS40">
+        <v>0</v>
+      </c>
+      <c r="AT40">
+        <v>0</v>
+      </c>
+      <c r="AU40" t="inlineStr">
+        <is>
+          <t>2026-09-16 18:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>USA USL Championship</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Hartford Athletic</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Sporting JAX</t>
+        </is>
+      </c>
+      <c r="G41">
+        <v>0</v>
+      </c>
+      <c r="H41">
+        <v>0</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <v>0</v>
+      </c>
+      <c r="K41">
+        <v>0</v>
+      </c>
+      <c r="L41">
+        <v>0</v>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N41">
+        <v>0</v>
+      </c>
+      <c r="O41">
+        <v>0</v>
+      </c>
+      <c r="P41">
+        <v>0</v>
+      </c>
+      <c r="Q41">
+        <v>0</v>
+      </c>
+      <c r="R41">
+        <v>0</v>
+      </c>
+      <c r="S41">
+        <v>0</v>
+      </c>
+      <c r="T41">
+        <v>0</v>
+      </c>
+      <c r="U41">
+        <v>0</v>
+      </c>
+      <c r="V41">
+        <v>0</v>
+      </c>
+      <c r="W41">
+        <v>0</v>
+      </c>
+      <c r="X41">
+        <v>0</v>
+      </c>
+      <c r="Y41">
+        <v>0</v>
+      </c>
+      <c r="Z41">
+        <v>0</v>
+      </c>
+      <c r="AA41">
+        <v>0</v>
+      </c>
+      <c r="AB41">
+        <v>0</v>
+      </c>
+      <c r="AC41">
+        <v>0</v>
+      </c>
+      <c r="AD41">
+        <v>0</v>
+      </c>
+      <c r="AE41">
+        <v>0</v>
+      </c>
+      <c r="AF41">
+        <v>0</v>
+      </c>
+      <c r="AG41">
+        <v>0</v>
+      </c>
+      <c r="AH41" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI41" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ41">
+        <v>0</v>
+      </c>
+      <c r="AK41">
+        <v>0</v>
+      </c>
+      <c r="AL41">
+        <v>0</v>
+      </c>
+      <c r="AM41">
+        <v>-1</v>
+      </c>
+      <c r="AN41">
+        <v>-1</v>
+      </c>
+      <c r="AO41">
+        <v>-1</v>
+      </c>
+      <c r="AP41">
+        <v>-1</v>
+      </c>
+      <c r="AQ41">
+        <v>0</v>
+      </c>
+      <c r="AR41">
+        <v>0</v>
+      </c>
+      <c r="AS41">
+        <v>0</v>
+      </c>
+      <c r="AT41">
+        <v>0</v>
+      </c>
+      <c r="AU41" t="inlineStr">
+        <is>
+          <t>2026-09-16 19:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Botafogo</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Grêmio</t>
+        </is>
+      </c>
+      <c r="G42">
+        <v>0</v>
+      </c>
+      <c r="H42">
+        <v>0</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>0</v>
+      </c>
+      <c r="K42">
+        <v>0</v>
+      </c>
+      <c r="L42">
+        <v>0</v>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>suspended</t>
+        </is>
+      </c>
+      <c r="N42">
+        <v>1.75</v>
+      </c>
+      <c r="O42">
+        <v>3.5</v>
+      </c>
+      <c r="P42">
+        <v>5</v>
+      </c>
+      <c r="Q42">
+        <v>2.3</v>
+      </c>
+      <c r="R42">
+        <v>2.07</v>
+      </c>
+      <c r="S42">
+        <v>1.4</v>
+      </c>
+      <c r="T42">
+        <v>2.73</v>
+      </c>
+      <c r="U42">
+        <v>2.71</v>
+      </c>
+      <c r="V42">
+        <v>1.36</v>
+      </c>
+      <c r="W42">
+        <v>1.03</v>
+      </c>
+      <c r="X42">
+        <v>1</v>
+      </c>
+      <c r="Y42">
+        <v>1.33</v>
+      </c>
+      <c r="Z42">
+        <v>3.3</v>
+      </c>
+      <c r="AA42">
+        <v>2</v>
+      </c>
+      <c r="AB42">
+        <v>1.8</v>
+      </c>
+      <c r="AC42">
+        <v>3.05</v>
+      </c>
+      <c r="AD42">
+        <v>1.25</v>
+      </c>
+      <c r="AE42">
+        <v>1.14</v>
+      </c>
+      <c r="AF42">
+        <v>1.85</v>
+      </c>
+      <c r="AG42">
+        <v>1.85</v>
+      </c>
+      <c r="AH42" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI42" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ42">
+        <v>1.29</v>
+      </c>
+      <c r="AK42">
+        <v>2.12</v>
+      </c>
+      <c r="AL42">
+        <v>0</v>
+      </c>
+      <c r="AM42">
+        <v>-1</v>
+      </c>
+      <c r="AN42">
+        <v>-1</v>
+      </c>
+      <c r="AO42">
+        <v>-1</v>
+      </c>
+      <c r="AP42">
+        <v>-1</v>
+      </c>
+      <c r="AQ42">
+        <v>0</v>
+      </c>
+      <c r="AR42">
+        <v>0</v>
+      </c>
+      <c r="AS42">
+        <v>0</v>
+      </c>
+      <c r="AT42">
+        <v>0</v>
+      </c>
+      <c r="AU42" t="inlineStr">
+        <is>
+          <t>2026-09-16 19:30:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Bolivia LFPB</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Nacional Potosí</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Club Always Ready</t>
+        </is>
+      </c>
+      <c r="G43">
+        <v>0</v>
+      </c>
+      <c r="H43">
+        <v>0</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <v>0</v>
+      </c>
+      <c r="K43">
+        <v>0</v>
+      </c>
+      <c r="L43">
+        <v>0</v>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N43">
+        <v>0</v>
+      </c>
+      <c r="O43">
+        <v>0</v>
+      </c>
+      <c r="P43">
+        <v>0</v>
+      </c>
+      <c r="Q43">
+        <v>0</v>
+      </c>
+      <c r="R43">
+        <v>0</v>
+      </c>
+      <c r="S43">
+        <v>0</v>
+      </c>
+      <c r="T43">
+        <v>0</v>
+      </c>
+      <c r="U43">
+        <v>0</v>
+      </c>
+      <c r="V43">
+        <v>0</v>
+      </c>
+      <c r="W43">
+        <v>0</v>
+      </c>
+      <c r="X43">
+        <v>0</v>
+      </c>
+      <c r="Y43">
+        <v>0</v>
+      </c>
+      <c r="Z43">
+        <v>0</v>
+      </c>
+      <c r="AA43">
+        <v>0</v>
+      </c>
+      <c r="AB43">
+        <v>0</v>
+      </c>
+      <c r="AC43">
+        <v>0</v>
+      </c>
+      <c r="AD43">
+        <v>0</v>
+      </c>
+      <c r="AE43">
+        <v>0</v>
+      </c>
+      <c r="AF43">
+        <v>0</v>
+      </c>
+      <c r="AG43">
+        <v>0</v>
+      </c>
+      <c r="AH43" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI43" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ43">
+        <v>0</v>
+      </c>
+      <c r="AK43">
+        <v>0</v>
+      </c>
+      <c r="AL43">
+        <v>0</v>
+      </c>
+      <c r="AM43">
+        <v>-1</v>
+      </c>
+      <c r="AN43">
+        <v>-1</v>
+      </c>
+      <c r="AO43">
+        <v>-1</v>
+      </c>
+      <c r="AP43">
+        <v>-1</v>
+      </c>
+      <c r="AQ43">
+        <v>0</v>
+      </c>
+      <c r="AR43">
+        <v>0</v>
+      </c>
+      <c r="AS43">
+        <v>0</v>
+      </c>
+      <c r="AT43">
+        <v>0</v>
+      </c>
+      <c r="AU43" t="inlineStr">
+        <is>
+          <t>2026-09-16 19:30:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Uzbekistan Uzbekistan Super League</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Navbahor</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Dinamo Samarqand</t>
+        </is>
+      </c>
+      <c r="G44">
+        <v>0</v>
+      </c>
+      <c r="H44">
+        <v>0</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="J44">
+        <v>0</v>
+      </c>
+      <c r="K44">
+        <v>0</v>
+      </c>
+      <c r="L44">
+        <v>0</v>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N44">
+        <v>0</v>
+      </c>
+      <c r="O44">
+        <v>0</v>
+      </c>
+      <c r="P44">
+        <v>0</v>
+      </c>
+      <c r="Q44">
+        <v>0</v>
+      </c>
+      <c r="R44">
+        <v>0</v>
+      </c>
+      <c r="S44">
+        <v>0</v>
+      </c>
+      <c r="T44">
+        <v>0</v>
+      </c>
+      <c r="U44">
+        <v>0</v>
+      </c>
+      <c r="V44">
+        <v>0</v>
+      </c>
+      <c r="W44">
+        <v>0</v>
+      </c>
+      <c r="X44">
+        <v>0</v>
+      </c>
+      <c r="Y44">
+        <v>0</v>
+      </c>
+      <c r="Z44">
+        <v>0</v>
+      </c>
+      <c r="AA44">
+        <v>0</v>
+      </c>
+      <c r="AB44">
+        <v>0</v>
+      </c>
+      <c r="AC44">
+        <v>0</v>
+      </c>
+      <c r="AD44">
+        <v>0</v>
+      </c>
+      <c r="AE44">
+        <v>0</v>
+      </c>
+      <c r="AF44">
+        <v>0</v>
+      </c>
+      <c r="AG44">
+        <v>0</v>
+      </c>
+      <c r="AH44" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI44" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ44">
+        <v>0</v>
+      </c>
+      <c r="AK44">
+        <v>0</v>
+      </c>
+      <c r="AL44">
+        <v>0</v>
+      </c>
+      <c r="AM44">
+        <v>-1</v>
+      </c>
+      <c r="AN44">
+        <v>-1</v>
+      </c>
+      <c r="AO44">
+        <v>-1</v>
+      </c>
+      <c r="AP44">
+        <v>-1</v>
+      </c>
+      <c r="AQ44">
+        <v>0</v>
+      </c>
+      <c r="AR44">
+        <v>0</v>
+      </c>
+      <c r="AS44">
+        <v>0</v>
+      </c>
+      <c r="AT44">
+        <v>0</v>
+      </c>
+      <c r="AU44" t="inlineStr">
+        <is>
+          <t>2026-09-16 21:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Algeria Ligue 1</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>CR Belouizdad</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>USM Khenchela</t>
+        </is>
+      </c>
+      <c r="G45">
+        <v>0</v>
+      </c>
+      <c r="H45">
+        <v>0</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>0</v>
+      </c>
+      <c r="K45">
+        <v>0</v>
+      </c>
+      <c r="L45">
+        <v>0</v>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N45">
+        <v>0</v>
+      </c>
+      <c r="O45">
+        <v>0</v>
+      </c>
+      <c r="P45">
+        <v>0</v>
+      </c>
+      <c r="Q45">
+        <v>0</v>
+      </c>
+      <c r="R45">
+        <v>0</v>
+      </c>
+      <c r="S45">
+        <v>0</v>
+      </c>
+      <c r="T45">
+        <v>0</v>
+      </c>
+      <c r="U45">
+        <v>0</v>
+      </c>
+      <c r="V45">
+        <v>0</v>
+      </c>
+      <c r="W45">
+        <v>0</v>
+      </c>
+      <c r="X45">
+        <v>0</v>
+      </c>
+      <c r="Y45">
+        <v>0</v>
+      </c>
+      <c r="Z45">
+        <v>0</v>
+      </c>
+      <c r="AA45">
+        <v>0</v>
+      </c>
+      <c r="AB45">
+        <v>0</v>
+      </c>
+      <c r="AC45">
+        <v>0</v>
+      </c>
+      <c r="AD45">
+        <v>0</v>
+      </c>
+      <c r="AE45">
+        <v>0</v>
+      </c>
+      <c r="AF45">
+        <v>0</v>
+      </c>
+      <c r="AG45">
+        <v>0</v>
+      </c>
+      <c r="AH45" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI45" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ45">
+        <v>0</v>
+      </c>
+      <c r="AK45">
+        <v>0</v>
+      </c>
+      <c r="AL45">
+        <v>0</v>
+      </c>
+      <c r="AM45">
+        <v>-1</v>
+      </c>
+      <c r="AN45">
+        <v>-1</v>
+      </c>
+      <c r="AO45">
+        <v>-1</v>
+      </c>
+      <c r="AP45">
+        <v>-1</v>
+      </c>
+      <c r="AQ45">
+        <v>0</v>
+      </c>
+      <c r="AR45">
+        <v>0</v>
+      </c>
+      <c r="AS45">
+        <v>0</v>
+      </c>
+      <c r="AT45">
+        <v>0</v>
+      </c>
+      <c r="AU45" t="inlineStr">
+        <is>
+          <t>2026-09-16 21:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Algeria Ligue 1</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>MC Alger</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Temouchent</t>
+        </is>
+      </c>
+      <c r="G46">
+        <v>0</v>
+      </c>
+      <c r="H46">
+        <v>0</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>0</v>
+      </c>
+      <c r="K46">
+        <v>0</v>
+      </c>
+      <c r="L46">
+        <v>0</v>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N46">
+        <v>0</v>
+      </c>
+      <c r="O46">
+        <v>0</v>
+      </c>
+      <c r="P46">
+        <v>0</v>
+      </c>
+      <c r="Q46">
+        <v>0</v>
+      </c>
+      <c r="R46">
+        <v>0</v>
+      </c>
+      <c r="S46">
+        <v>0</v>
+      </c>
+      <c r="T46">
+        <v>0</v>
+      </c>
+      <c r="U46">
+        <v>0</v>
+      </c>
+      <c r="V46">
+        <v>0</v>
+      </c>
+      <c r="W46">
+        <v>0</v>
+      </c>
+      <c r="X46">
+        <v>0</v>
+      </c>
+      <c r="Y46">
+        <v>0</v>
+      </c>
+      <c r="Z46">
+        <v>0</v>
+      </c>
+      <c r="AA46">
+        <v>0</v>
+      </c>
+      <c r="AB46">
+        <v>0</v>
+      </c>
+      <c r="AC46">
+        <v>0</v>
+      </c>
+      <c r="AD46">
+        <v>0</v>
+      </c>
+      <c r="AE46">
+        <v>0</v>
+      </c>
+      <c r="AF46">
+        <v>0</v>
+      </c>
+      <c r="AG46">
+        <v>0</v>
+      </c>
+      <c r="AH46" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI46" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ46">
+        <v>0</v>
+      </c>
+      <c r="AK46">
+        <v>0</v>
+      </c>
+      <c r="AL46">
+        <v>0</v>
+      </c>
+      <c r="AM46">
+        <v>-1</v>
+      </c>
+      <c r="AN46">
+        <v>-1</v>
+      </c>
+      <c r="AO46">
+        <v>-1</v>
+      </c>
+      <c r="AP46">
+        <v>-1</v>
+      </c>
+      <c r="AQ46">
+        <v>0</v>
+      </c>
+      <c r="AR46">
+        <v>0</v>
+      </c>
+      <c r="AS46">
+        <v>0</v>
+      </c>
+      <c r="AT46">
+        <v>0</v>
+      </c>
+      <c r="AU46" t="inlineStr">
+        <is>
+          <t>2026-09-16 21:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Algeria Ligue 1</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>MB Rouisset</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>USM Alger</t>
+        </is>
+      </c>
+      <c r="G47">
+        <v>0</v>
+      </c>
+      <c r="H47">
+        <v>0</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>0</v>
+      </c>
+      <c r="K47">
+        <v>0</v>
+      </c>
+      <c r="L47">
+        <v>0</v>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N47">
+        <v>0</v>
+      </c>
+      <c r="O47">
+        <v>0</v>
+      </c>
+      <c r="P47">
+        <v>0</v>
+      </c>
+      <c r="Q47">
+        <v>0</v>
+      </c>
+      <c r="R47">
+        <v>0</v>
+      </c>
+      <c r="S47">
+        <v>0</v>
+      </c>
+      <c r="T47">
+        <v>0</v>
+      </c>
+      <c r="U47">
+        <v>0</v>
+      </c>
+      <c r="V47">
+        <v>0</v>
+      </c>
+      <c r="W47">
+        <v>0</v>
+      </c>
+      <c r="X47">
+        <v>0</v>
+      </c>
+      <c r="Y47">
+        <v>0</v>
+      </c>
+      <c r="Z47">
+        <v>0</v>
+      </c>
+      <c r="AA47">
+        <v>0</v>
+      </c>
+      <c r="AB47">
+        <v>0</v>
+      </c>
+      <c r="AC47">
+        <v>0</v>
+      </c>
+      <c r="AD47">
+        <v>0</v>
+      </c>
+      <c r="AE47">
+        <v>0</v>
+      </c>
+      <c r="AF47">
+        <v>0</v>
+      </c>
+      <c r="AG47">
+        <v>0</v>
+      </c>
+      <c r="AH47" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI47" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ47">
+        <v>0</v>
+      </c>
+      <c r="AK47">
+        <v>0</v>
+      </c>
+      <c r="AL47">
+        <v>0</v>
+      </c>
+      <c r="AM47">
+        <v>-1</v>
+      </c>
+      <c r="AN47">
+        <v>-1</v>
+      </c>
+      <c r="AO47">
+        <v>-1</v>
+      </c>
+      <c r="AP47">
+        <v>-1</v>
+      </c>
+      <c r="AQ47">
+        <v>0</v>
+      </c>
+      <c r="AR47">
+        <v>0</v>
+      </c>
+      <c r="AS47">
+        <v>0</v>
+      </c>
+      <c r="AT47">
+        <v>0</v>
+      </c>
+      <c r="AU47" t="inlineStr">
+        <is>
+          <t>2026-09-16 21:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Algeria Ligue 1</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>MC Oran</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>ES Sétif</t>
+        </is>
+      </c>
+      <c r="G48">
+        <v>0</v>
+      </c>
+      <c r="H48">
+        <v>0</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>0</v>
+      </c>
+      <c r="K48">
+        <v>0</v>
+      </c>
+      <c r="L48">
+        <v>0</v>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N48">
+        <v>0</v>
+      </c>
+      <c r="O48">
+        <v>0</v>
+      </c>
+      <c r="P48">
+        <v>0</v>
+      </c>
+      <c r="Q48">
+        <v>0</v>
+      </c>
+      <c r="R48">
+        <v>0</v>
+      </c>
+      <c r="S48">
+        <v>0</v>
+      </c>
+      <c r="T48">
+        <v>0</v>
+      </c>
+      <c r="U48">
+        <v>0</v>
+      </c>
+      <c r="V48">
+        <v>0</v>
+      </c>
+      <c r="W48">
+        <v>0</v>
+      </c>
+      <c r="X48">
+        <v>0</v>
+      </c>
+      <c r="Y48">
+        <v>0</v>
+      </c>
+      <c r="Z48">
+        <v>0</v>
+      </c>
+      <c r="AA48">
+        <v>0</v>
+      </c>
+      <c r="AB48">
+        <v>0</v>
+      </c>
+      <c r="AC48">
+        <v>0</v>
+      </c>
+      <c r="AD48">
+        <v>0</v>
+      </c>
+      <c r="AE48">
+        <v>0</v>
+      </c>
+      <c r="AF48">
+        <v>0</v>
+      </c>
+      <c r="AG48">
+        <v>0</v>
+      </c>
+      <c r="AH48" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI48" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ48">
+        <v>0</v>
+      </c>
+      <c r="AK48">
+        <v>0</v>
+      </c>
+      <c r="AL48">
+        <v>0</v>
+      </c>
+      <c r="AM48">
+        <v>-1</v>
+      </c>
+      <c r="AN48">
+        <v>-1</v>
+      </c>
+      <c r="AO48">
+        <v>-1</v>
+      </c>
+      <c r="AP48">
+        <v>-1</v>
+      </c>
+      <c r="AQ48">
+        <v>0</v>
+      </c>
+      <c r="AR48">
+        <v>0</v>
+      </c>
+      <c r="AS48">
+        <v>0</v>
+      </c>
+      <c r="AT48">
+        <v>0</v>
+      </c>
+      <c r="AU48" t="inlineStr">
+        <is>
+          <t>2026-09-16 21:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Algeria Ligue 1</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>CS Constantine</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>US Biskra</t>
+        </is>
+      </c>
+      <c r="G49">
+        <v>0</v>
+      </c>
+      <c r="H49">
+        <v>0</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>0</v>
+      </c>
+      <c r="K49">
+        <v>0</v>
+      </c>
+      <c r="L49">
+        <v>0</v>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N49">
+        <v>0</v>
+      </c>
+      <c r="O49">
+        <v>0</v>
+      </c>
+      <c r="P49">
+        <v>0</v>
+      </c>
+      <c r="Q49">
+        <v>0</v>
+      </c>
+      <c r="R49">
+        <v>0</v>
+      </c>
+      <c r="S49">
+        <v>0</v>
+      </c>
+      <c r="T49">
+        <v>0</v>
+      </c>
+      <c r="U49">
+        <v>0</v>
+      </c>
+      <c r="V49">
+        <v>0</v>
+      </c>
+      <c r="W49">
+        <v>0</v>
+      </c>
+      <c r="X49">
+        <v>0</v>
+      </c>
+      <c r="Y49">
+        <v>0</v>
+      </c>
+      <c r="Z49">
+        <v>0</v>
+      </c>
+      <c r="AA49">
+        <v>0</v>
+      </c>
+      <c r="AB49">
+        <v>0</v>
+      </c>
+      <c r="AC49">
+        <v>0</v>
+      </c>
+      <c r="AD49">
+        <v>0</v>
+      </c>
+      <c r="AE49">
+        <v>0</v>
+      </c>
+      <c r="AF49">
+        <v>0</v>
+      </c>
+      <c r="AG49">
+        <v>0</v>
+      </c>
+      <c r="AH49" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI49" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ49">
+        <v>0</v>
+      </c>
+      <c r="AK49">
+        <v>0</v>
+      </c>
+      <c r="AL49">
+        <v>0</v>
+      </c>
+      <c r="AM49">
+        <v>-1</v>
+      </c>
+      <c r="AN49">
+        <v>-1</v>
+      </c>
+      <c r="AO49">
+        <v>-1</v>
+      </c>
+      <c r="AP49">
+        <v>-1</v>
+      </c>
+      <c r="AQ49">
+        <v>0</v>
+      </c>
+      <c r="AR49">
+        <v>0</v>
+      </c>
+      <c r="AS49">
+        <v>0</v>
+      </c>
+      <c r="AT49">
+        <v>0</v>
+      </c>
+      <c r="AU49" t="inlineStr">
+        <is>
+          <t>2026-09-16 21:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Algeria Ligue 1</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Ben Aknoun</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>JS El Biar</t>
+        </is>
+      </c>
+      <c r="G50">
+        <v>0</v>
+      </c>
+      <c r="H50">
+        <v>0</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>0</v>
+      </c>
+      <c r="K50">
+        <v>0</v>
+      </c>
+      <c r="L50">
+        <v>0</v>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N50">
+        <v>0</v>
+      </c>
+      <c r="O50">
+        <v>0</v>
+      </c>
+      <c r="P50">
+        <v>0</v>
+      </c>
+      <c r="Q50">
+        <v>0</v>
+      </c>
+      <c r="R50">
+        <v>0</v>
+      </c>
+      <c r="S50">
+        <v>0</v>
+      </c>
+      <c r="T50">
+        <v>0</v>
+      </c>
+      <c r="U50">
+        <v>0</v>
+      </c>
+      <c r="V50">
+        <v>0</v>
+      </c>
+      <c r="W50">
+        <v>0</v>
+      </c>
+      <c r="X50">
+        <v>0</v>
+      </c>
+      <c r="Y50">
+        <v>0</v>
+      </c>
+      <c r="Z50">
+        <v>0</v>
+      </c>
+      <c r="AA50">
+        <v>0</v>
+      </c>
+      <c r="AB50">
+        <v>0</v>
+      </c>
+      <c r="AC50">
+        <v>0</v>
+      </c>
+      <c r="AD50">
+        <v>0</v>
+      </c>
+      <c r="AE50">
+        <v>0</v>
+      </c>
+      <c r="AF50">
+        <v>0</v>
+      </c>
+      <c r="AG50">
+        <v>0</v>
+      </c>
+      <c r="AH50" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI50" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ50">
+        <v>0</v>
+      </c>
+      <c r="AK50">
+        <v>0</v>
+      </c>
+      <c r="AL50">
+        <v>0</v>
+      </c>
+      <c r="AM50">
+        <v>-1</v>
+      </c>
+      <c r="AN50">
+        <v>-1</v>
+      </c>
+      <c r="AO50">
+        <v>-1</v>
+      </c>
+      <c r="AP50">
+        <v>-1</v>
+      </c>
+      <c r="AQ50">
+        <v>0</v>
+      </c>
+      <c r="AR50">
+        <v>0</v>
+      </c>
+      <c r="AS50">
+        <v>0</v>
+      </c>
+      <c r="AT50">
+        <v>0</v>
+      </c>
+      <c r="AU50" t="inlineStr">
+        <is>
+          <t>2026-09-16 21:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Algeria Ligue 1</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>JS Kabylie</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>ASO Chlef</t>
+        </is>
+      </c>
+      <c r="G51">
+        <v>0</v>
+      </c>
+      <c r="H51">
+        <v>0</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <v>0</v>
+      </c>
+      <c r="K51">
+        <v>0</v>
+      </c>
+      <c r="L51">
+        <v>0</v>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N51">
+        <v>0</v>
+      </c>
+      <c r="O51">
+        <v>0</v>
+      </c>
+      <c r="P51">
+        <v>0</v>
+      </c>
+      <c r="Q51">
+        <v>0</v>
+      </c>
+      <c r="R51">
+        <v>0</v>
+      </c>
+      <c r="S51">
+        <v>0</v>
+      </c>
+      <c r="T51">
+        <v>0</v>
+      </c>
+      <c r="U51">
+        <v>0</v>
+      </c>
+      <c r="V51">
+        <v>0</v>
+      </c>
+      <c r="W51">
+        <v>0</v>
+      </c>
+      <c r="X51">
+        <v>0</v>
+      </c>
+      <c r="Y51">
+        <v>0</v>
+      </c>
+      <c r="Z51">
+        <v>0</v>
+      </c>
+      <c r="AA51">
+        <v>0</v>
+      </c>
+      <c r="AB51">
+        <v>0</v>
+      </c>
+      <c r="AC51">
+        <v>0</v>
+      </c>
+      <c r="AD51">
+        <v>0</v>
+      </c>
+      <c r="AE51">
+        <v>0</v>
+      </c>
+      <c r="AF51">
+        <v>0</v>
+      </c>
+      <c r="AG51">
+        <v>0</v>
+      </c>
+      <c r="AH51" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI51" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ51">
+        <v>0</v>
+      </c>
+      <c r="AK51">
+        <v>0</v>
+      </c>
+      <c r="AL51">
+        <v>0</v>
+      </c>
+      <c r="AM51">
+        <v>-1</v>
+      </c>
+      <c r="AN51">
+        <v>-1</v>
+      </c>
+      <c r="AO51">
+        <v>-1</v>
+      </c>
+      <c r="AP51">
+        <v>-1</v>
+      </c>
+      <c r="AQ51">
+        <v>0</v>
+      </c>
+      <c r="AR51">
+        <v>0</v>
+      </c>
+      <c r="AS51">
+        <v>0</v>
+      </c>
+      <c r="AT51">
+        <v>0</v>
+      </c>
+      <c r="AU51" t="inlineStr">
+        <is>
+          <t>2026-09-16 21:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Algeria Ligue 1</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>JS Saoura</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Oued Akbou</t>
+        </is>
+      </c>
+      <c r="G52">
+        <v>0</v>
+      </c>
+      <c r="H52">
+        <v>0</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+      <c r="J52">
+        <v>0</v>
+      </c>
+      <c r="K52">
+        <v>0</v>
+      </c>
+      <c r="L52">
+        <v>0</v>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N52">
+        <v>0</v>
+      </c>
+      <c r="O52">
+        <v>0</v>
+      </c>
+      <c r="P52">
+        <v>0</v>
+      </c>
+      <c r="Q52">
+        <v>0</v>
+      </c>
+      <c r="R52">
+        <v>0</v>
+      </c>
+      <c r="S52">
+        <v>0</v>
+      </c>
+      <c r="T52">
+        <v>0</v>
+      </c>
+      <c r="U52">
+        <v>0</v>
+      </c>
+      <c r="V52">
+        <v>0</v>
+      </c>
+      <c r="W52">
+        <v>0</v>
+      </c>
+      <c r="X52">
+        <v>0</v>
+      </c>
+      <c r="Y52">
+        <v>0</v>
+      </c>
+      <c r="Z52">
+        <v>0</v>
+      </c>
+      <c r="AA52">
+        <v>0</v>
+      </c>
+      <c r="AB52">
+        <v>0</v>
+      </c>
+      <c r="AC52">
+        <v>0</v>
+      </c>
+      <c r="AD52">
+        <v>0</v>
+      </c>
+      <c r="AE52">
+        <v>0</v>
+      </c>
+      <c r="AF52">
+        <v>0</v>
+      </c>
+      <c r="AG52">
+        <v>0</v>
+      </c>
+      <c r="AH52" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI52" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ52">
+        <v>0</v>
+      </c>
+      <c r="AK52">
+        <v>0</v>
+      </c>
+      <c r="AL52">
+        <v>0</v>
+      </c>
+      <c r="AM52">
+        <v>-1</v>
+      </c>
+      <c r="AN52">
+        <v>-1</v>
+      </c>
+      <c r="AO52">
+        <v>-1</v>
+      </c>
+      <c r="AP52">
+        <v>-1</v>
+      </c>
+      <c r="AQ52">
+        <v>0</v>
+      </c>
+      <c r="AR52">
+        <v>0</v>
+      </c>
+      <c r="AS52">
+        <v>0</v>
+      </c>
+      <c r="AT52">
+        <v>0</v>
+      </c>
+      <c r="AU52" t="inlineStr">
+        <is>
+          <t>2026-09-16 21:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>USA USL Championship</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Birmingham Legion</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>New Mexico United</t>
+        </is>
+      </c>
+      <c r="G53">
+        <v>0</v>
+      </c>
+      <c r="H53">
+        <v>0</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+      <c r="J53">
+        <v>0</v>
+      </c>
+      <c r="K53">
+        <v>0</v>
+      </c>
+      <c r="L53">
+        <v>0</v>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>suspended</t>
+        </is>
+      </c>
+      <c r="N53">
+        <v>2.1</v>
+      </c>
+      <c r="O53">
+        <v>3.4</v>
+      </c>
+      <c r="P53">
+        <v>2.85</v>
+      </c>
+      <c r="Q53">
+        <v>2.63</v>
+      </c>
+      <c r="R53">
+        <v>2.25</v>
+      </c>
+      <c r="S53">
+        <v>1.3</v>
+      </c>
+      <c r="T53">
+        <v>3.08</v>
+      </c>
+      <c r="U53">
+        <v>2.38</v>
+      </c>
+      <c r="V53">
+        <v>1.51</v>
+      </c>
+      <c r="W53">
+        <v>1.09</v>
+      </c>
+      <c r="X53">
+        <v>1</v>
+      </c>
+      <c r="Y53">
+        <v>1.22</v>
+      </c>
+      <c r="Z53">
+        <v>4.24</v>
+      </c>
+      <c r="AA53">
+        <v>1.68</v>
+      </c>
+      <c r="AB53">
+        <v>2.06</v>
+      </c>
+      <c r="AC53">
+        <v>2.75</v>
+      </c>
+      <c r="AD53">
+        <v>1.39</v>
+      </c>
+      <c r="AE53">
+        <v>1.17</v>
+      </c>
+      <c r="AF53">
+        <v>1.55</v>
+      </c>
+      <c r="AG53">
+        <v>2.3</v>
+      </c>
+      <c r="AH53" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI53" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ53">
+        <v>1.23</v>
+      </c>
+      <c r="AK53">
+        <v>1.54</v>
+      </c>
+      <c r="AL53">
+        <v>0</v>
+      </c>
+      <c r="AM53">
+        <v>-1</v>
+      </c>
+      <c r="AN53">
+        <v>-1</v>
+      </c>
+      <c r="AO53">
+        <v>-1</v>
+      </c>
+      <c r="AP53">
+        <v>-1</v>
+      </c>
+      <c r="AQ53">
+        <v>0</v>
+      </c>
+      <c r="AR53">
+        <v>0</v>
+      </c>
+      <c r="AS53">
+        <v>0</v>
+      </c>
+      <c r="AT53">
+        <v>0</v>
+      </c>
+      <c r="AU53" t="inlineStr">
+        <is>
+          <t>2026-09-16 21:30:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Bolivia LFPB</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Blooming</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Universitario de Vinto</t>
+        </is>
+      </c>
+      <c r="G54">
+        <v>0</v>
+      </c>
+      <c r="H54">
+        <v>0</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="J54">
+        <v>0</v>
+      </c>
+      <c r="K54">
+        <v>0</v>
+      </c>
+      <c r="L54">
+        <v>0</v>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N54">
+        <v>0</v>
+      </c>
+      <c r="O54">
+        <v>0</v>
+      </c>
+      <c r="P54">
+        <v>0</v>
+      </c>
+      <c r="Q54">
+        <v>0</v>
+      </c>
+      <c r="R54">
+        <v>0</v>
+      </c>
+      <c r="S54">
+        <v>0</v>
+      </c>
+      <c r="T54">
+        <v>0</v>
+      </c>
+      <c r="U54">
+        <v>0</v>
+      </c>
+      <c r="V54">
+        <v>0</v>
+      </c>
+      <c r="W54">
+        <v>0</v>
+      </c>
+      <c r="X54">
+        <v>0</v>
+      </c>
+      <c r="Y54">
+        <v>0</v>
+      </c>
+      <c r="Z54">
+        <v>0</v>
+      </c>
+      <c r="AA54">
+        <v>0</v>
+      </c>
+      <c r="AB54">
+        <v>0</v>
+      </c>
+      <c r="AC54">
+        <v>0</v>
+      </c>
+      <c r="AD54">
+        <v>0</v>
+      </c>
+      <c r="AE54">
+        <v>0</v>
+      </c>
+      <c r="AF54">
+        <v>0</v>
+      </c>
+      <c r="AG54">
+        <v>0</v>
+      </c>
+      <c r="AH54" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI54" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ54">
+        <v>0</v>
+      </c>
+      <c r="AK54">
+        <v>0</v>
+      </c>
+      <c r="AL54">
+        <v>0</v>
+      </c>
+      <c r="AM54">
+        <v>-1</v>
+      </c>
+      <c r="AN54">
+        <v>-1</v>
+      </c>
+      <c r="AO54">
+        <v>-1</v>
+      </c>
+      <c r="AP54">
+        <v>-1</v>
+      </c>
+      <c r="AQ54">
+        <v>0</v>
+      </c>
+      <c r="AR54">
+        <v>0</v>
+      </c>
+      <c r="AS54">
+        <v>0</v>
+      </c>
+      <c r="AT54">
+        <v>0</v>
+      </c>
+      <c r="AU54" t="inlineStr">
+        <is>
+          <t>2026-09-16 21:30:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>22:30</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>USA NWSL</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Denver Summit W</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Bay</t>
+        </is>
+      </c>
+      <c r="G55">
+        <v>0</v>
+      </c>
+      <c r="H55">
+        <v>0</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55">
+        <v>0</v>
+      </c>
+      <c r="K55">
+        <v>0</v>
+      </c>
+      <c r="L55">
+        <v>0</v>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N55">
+        <v>0</v>
+      </c>
+      <c r="O55">
+        <v>0</v>
+      </c>
+      <c r="P55">
+        <v>0</v>
+      </c>
+      <c r="Q55">
+        <v>0</v>
+      </c>
+      <c r="R55">
+        <v>0</v>
+      </c>
+      <c r="S55">
+        <v>0</v>
+      </c>
+      <c r="T55">
+        <v>0</v>
+      </c>
+      <c r="U55">
+        <v>0</v>
+      </c>
+      <c r="V55">
+        <v>0</v>
+      </c>
+      <c r="W55">
+        <v>0</v>
+      </c>
+      <c r="X55">
+        <v>0</v>
+      </c>
+      <c r="Y55">
+        <v>0</v>
+      </c>
+      <c r="Z55">
+        <v>0</v>
+      </c>
+      <c r="AA55">
+        <v>0</v>
+      </c>
+      <c r="AB55">
+        <v>0</v>
+      </c>
+      <c r="AC55">
+        <v>0</v>
+      </c>
+      <c r="AD55">
+        <v>0</v>
+      </c>
+      <c r="AE55">
+        <v>0</v>
+      </c>
+      <c r="AF55">
+        <v>0</v>
+      </c>
+      <c r="AG55">
+        <v>0</v>
+      </c>
+      <c r="AH55" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI55" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ55">
+        <v>0</v>
+      </c>
+      <c r="AK55">
+        <v>0</v>
+      </c>
+      <c r="AL55">
+        <v>0</v>
+      </c>
+      <c r="AM55">
+        <v>-1</v>
+      </c>
+      <c r="AN55">
+        <v>-1</v>
+      </c>
+      <c r="AO55">
+        <v>-1</v>
+      </c>
+      <c r="AP55">
+        <v>-1</v>
+      </c>
+      <c r="AQ55">
+        <v>0</v>
+      </c>
+      <c r="AR55">
+        <v>0</v>
+      </c>
+      <c r="AS55">
+        <v>0</v>
+      </c>
+      <c r="AT55">
+        <v>0</v>
+      </c>
+      <c r="AU55" t="inlineStr">
+        <is>
+          <t>2026-09-16 22:30:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>23:00</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>USA NWSL</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Angel City</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Seattle Reign</t>
+        </is>
+      </c>
+      <c r="G56">
+        <v>0</v>
+      </c>
+      <c r="H56">
+        <v>0</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+      <c r="J56">
+        <v>0</v>
+      </c>
+      <c r="K56">
+        <v>0</v>
+      </c>
+      <c r="L56">
+        <v>0</v>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N56">
+        <v>0</v>
+      </c>
+      <c r="O56">
+        <v>0</v>
+      </c>
+      <c r="P56">
+        <v>0</v>
+      </c>
+      <c r="Q56">
+        <v>0</v>
+      </c>
+      <c r="R56">
+        <v>0</v>
+      </c>
+      <c r="S56">
+        <v>0</v>
+      </c>
+      <c r="T56">
+        <v>0</v>
+      </c>
+      <c r="U56">
+        <v>0</v>
+      </c>
+      <c r="V56">
+        <v>0</v>
+      </c>
+      <c r="W56">
+        <v>0</v>
+      </c>
+      <c r="X56">
+        <v>0</v>
+      </c>
+      <c r="Y56">
+        <v>0</v>
+      </c>
+      <c r="Z56">
+        <v>0</v>
+      </c>
+      <c r="AA56">
+        <v>0</v>
+      </c>
+      <c r="AB56">
+        <v>0</v>
+      </c>
+      <c r="AC56">
+        <v>0</v>
+      </c>
+      <c r="AD56">
+        <v>0</v>
+      </c>
+      <c r="AE56">
+        <v>0</v>
+      </c>
+      <c r="AF56">
+        <v>0</v>
+      </c>
+      <c r="AG56">
+        <v>0</v>
+      </c>
+      <c r="AH56" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI56" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ56">
+        <v>0</v>
+      </c>
+      <c r="AK56">
+        <v>0</v>
+      </c>
+      <c r="AL56">
+        <v>0</v>
+      </c>
+      <c r="AM56">
+        <v>-1</v>
+      </c>
+      <c r="AN56">
+        <v>-1</v>
+      </c>
+      <c r="AO56">
+        <v>-1</v>
+      </c>
+      <c r="AP56">
+        <v>-1</v>
+      </c>
+      <c r="AQ56">
+        <v>0</v>
+      </c>
+      <c r="AR56">
+        <v>0</v>
+      </c>
+      <c r="AS56">
+        <v>0</v>
+      </c>
+      <c r="AT56">
+        <v>0</v>
+      </c>
+      <c r="AU56" t="inlineStr">
+        <is>
+          <t>2026-09-16 23:00:00</t>
         </is>
       </c>
     </row>

--- a/jogos_2026-09-16.xlsx
+++ b/jogos_2026-09-16.xlsx
@@ -2396,12 +2396,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ostia Mare Lidocalcio</t>
+          <t>Grosseto</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="G13">
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Sambenedettese</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="G14">
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Sambenedettese</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="G15">
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Grosseto</t>
+          <t>Ostia Mare Lidocalcio</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G16">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="G17">
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vado</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="G33">
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>Vado</t>
         </is>
       </c>
       <c r="G35">
@@ -7938,12 +7938,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G47">
@@ -8101,12 +8101,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>US Biskra</t>
         </is>
       </c>
       <c r="G48">
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>US Biskra</t>
+          <t>JS El Biar</t>
         </is>
       </c>
       <c r="G49">
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>JS El Biar</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G50">
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G51">
@@ -8753,12 +8753,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G52">

--- a/jogos_2026-09-16.xlsx
+++ b/jogos_2026-09-16.xlsx
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Sambenedettese</t>
+          <t>Ostia Mare Lidocalcio</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G15">
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Ostia Mare Lidocalcio</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="G16">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Sambenedettese</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="G17">

--- a/jogos_2026-09-16.xlsx
+++ b/jogos_2026-09-16.xlsx
@@ -7640,7 +7640,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N45">
@@ -7803,7 +7803,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N46">
@@ -7938,12 +7938,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>JS El Biar</t>
         </is>
       </c>
       <c r="G47">
@@ -7966,7 +7966,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N47">
@@ -8101,12 +8101,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>US Biskra</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G48">
@@ -8129,7 +8129,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N48">
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>JS El Biar</t>
+          <t>US Biskra</t>
         </is>
       </c>
       <c r="G49">
@@ -8292,7 +8292,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N49">
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G50">
@@ -8455,7 +8455,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N50">
@@ -8781,7 +8781,7 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N52">

--- a/jogos_2026-09-16.xlsx
+++ b/jogos_2026-09-16.xlsx
@@ -2233,12 +2233,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Grosseto</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="G12">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Grosseto</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="G13">
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Ostia Mare Lidocalcio</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G14">
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Ostia Mare Lidocalcio</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="G15">
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Sambenedettese</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="G16">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Sambenedettese</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="G17">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Hansa Rostock</t>
+          <t>Preußen Münster</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Saarbrucken</t>
         </is>
       </c>
       <c r="G22">
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Preußen Münster</t>
+          <t>Hansa Rostock</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Saarbrucken</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="G23">

--- a/jogos_2026-09-16.xlsx
+++ b/jogos_2026-09-16.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU56"/>
+  <dimension ref="A1:AU63"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1077,12 +1077,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1092,12 +1092,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="G5">
@@ -1228,7 +1228,7 @@
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>2026-09-16 12:00:00</t>
+          <t>2026-09-16 11:00:00</t>
         </is>
       </c>
     </row>
@@ -1240,12 +1240,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Spartak Moskva</t>
+          <t>Naftagas</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="G6">
@@ -1391,7 +1391,7 @@
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>2026-09-16 12:30:00</t>
+          <t>2026-09-16 11:00:00</t>
         </is>
       </c>
     </row>
@@ -1403,12 +1403,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Rodina Moskva</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rubin Kazan</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="G7">
@@ -1554,7 +1554,7 @@
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>2026-09-16 12:30:00</t>
+          <t>2026-09-16 12:00:00</t>
         </is>
       </c>
     </row>
@@ -1566,27 +1566,27 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Spartak Moskva</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="G8">
@@ -1613,13 +1613,13 @@
         </is>
       </c>
       <c r="N8">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="O8">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="P8">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q8">
         <v>0</v>
@@ -1717,7 +1717,7 @@
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>2026-09-16 12:45:00</t>
+          <t>2026-09-16 12:30:00</t>
         </is>
       </c>
     </row>
@@ -1729,27 +1729,27 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Rodina Moskva</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Rubin Kazan</t>
         </is>
       </c>
       <c r="G9">
@@ -1880,7 +1880,7 @@
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>2026-09-16 13:00:00</t>
+          <t>2026-09-16 12:30:00</t>
         </is>
       </c>
     </row>
@@ -1892,12 +1892,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="G10">
@@ -1935,68 +1935,68 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N10">
-        <v>1.23</v>
+        <v>2.88</v>
       </c>
       <c r="O10">
-        <v>5.5</v>
+        <v>3.35</v>
       </c>
       <c r="P10">
-        <v>8.5</v>
+        <v>2.25</v>
       </c>
       <c r="Q10">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="R10">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="S10">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="T10">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="U10">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="V10">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="W10">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="X10">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y10">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Z10">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="AA10">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AB10">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AC10">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD10">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AE10">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AF10">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AG10">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AK10">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2043,7 +2043,7 @@
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>2026-09-16 13:00:00</t>
+          <t>2026-09-16 12:45:00</t>
         </is>
       </c>
     </row>
@@ -2060,7 +2060,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2070,12 +2070,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>CSKA Sofia</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="G11">
@@ -2102,80 +2102,80 @@
         </is>
       </c>
       <c r="N11">
-        <v>4.6</v>
+        <v>5.25</v>
       </c>
       <c r="O11">
-        <v>3.9</v>
+        <v>3.45</v>
       </c>
       <c r="P11">
-        <v>1.55</v>
+        <v>1.94</v>
       </c>
       <c r="Q11">
-        <v>5.07</v>
+        <v>5.8</v>
       </c>
       <c r="R11">
-        <v>2.43</v>
+        <v>2.05</v>
       </c>
       <c r="S11">
-        <v>1.3</v>
+        <v>1.46</v>
       </c>
       <c r="T11">
-        <v>3.1</v>
+        <v>2.44</v>
       </c>
       <c r="U11">
-        <v>2.63</v>
+        <v>3.12</v>
       </c>
       <c r="V11">
-        <v>1.47</v>
+        <v>1.29</v>
       </c>
       <c r="W11">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X11">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y11">
-        <v>1.24</v>
+        <v>1.39</v>
       </c>
       <c r="Z11">
-        <v>3.72</v>
+        <v>2.83</v>
       </c>
       <c r="AA11">
-        <v>1.75</v>
+        <v>2.2</v>
       </c>
       <c r="AB11">
+        <v>1.6</v>
+      </c>
+      <c r="AC11">
+        <v>4.2</v>
+      </c>
+      <c r="AD11">
+        <v>1.2</v>
+      </c>
+      <c r="AE11">
+        <v>1.03</v>
+      </c>
+      <c r="AF11">
         <v>2.05</v>
       </c>
-      <c r="AC11">
-        <v>2.75</v>
-      </c>
-      <c r="AD11">
-        <v>1.4</v>
-      </c>
-      <c r="AE11">
+      <c r="AG11">
+        <v>1.7</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ11">
+        <v>1.22</v>
+      </c>
+      <c r="AK11">
         <v>1.15</v>
-      </c>
-      <c r="AF11">
-        <v>1.74</v>
-      </c>
-      <c r="AG11">
-        <v>1.95</v>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ11">
-        <v>1.25</v>
-      </c>
-      <c r="AK11">
-        <v>1.17</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2218,27 +2218,27 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Grosseto</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="G12">
@@ -2369,7 +2369,7 @@
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>2026-09-16 13:30:00</t>
+          <t>2026-09-16 13:00:00</t>
         </is>
       </c>
     </row>
@@ -2381,27 +2381,27 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="G13">
@@ -2424,68 +2424,68 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N13">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="O13">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="P13">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="Q13">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="R13">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="S13">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T13">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U13">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="V13">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="W13">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X13">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y13">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Z13">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AA13">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AB13">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AC13">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD13">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AE13">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AF13">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AG13">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AK13">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2532,7 +2532,7 @@
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>2026-09-16 13:30:00</t>
+          <t>2026-09-16 13:00:00</t>
         </is>
       </c>
     </row>
@@ -2544,12 +2544,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Ostia Mare Lidocalcio</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>CSKA Sofia</t>
         </is>
       </c>
       <c r="G14">
@@ -2587,68 +2587,68 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N14">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="O14">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="P14">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Q14">
-        <v>0</v>
+        <v>5.07</v>
       </c>
       <c r="R14">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="S14">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T14">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U14">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="V14">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="W14">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X14">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y14">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z14">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="AA14">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB14">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC14">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AD14">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE14">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF14">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AG14">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK14">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2695,7 +2695,7 @@
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>2026-09-16 13:30:00</t>
+          <t>2026-09-16 13:00:00</t>
         </is>
       </c>
     </row>
@@ -2707,12 +2707,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G15">
@@ -2858,7 +2858,7 @@
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>2026-09-16 13:30:00</t>
+          <t>2026-09-16 13:00:00</t>
         </is>
       </c>
     </row>
@@ -2870,12 +2870,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Sambenedettese</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Teleoptik</t>
         </is>
       </c>
       <c r="G16">
@@ -3021,7 +3021,7 @@
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>2026-09-16 13:30:00</t>
+          <t>2026-09-16 13:00:00</t>
         </is>
       </c>
     </row>
@@ -3033,12 +3033,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="G17">
@@ -3184,7 +3184,7 @@
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>2026-09-16 13:30:00</t>
+          <t>2026-09-16 13:00:00</t>
         </is>
       </c>
     </row>
@@ -3196,12 +3196,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Grosseto</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="G18">
@@ -3347,7 +3347,7 @@
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>2026-09-16 14:00:00</t>
+          <t>2026-09-16 13:30:00</t>
         </is>
       </c>
     </row>
@@ -3359,12 +3359,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="G19">
@@ -3510,7 +3510,7 @@
       </c>
       <c r="AU19" t="inlineStr">
         <is>
-          <t>2026-09-16 14:00:00</t>
+          <t>2026-09-16 13:30:00</t>
         </is>
       </c>
     </row>
@@ -3522,12 +3522,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>Ostia Mare Lidocalcio</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G20">
@@ -3565,68 +3565,68 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N20">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="O20">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="P20">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="Q20">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="R20">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="S20">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="T20">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="U20">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="V20">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="W20">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="X20">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y20">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="Z20">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="AA20">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AB20">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="AC20">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="AD20">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AE20">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AF20">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AG20">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AK20">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3673,7 +3673,7 @@
       </c>
       <c r="AU20" t="inlineStr">
         <is>
-          <t>2026-09-16 14:00:00</t>
+          <t>2026-09-16 13:30:00</t>
         </is>
       </c>
     </row>
@@ -3685,12 +3685,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Servette</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="G21">
@@ -3728,68 +3728,68 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N21">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="O21">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="P21">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q21">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="R21">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="S21">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="T21">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="U21">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="V21">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="W21">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="X21">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y21">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="Z21">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AA21">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AB21">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="AC21">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD21">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AE21">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AF21">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AG21">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AK21">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="AU21" t="inlineStr">
         <is>
-          <t>2026-09-16 14:00:00</t>
+          <t>2026-09-16 13:30:00</t>
         </is>
       </c>
     </row>
@@ -3848,12 +3848,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Preußen Münster</t>
+          <t>Sambenedettese</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Saarbrucken</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="G22">
@@ -3999,7 +3999,7 @@
       </c>
       <c r="AU22" t="inlineStr">
         <is>
-          <t>2026-09-16 14:00:00</t>
+          <t>2026-09-16 13:30:00</t>
         </is>
       </c>
     </row>
@@ -4011,12 +4011,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Hansa Rostock</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="G23">
@@ -4162,7 +4162,7 @@
       </c>
       <c r="AU23" t="inlineStr">
         <is>
-          <t>2026-09-16 14:00:00</t>
+          <t>2026-09-16 13:30:00</t>
         </is>
       </c>
     </row>
@@ -4179,7 +4179,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Fortuna Köln</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Wehen Wiesbaden</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="G24">
@@ -4342,7 +4342,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Ingolstadt</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Hoffenheim II</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="G25">
@@ -4505,7 +4505,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Waldhof Mannheim</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rot-Weiss Essen</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="G26">
@@ -4543,68 +4543,68 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N26">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="O26">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="P26">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="Q26">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="R26">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S26">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="T26">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="U26">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="V26">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="W26">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X26">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y26">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z26">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AA26">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AB26">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AC26">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AD26">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AE26">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AF26">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG26">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK26">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4668,7 +4668,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>Servette</t>
         </is>
       </c>
       <c r="G27">
@@ -4706,68 +4706,68 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N27">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="O27">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P27">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q27">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="R27">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="S27">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="T27">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U27">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="V27">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="W27">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X27">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y27">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z27">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA27">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB27">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="AC27">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD27">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AE27">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF27">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AG27">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AK27">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4831,7 +4831,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>Preußen Münster</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Saarbrucken</t>
         </is>
       </c>
       <c r="G28">
@@ -4994,22 +4994,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>Hansa Rostock</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="G29">
@@ -5152,12 +5152,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Baltika</t>
+          <t>Fortuna Köln</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Zenit</t>
+          <t>Wehen Wiesbaden</t>
         </is>
       </c>
       <c r="G30">
@@ -5303,7 +5303,7 @@
       </c>
       <c r="AU30" t="inlineStr">
         <is>
-          <t>2026-09-16 14:45:00</t>
+          <t>2026-09-16 14:00:00</t>
         </is>
       </c>
     </row>
@@ -5315,12 +5315,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Lokomotiv Moskva</t>
+          <t>Ingolstadt</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Krylya Sovetov</t>
+          <t>Hoffenheim II</t>
         </is>
       </c>
       <c r="G31">
@@ -5466,7 +5466,7 @@
       </c>
       <c r="AU31" t="inlineStr">
         <is>
-          <t>2026-09-16 14:45:00</t>
+          <t>2026-09-16 14:00:00</t>
         </is>
       </c>
     </row>
@@ -5478,27 +5478,27 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Waldhof Mannheim</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Rot-Weiss Essen</t>
         </is>
       </c>
       <c r="G32">
@@ -5521,68 +5521,68 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N32">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="O32">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="P32">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="Q32">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="R32">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="S32">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="T32">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="U32">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="V32">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="W32">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X32">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="Y32">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="Z32">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AA32">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AB32">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AC32">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="AD32">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AE32">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AF32">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AG32">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AK32">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5629,7 +5629,7 @@
       </c>
       <c r="AU32" t="inlineStr">
         <is>
-          <t>2026-09-16 15:00:00</t>
+          <t>2026-09-16 14:00:00</t>
         </is>
       </c>
     </row>
@@ -5641,12 +5641,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="G33">
@@ -5792,7 +5792,7 @@
       </c>
       <c r="AU33" t="inlineStr">
         <is>
-          <t>2026-09-16 16:00:00</t>
+          <t>2026-09-16 14:00:00</t>
         </is>
       </c>
     </row>
@@ -5804,12 +5804,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="G34">
@@ -5955,7 +5955,7 @@
       </c>
       <c r="AU34" t="inlineStr">
         <is>
-          <t>2026-09-16 16:00:00</t>
+          <t>2026-09-16 14:00:00</t>
         </is>
       </c>
     </row>
@@ -5967,27 +5967,27 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vado</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="G35">
@@ -6118,7 +6118,7 @@
       </c>
       <c r="AU35" t="inlineStr">
         <is>
-          <t>2026-09-16 16:00:00</t>
+          <t>2026-09-16 14:00:00</t>
         </is>
       </c>
     </row>
@@ -6130,12 +6130,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Pescara</t>
+          <t>Lokomotiv Moskva</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Gubbio</t>
+          <t>Krylya Sovetov</t>
         </is>
       </c>
       <c r="G36">
@@ -6281,7 +6281,7 @@
       </c>
       <c r="AU36" t="inlineStr">
         <is>
-          <t>2026-09-16 16:00:00</t>
+          <t>2026-09-16 14:45:00</t>
         </is>
       </c>
     </row>
@@ -6293,27 +6293,27 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Guabirá</t>
+          <t>Baltika</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>Zenit</t>
         </is>
       </c>
       <c r="G37">
@@ -6444,7 +6444,7 @@
       </c>
       <c r="AU37" t="inlineStr">
         <is>
-          <t>2026-09-16 16:00:00</t>
+          <t>2026-09-16 14:45:00</t>
         </is>
       </c>
     </row>
@@ -6456,27 +6456,27 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G38">
@@ -6499,68 +6499,68 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N38">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="O38">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="P38">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="Q38">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="R38">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="S38">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="T38">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="U38">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V38">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="W38">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X38">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Y38">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Z38">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AA38">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AB38">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AC38">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AD38">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AE38">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF38">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AG38">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK38">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6607,7 +6607,7 @@
       </c>
       <c r="AU38" t="inlineStr">
         <is>
-          <t>2026-09-16 16:30:00</t>
+          <t>2026-09-16 15:00:00</t>
         </is>
       </c>
     </row>
@@ -6619,12 +6619,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Levante UD</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Metalac GM</t>
         </is>
       </c>
       <c r="G39">
@@ -6770,7 +6770,7 @@
       </c>
       <c r="AU39" t="inlineStr">
         <is>
-          <t>2026-09-16 16:30:00</t>
+          <t>2026-09-16 15:00:00</t>
         </is>
       </c>
     </row>
@@ -6782,27 +6782,27 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Huachipato</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="G40">
@@ -6829,64 +6829,64 @@
         </is>
       </c>
       <c r="N40">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="O40">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="P40">
-        <v>6.54</v>
+        <v>0</v>
       </c>
       <c r="Q40">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="R40">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="S40">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="T40">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="U40">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="V40">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="W40">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X40">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y40">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Z40">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AA40">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB40">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="AC40">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AD40">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AE40">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AF40">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG40">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AK40">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -6933,7 +6933,7 @@
       </c>
       <c r="AU40" t="inlineStr">
         <is>
-          <t>2026-09-16 18:00:00</t>
+          <t>2026-09-16 16:00:00</t>
         </is>
       </c>
     </row>
@@ -6945,27 +6945,27 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Sporting JAX</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="G41">
@@ -7096,7 +7096,7 @@
       </c>
       <c r="AU41" t="inlineStr">
         <is>
-          <t>2026-09-16 19:00:00</t>
+          <t>2026-09-16 16:00:00</t>
         </is>
       </c>
     </row>
@@ -7108,27 +7108,27 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Vado</t>
         </is>
       </c>
       <c r="G42">
@@ -7151,68 +7151,68 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N42">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="O42">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="P42">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Q42">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="R42">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="S42">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="T42">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="U42">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="V42">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="W42">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X42">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y42">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z42">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AA42">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB42">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC42">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AD42">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AE42">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AF42">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG42">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AK42">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7259,7 +7259,7 @@
       </c>
       <c r="AU42" t="inlineStr">
         <is>
-          <t>2026-09-16 19:30:00</t>
+          <t>2026-09-16 16:00:00</t>
         </is>
       </c>
     </row>
@@ -7271,27 +7271,27 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Pescara</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Club Always Ready</t>
+          <t>Gubbio</t>
         </is>
       </c>
       <c r="G43">
@@ -7422,7 +7422,7 @@
       </c>
       <c r="AU43" t="inlineStr">
         <is>
-          <t>2026-09-16 19:30:00</t>
+          <t>2026-09-16 16:00:00</t>
         </is>
       </c>
     </row>
@@ -7434,12 +7434,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>Guabirá</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="G44">
@@ -7585,7 +7585,7 @@
       </c>
       <c r="AU44" t="inlineStr">
         <is>
-          <t>2026-09-16 21:00:00</t>
+          <t>2026-09-16 16:00:00</t>
         </is>
       </c>
     </row>
@@ -7597,12 +7597,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -7612,12 +7612,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="G45">
@@ -7640,7 +7640,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N45">
@@ -7748,7 +7748,7 @@
       </c>
       <c r="AU45" t="inlineStr">
         <is>
-          <t>2026-09-16 21:00:00</t>
+          <t>2026-09-16 16:30:00</t>
         </is>
       </c>
     </row>
@@ -7760,12 +7760,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -7775,12 +7775,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Levante UD</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Temouchent</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="G46">
@@ -7803,7 +7803,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N46">
@@ -7911,7 +7911,7 @@
       </c>
       <c r="AU46" t="inlineStr">
         <is>
-          <t>2026-09-16 21:00:00</t>
+          <t>2026-09-16 16:30:00</t>
         </is>
       </c>
     </row>
@@ -7923,27 +7923,27 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Coquimbo Unido</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>JS El Biar</t>
+          <t>Huachipato</t>
         </is>
       </c>
       <c r="G47">
@@ -7966,68 +7966,68 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N47">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="O47">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="P47">
-        <v>0</v>
+        <v>6.54</v>
       </c>
       <c r="Q47">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="R47">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S47">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T47">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U47">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="V47">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W47">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X47">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y47">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z47">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AA47">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB47">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AC47">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AD47">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE47">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF47">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG47">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -8040,10 +8040,10 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AK47">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8074,7 +8074,7 @@
       </c>
       <c r="AU47" t="inlineStr">
         <is>
-          <t>2026-09-16 21:00:00</t>
+          <t>2026-09-16 18:00:00</t>
         </is>
       </c>
     </row>
@@ -8086,27 +8086,27 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Sporting JAX</t>
         </is>
       </c>
       <c r="G48">
@@ -8129,7 +8129,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N48">
@@ -8237,7 +8237,7 @@
       </c>
       <c r="AU48" t="inlineStr">
         <is>
-          <t>2026-09-16 21:00:00</t>
+          <t>2026-09-16 19:00:00</t>
         </is>
       </c>
     </row>
@@ -8249,27 +8249,27 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>US Biskra</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="G49">
@@ -8296,64 +8296,64 @@
         </is>
       </c>
       <c r="N49">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="O49">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P49">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q49">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="R49">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="S49">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T49">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="U49">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="V49">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W49">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X49">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y49">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z49">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AA49">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB49">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC49">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AD49">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE49">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF49">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG49">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8366,10 +8366,10 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK49">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -8400,7 +8400,7 @@
       </c>
       <c r="AU49" t="inlineStr">
         <is>
-          <t>2026-09-16 21:00:00</t>
+          <t>2026-09-16 19:30:00</t>
         </is>
       </c>
     </row>
@@ -8412,27 +8412,27 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Club Always Ready</t>
         </is>
       </c>
       <c r="G50">
@@ -8455,7 +8455,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N50">
@@ -8563,7 +8563,7 @@
       </c>
       <c r="AU50" t="inlineStr">
         <is>
-          <t>2026-09-16 21:00:00</t>
+          <t>2026-09-16 19:30:00</t>
         </is>
       </c>
     </row>
@@ -8580,22 +8580,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="G51">
@@ -8753,12 +8753,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G52">
@@ -8901,27 +8901,27 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>New Mexico United</t>
+          <t>Temouchent</t>
         </is>
       </c>
       <c r="G53">
@@ -8948,64 +8948,64 @@
         </is>
       </c>
       <c r="N53">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="O53">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P53">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="Q53">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="R53">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="S53">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="T53">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="U53">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="V53">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="W53">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X53">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y53">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="Z53">
-        <v>4.24</v>
+        <v>0</v>
       </c>
       <c r="AA53">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AB53">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AC53">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AD53">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AE53">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AF53">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AG53">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -9018,10 +9018,10 @@
         </is>
       </c>
       <c r="AJ53">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AK53">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AL53">
         <v>0</v>
@@ -9052,7 +9052,7 @@
       </c>
       <c r="AU53" t="inlineStr">
         <is>
-          <t>2026-09-16 21:30:00</t>
+          <t>2026-09-16 21:00:00</t>
         </is>
       </c>
     </row>
@@ -9064,27 +9064,27 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Blooming</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Universitario de Vinto</t>
+          <t>JS El Biar</t>
         </is>
       </c>
       <c r="G54">
@@ -9107,7 +9107,7 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N54">
@@ -9215,7 +9215,7 @@
       </c>
       <c r="AU54" t="inlineStr">
         <is>
-          <t>2026-09-16 21:30:00</t>
+          <t>2026-09-16 21:00:00</t>
         </is>
       </c>
     </row>
@@ -9227,27 +9227,27 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>22:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Denver Summit W</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Bay</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G55">
@@ -9270,7 +9270,7 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N55">
@@ -9378,7 +9378,7 @@
       </c>
       <c r="AU55" t="inlineStr">
         <is>
-          <t>2026-09-16 22:30:00</t>
+          <t>2026-09-16 21:00:00</t>
         </is>
       </c>
     </row>
@@ -9390,156 +9390,1297 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Algeria Ligue 1</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>CS Constantine</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>US Biskra</t>
+        </is>
+      </c>
+      <c r="G56">
+        <v>0</v>
+      </c>
+      <c r="H56">
+        <v>0</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+      <c r="J56">
+        <v>0</v>
+      </c>
+      <c r="K56">
+        <v>0</v>
+      </c>
+      <c r="L56">
+        <v>0</v>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>suspended</t>
+        </is>
+      </c>
+      <c r="N56">
+        <v>0</v>
+      </c>
+      <c r="O56">
+        <v>0</v>
+      </c>
+      <c r="P56">
+        <v>0</v>
+      </c>
+      <c r="Q56">
+        <v>0</v>
+      </c>
+      <c r="R56">
+        <v>0</v>
+      </c>
+      <c r="S56">
+        <v>0</v>
+      </c>
+      <c r="T56">
+        <v>0</v>
+      </c>
+      <c r="U56">
+        <v>0</v>
+      </c>
+      <c r="V56">
+        <v>0</v>
+      </c>
+      <c r="W56">
+        <v>0</v>
+      </c>
+      <c r="X56">
+        <v>0</v>
+      </c>
+      <c r="Y56">
+        <v>0</v>
+      </c>
+      <c r="Z56">
+        <v>0</v>
+      </c>
+      <c r="AA56">
+        <v>0</v>
+      </c>
+      <c r="AB56">
+        <v>0</v>
+      </c>
+      <c r="AC56">
+        <v>0</v>
+      </c>
+      <c r="AD56">
+        <v>0</v>
+      </c>
+      <c r="AE56">
+        <v>0</v>
+      </c>
+      <c r="AF56">
+        <v>0</v>
+      </c>
+      <c r="AG56">
+        <v>0</v>
+      </c>
+      <c r="AH56" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI56" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ56">
+        <v>0</v>
+      </c>
+      <c r="AK56">
+        <v>0</v>
+      </c>
+      <c r="AL56">
+        <v>0</v>
+      </c>
+      <c r="AM56">
+        <v>-1</v>
+      </c>
+      <c r="AN56">
+        <v>-1</v>
+      </c>
+      <c r="AO56">
+        <v>-1</v>
+      </c>
+      <c r="AP56">
+        <v>-1</v>
+      </c>
+      <c r="AQ56">
+        <v>0</v>
+      </c>
+      <c r="AR56">
+        <v>0</v>
+      </c>
+      <c r="AS56">
+        <v>0</v>
+      </c>
+      <c r="AT56">
+        <v>0</v>
+      </c>
+      <c r="AU56" t="inlineStr">
+        <is>
+          <t>2026-09-16 21:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Algeria Ligue 1</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>MC Oran</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>ES Sétif</t>
+        </is>
+      </c>
+      <c r="G57">
+        <v>0</v>
+      </c>
+      <c r="H57">
+        <v>0</v>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+      <c r="J57">
+        <v>0</v>
+      </c>
+      <c r="K57">
+        <v>0</v>
+      </c>
+      <c r="L57">
+        <v>0</v>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>suspended</t>
+        </is>
+      </c>
+      <c r="N57">
+        <v>0</v>
+      </c>
+      <c r="O57">
+        <v>0</v>
+      </c>
+      <c r="P57">
+        <v>0</v>
+      </c>
+      <c r="Q57">
+        <v>0</v>
+      </c>
+      <c r="R57">
+        <v>0</v>
+      </c>
+      <c r="S57">
+        <v>0</v>
+      </c>
+      <c r="T57">
+        <v>0</v>
+      </c>
+      <c r="U57">
+        <v>0</v>
+      </c>
+      <c r="V57">
+        <v>0</v>
+      </c>
+      <c r="W57">
+        <v>0</v>
+      </c>
+      <c r="X57">
+        <v>0</v>
+      </c>
+      <c r="Y57">
+        <v>0</v>
+      </c>
+      <c r="Z57">
+        <v>0</v>
+      </c>
+      <c r="AA57">
+        <v>0</v>
+      </c>
+      <c r="AB57">
+        <v>0</v>
+      </c>
+      <c r="AC57">
+        <v>0</v>
+      </c>
+      <c r="AD57">
+        <v>0</v>
+      </c>
+      <c r="AE57">
+        <v>0</v>
+      </c>
+      <c r="AF57">
+        <v>0</v>
+      </c>
+      <c r="AG57">
+        <v>0</v>
+      </c>
+      <c r="AH57" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI57" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ57">
+        <v>0</v>
+      </c>
+      <c r="AK57">
+        <v>0</v>
+      </c>
+      <c r="AL57">
+        <v>0</v>
+      </c>
+      <c r="AM57">
+        <v>-1</v>
+      </c>
+      <c r="AN57">
+        <v>-1</v>
+      </c>
+      <c r="AO57">
+        <v>-1</v>
+      </c>
+      <c r="AP57">
+        <v>-1</v>
+      </c>
+      <c r="AQ57">
+        <v>0</v>
+      </c>
+      <c r="AR57">
+        <v>0</v>
+      </c>
+      <c r="AS57">
+        <v>0</v>
+      </c>
+      <c r="AT57">
+        <v>0</v>
+      </c>
+      <c r="AU57" t="inlineStr">
+        <is>
+          <t>2026-09-16 21:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Algeria Ligue 1</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>JS Saoura</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Oued Akbou</t>
+        </is>
+      </c>
+      <c r="G58">
+        <v>0</v>
+      </c>
+      <c r="H58">
+        <v>0</v>
+      </c>
+      <c r="I58">
+        <v>0</v>
+      </c>
+      <c r="J58">
+        <v>0</v>
+      </c>
+      <c r="K58">
+        <v>0</v>
+      </c>
+      <c r="L58">
+        <v>0</v>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N58">
+        <v>0</v>
+      </c>
+      <c r="O58">
+        <v>0</v>
+      </c>
+      <c r="P58">
+        <v>0</v>
+      </c>
+      <c r="Q58">
+        <v>0</v>
+      </c>
+      <c r="R58">
+        <v>0</v>
+      </c>
+      <c r="S58">
+        <v>0</v>
+      </c>
+      <c r="T58">
+        <v>0</v>
+      </c>
+      <c r="U58">
+        <v>0</v>
+      </c>
+      <c r="V58">
+        <v>0</v>
+      </c>
+      <c r="W58">
+        <v>0</v>
+      </c>
+      <c r="X58">
+        <v>0</v>
+      </c>
+      <c r="Y58">
+        <v>0</v>
+      </c>
+      <c r="Z58">
+        <v>0</v>
+      </c>
+      <c r="AA58">
+        <v>0</v>
+      </c>
+      <c r="AB58">
+        <v>0</v>
+      </c>
+      <c r="AC58">
+        <v>0</v>
+      </c>
+      <c r="AD58">
+        <v>0</v>
+      </c>
+      <c r="AE58">
+        <v>0</v>
+      </c>
+      <c r="AF58">
+        <v>0</v>
+      </c>
+      <c r="AG58">
+        <v>0</v>
+      </c>
+      <c r="AH58" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI58" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ58">
+        <v>0</v>
+      </c>
+      <c r="AK58">
+        <v>0</v>
+      </c>
+      <c r="AL58">
+        <v>0</v>
+      </c>
+      <c r="AM58">
+        <v>-1</v>
+      </c>
+      <c r="AN58">
+        <v>-1</v>
+      </c>
+      <c r="AO58">
+        <v>-1</v>
+      </c>
+      <c r="AP58">
+        <v>-1</v>
+      </c>
+      <c r="AQ58">
+        <v>0</v>
+      </c>
+      <c r="AR58">
+        <v>0</v>
+      </c>
+      <c r="AS58">
+        <v>0</v>
+      </c>
+      <c r="AT58">
+        <v>0</v>
+      </c>
+      <c r="AU58" t="inlineStr">
+        <is>
+          <t>2026-09-16 21:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Algeria Ligue 1</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>MB Rouisset</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>USM Alger</t>
+        </is>
+      </c>
+      <c r="G59">
+        <v>0</v>
+      </c>
+      <c r="H59">
+        <v>0</v>
+      </c>
+      <c r="I59">
+        <v>0</v>
+      </c>
+      <c r="J59">
+        <v>0</v>
+      </c>
+      <c r="K59">
+        <v>0</v>
+      </c>
+      <c r="L59">
+        <v>0</v>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>suspended</t>
+        </is>
+      </c>
+      <c r="N59">
+        <v>0</v>
+      </c>
+      <c r="O59">
+        <v>0</v>
+      </c>
+      <c r="P59">
+        <v>0</v>
+      </c>
+      <c r="Q59">
+        <v>0</v>
+      </c>
+      <c r="R59">
+        <v>0</v>
+      </c>
+      <c r="S59">
+        <v>0</v>
+      </c>
+      <c r="T59">
+        <v>0</v>
+      </c>
+      <c r="U59">
+        <v>0</v>
+      </c>
+      <c r="V59">
+        <v>0</v>
+      </c>
+      <c r="W59">
+        <v>0</v>
+      </c>
+      <c r="X59">
+        <v>0</v>
+      </c>
+      <c r="Y59">
+        <v>0</v>
+      </c>
+      <c r="Z59">
+        <v>0</v>
+      </c>
+      <c r="AA59">
+        <v>0</v>
+      </c>
+      <c r="AB59">
+        <v>0</v>
+      </c>
+      <c r="AC59">
+        <v>0</v>
+      </c>
+      <c r="AD59">
+        <v>0</v>
+      </c>
+      <c r="AE59">
+        <v>0</v>
+      </c>
+      <c r="AF59">
+        <v>0</v>
+      </c>
+      <c r="AG59">
+        <v>0</v>
+      </c>
+      <c r="AH59" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI59" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ59">
+        <v>0</v>
+      </c>
+      <c r="AK59">
+        <v>0</v>
+      </c>
+      <c r="AL59">
+        <v>0</v>
+      </c>
+      <c r="AM59">
+        <v>-1</v>
+      </c>
+      <c r="AN59">
+        <v>-1</v>
+      </c>
+      <c r="AO59">
+        <v>-1</v>
+      </c>
+      <c r="AP59">
+        <v>-1</v>
+      </c>
+      <c r="AQ59">
+        <v>0</v>
+      </c>
+      <c r="AR59">
+        <v>0</v>
+      </c>
+      <c r="AS59">
+        <v>0</v>
+      </c>
+      <c r="AT59">
+        <v>0</v>
+      </c>
+      <c r="AU59" t="inlineStr">
+        <is>
+          <t>2026-09-16 21:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>USA USL Championship</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Birmingham Legion</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>New Mexico United</t>
+        </is>
+      </c>
+      <c r="G60">
+        <v>0</v>
+      </c>
+      <c r="H60">
+        <v>0</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+      <c r="J60">
+        <v>0</v>
+      </c>
+      <c r="K60">
+        <v>0</v>
+      </c>
+      <c r="L60">
+        <v>0</v>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>suspended</t>
+        </is>
+      </c>
+      <c r="N60">
+        <v>2.1</v>
+      </c>
+      <c r="O60">
+        <v>3.4</v>
+      </c>
+      <c r="P60">
+        <v>2.85</v>
+      </c>
+      <c r="Q60">
+        <v>2.63</v>
+      </c>
+      <c r="R60">
+        <v>2.25</v>
+      </c>
+      <c r="S60">
+        <v>1.3</v>
+      </c>
+      <c r="T60">
+        <v>3.08</v>
+      </c>
+      <c r="U60">
+        <v>2.38</v>
+      </c>
+      <c r="V60">
+        <v>1.51</v>
+      </c>
+      <c r="W60">
+        <v>1.09</v>
+      </c>
+      <c r="X60">
+        <v>1</v>
+      </c>
+      <c r="Y60">
+        <v>1.22</v>
+      </c>
+      <c r="Z60">
+        <v>4.24</v>
+      </c>
+      <c r="AA60">
+        <v>1.68</v>
+      </c>
+      <c r="AB60">
+        <v>2.06</v>
+      </c>
+      <c r="AC60">
+        <v>2.75</v>
+      </c>
+      <c r="AD60">
+        <v>1.39</v>
+      </c>
+      <c r="AE60">
+        <v>1.17</v>
+      </c>
+      <c r="AF60">
+        <v>1.55</v>
+      </c>
+      <c r="AG60">
+        <v>2.3</v>
+      </c>
+      <c r="AH60" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI60" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ60">
+        <v>1.23</v>
+      </c>
+      <c r="AK60">
+        <v>1.54</v>
+      </c>
+      <c r="AL60">
+        <v>0</v>
+      </c>
+      <c r="AM60">
+        <v>-1</v>
+      </c>
+      <c r="AN60">
+        <v>-1</v>
+      </c>
+      <c r="AO60">
+        <v>-1</v>
+      </c>
+      <c r="AP60">
+        <v>-1</v>
+      </c>
+      <c r="AQ60">
+        <v>0</v>
+      </c>
+      <c r="AR60">
+        <v>0</v>
+      </c>
+      <c r="AS60">
+        <v>0</v>
+      </c>
+      <c r="AT60">
+        <v>0</v>
+      </c>
+      <c r="AU60" t="inlineStr">
+        <is>
+          <t>2026-09-16 21:30:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Bolivia LFPB</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Blooming</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Universitario de Vinto</t>
+        </is>
+      </c>
+      <c r="G61">
+        <v>0</v>
+      </c>
+      <c r="H61">
+        <v>0</v>
+      </c>
+      <c r="I61">
+        <v>0</v>
+      </c>
+      <c r="J61">
+        <v>0</v>
+      </c>
+      <c r="K61">
+        <v>0</v>
+      </c>
+      <c r="L61">
+        <v>0</v>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N61">
+        <v>0</v>
+      </c>
+      <c r="O61">
+        <v>0</v>
+      </c>
+      <c r="P61">
+        <v>0</v>
+      </c>
+      <c r="Q61">
+        <v>0</v>
+      </c>
+      <c r="R61">
+        <v>0</v>
+      </c>
+      <c r="S61">
+        <v>0</v>
+      </c>
+      <c r="T61">
+        <v>0</v>
+      </c>
+      <c r="U61">
+        <v>0</v>
+      </c>
+      <c r="V61">
+        <v>0</v>
+      </c>
+      <c r="W61">
+        <v>0</v>
+      </c>
+      <c r="X61">
+        <v>0</v>
+      </c>
+      <c r="Y61">
+        <v>0</v>
+      </c>
+      <c r="Z61">
+        <v>0</v>
+      </c>
+      <c r="AA61">
+        <v>0</v>
+      </c>
+      <c r="AB61">
+        <v>0</v>
+      </c>
+      <c r="AC61">
+        <v>0</v>
+      </c>
+      <c r="AD61">
+        <v>0</v>
+      </c>
+      <c r="AE61">
+        <v>0</v>
+      </c>
+      <c r="AF61">
+        <v>0</v>
+      </c>
+      <c r="AG61">
+        <v>0</v>
+      </c>
+      <c r="AH61" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI61" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ61">
+        <v>0</v>
+      </c>
+      <c r="AK61">
+        <v>0</v>
+      </c>
+      <c r="AL61">
+        <v>0</v>
+      </c>
+      <c r="AM61">
+        <v>-1</v>
+      </c>
+      <c r="AN61">
+        <v>-1</v>
+      </c>
+      <c r="AO61">
+        <v>-1</v>
+      </c>
+      <c r="AP61">
+        <v>-1</v>
+      </c>
+      <c r="AQ61">
+        <v>0</v>
+      </c>
+      <c r="AR61">
+        <v>0</v>
+      </c>
+      <c r="AS61">
+        <v>0</v>
+      </c>
+      <c r="AT61">
+        <v>0</v>
+      </c>
+      <c r="AU61" t="inlineStr">
+        <is>
+          <t>2026-09-16 21:30:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>22:30</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>USA NWSL</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Denver Summit W</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Bay</t>
+        </is>
+      </c>
+      <c r="G62">
+        <v>0</v>
+      </c>
+      <c r="H62">
+        <v>0</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+      <c r="J62">
+        <v>0</v>
+      </c>
+      <c r="K62">
+        <v>0</v>
+      </c>
+      <c r="L62">
+        <v>0</v>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N62">
+        <v>0</v>
+      </c>
+      <c r="O62">
+        <v>0</v>
+      </c>
+      <c r="P62">
+        <v>0</v>
+      </c>
+      <c r="Q62">
+        <v>0</v>
+      </c>
+      <c r="R62">
+        <v>0</v>
+      </c>
+      <c r="S62">
+        <v>0</v>
+      </c>
+      <c r="T62">
+        <v>0</v>
+      </c>
+      <c r="U62">
+        <v>0</v>
+      </c>
+      <c r="V62">
+        <v>0</v>
+      </c>
+      <c r="W62">
+        <v>0</v>
+      </c>
+      <c r="X62">
+        <v>0</v>
+      </c>
+      <c r="Y62">
+        <v>0</v>
+      </c>
+      <c r="Z62">
+        <v>0</v>
+      </c>
+      <c r="AA62">
+        <v>0</v>
+      </c>
+      <c r="AB62">
+        <v>0</v>
+      </c>
+      <c r="AC62">
+        <v>0</v>
+      </c>
+      <c r="AD62">
+        <v>0</v>
+      </c>
+      <c r="AE62">
+        <v>0</v>
+      </c>
+      <c r="AF62">
+        <v>0</v>
+      </c>
+      <c r="AG62">
+        <v>0</v>
+      </c>
+      <c r="AH62" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI62" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ62">
+        <v>0</v>
+      </c>
+      <c r="AK62">
+        <v>0</v>
+      </c>
+      <c r="AL62">
+        <v>0</v>
+      </c>
+      <c r="AM62">
+        <v>-1</v>
+      </c>
+      <c r="AN62">
+        <v>-1</v>
+      </c>
+      <c r="AO62">
+        <v>-1</v>
+      </c>
+      <c r="AP62">
+        <v>-1</v>
+      </c>
+      <c r="AQ62">
+        <v>0</v>
+      </c>
+      <c r="AR62">
+        <v>0</v>
+      </c>
+      <c r="AS62">
+        <v>0</v>
+      </c>
+      <c r="AT62">
+        <v>0</v>
+      </c>
+      <c r="AU62" t="inlineStr">
+        <is>
+          <t>2026-09-16 22:30:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
           <t>23:00</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr">
+      <c r="C63" t="inlineStr">
         <is>
           <t>USA NWSL</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr">
+      <c r="D63" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr">
+      <c r="E63" t="inlineStr">
         <is>
           <t>Angel City</t>
         </is>
       </c>
-      <c r="F56" t="inlineStr">
+      <c r="F63" t="inlineStr">
         <is>
           <t>Seattle Reign</t>
         </is>
       </c>
-      <c r="G56">
-        <v>0</v>
-      </c>
-      <c r="H56">
-        <v>0</v>
-      </c>
-      <c r="I56">
-        <v>0</v>
-      </c>
-      <c r="J56">
-        <v>0</v>
-      </c>
-      <c r="K56">
-        <v>0</v>
-      </c>
-      <c r="L56">
-        <v>0</v>
-      </c>
-      <c r="M56" t="inlineStr">
+      <c r="G63">
+        <v>0</v>
+      </c>
+      <c r="H63">
+        <v>0</v>
+      </c>
+      <c r="I63">
+        <v>0</v>
+      </c>
+      <c r="J63">
+        <v>0</v>
+      </c>
+      <c r="K63">
+        <v>0</v>
+      </c>
+      <c r="L63">
+        <v>0</v>
+      </c>
+      <c r="M63" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="N56">
-        <v>0</v>
-      </c>
-      <c r="O56">
-        <v>0</v>
-      </c>
-      <c r="P56">
-        <v>0</v>
-      </c>
-      <c r="Q56">
-        <v>0</v>
-      </c>
-      <c r="R56">
-        <v>0</v>
-      </c>
-      <c r="S56">
-        <v>0</v>
-      </c>
-      <c r="T56">
-        <v>0</v>
-      </c>
-      <c r="U56">
-        <v>0</v>
-      </c>
-      <c r="V56">
-        <v>0</v>
-      </c>
-      <c r="W56">
-        <v>0</v>
-      </c>
-      <c r="X56">
-        <v>0</v>
-      </c>
-      <c r="Y56">
-        <v>0</v>
-      </c>
-      <c r="Z56">
-        <v>0</v>
-      </c>
-      <c r="AA56">
-        <v>0</v>
-      </c>
-      <c r="AB56">
-        <v>0</v>
-      </c>
-      <c r="AC56">
-        <v>0</v>
-      </c>
-      <c r="AD56">
-        <v>0</v>
-      </c>
-      <c r="AE56">
-        <v>0</v>
-      </c>
-      <c r="AF56">
-        <v>0</v>
-      </c>
-      <c r="AG56">
-        <v>0</v>
-      </c>
-      <c r="AH56" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI56" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ56">
-        <v>0</v>
-      </c>
-      <c r="AK56">
-        <v>0</v>
-      </c>
-      <c r="AL56">
-        <v>0</v>
-      </c>
-      <c r="AM56">
-        <v>-1</v>
-      </c>
-      <c r="AN56">
-        <v>-1</v>
-      </c>
-      <c r="AO56">
-        <v>-1</v>
-      </c>
-      <c r="AP56">
-        <v>-1</v>
-      </c>
-      <c r="AQ56">
-        <v>0</v>
-      </c>
-      <c r="AR56">
-        <v>0</v>
-      </c>
-      <c r="AS56">
-        <v>0</v>
-      </c>
-      <c r="AT56">
-        <v>0</v>
-      </c>
-      <c r="AU56" t="inlineStr">
+      <c r="N63">
+        <v>0</v>
+      </c>
+      <c r="O63">
+        <v>0</v>
+      </c>
+      <c r="P63">
+        <v>0</v>
+      </c>
+      <c r="Q63">
+        <v>0</v>
+      </c>
+      <c r="R63">
+        <v>0</v>
+      </c>
+      <c r="S63">
+        <v>0</v>
+      </c>
+      <c r="T63">
+        <v>0</v>
+      </c>
+      <c r="U63">
+        <v>0</v>
+      </c>
+      <c r="V63">
+        <v>0</v>
+      </c>
+      <c r="W63">
+        <v>0</v>
+      </c>
+      <c r="X63">
+        <v>0</v>
+      </c>
+      <c r="Y63">
+        <v>0</v>
+      </c>
+      <c r="Z63">
+        <v>0</v>
+      </c>
+      <c r="AA63">
+        <v>0</v>
+      </c>
+      <c r="AB63">
+        <v>0</v>
+      </c>
+      <c r="AC63">
+        <v>0</v>
+      </c>
+      <c r="AD63">
+        <v>0</v>
+      </c>
+      <c r="AE63">
+        <v>0</v>
+      </c>
+      <c r="AF63">
+        <v>0</v>
+      </c>
+      <c r="AG63">
+        <v>0</v>
+      </c>
+      <c r="AH63" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI63" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ63">
+        <v>0</v>
+      </c>
+      <c r="AK63">
+        <v>0</v>
+      </c>
+      <c r="AL63">
+        <v>0</v>
+      </c>
+      <c r="AM63">
+        <v>-1</v>
+      </c>
+      <c r="AN63">
+        <v>-1</v>
+      </c>
+      <c r="AO63">
+        <v>-1</v>
+      </c>
+      <c r="AP63">
+        <v>-1</v>
+      </c>
+      <c r="AQ63">
+        <v>0</v>
+      </c>
+      <c r="AR63">
+        <v>0</v>
+      </c>
+      <c r="AS63">
+        <v>0</v>
+      </c>
+      <c r="AT63">
+        <v>0</v>
+      </c>
+      <c r="AU63" t="inlineStr">
         <is>
           <t>2026-09-16 23:00:00</t>
         </is>

--- a/jogos_2026-09-16.xlsx
+++ b/jogos_2026-09-16.xlsx
@@ -9759,7 +9759,7 @@
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N58">

--- a/jogos_2026-09-16.xlsx
+++ b/jogos_2026-09-16.xlsx
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="G33">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="G34">

--- a/jogos_2026-09-16.xlsx
+++ b/jogos_2026-09-16.xlsx
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Teleoptik</t>
         </is>
       </c>
       <c r="G15">
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Teleoptik</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="G16">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G17">
@@ -9079,12 +9079,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>JS El Biar</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G54">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G55">
@@ -9405,12 +9405,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>US Biskra</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G56">
@@ -9568,12 +9568,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G57">
@@ -9731,12 +9731,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>JS El Biar</t>
         </is>
       </c>
       <c r="G58">
@@ -9894,12 +9894,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>US Biskra</t>
         </is>
       </c>
       <c r="G59">

--- a/jogos_2026-09-16.xlsx
+++ b/jogos_2026-09-16.xlsx
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Ingolstadt</t>
+          <t>Waldhof Mannheim</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Hoffenheim II</t>
+          <t>Rot-Weiss Essen</t>
         </is>
       </c>
       <c r="G31">
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Waldhof Mannheim</t>
+          <t>Ingolstadt</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rot-Weiss Essen</t>
+          <t>Hoffenheim II</t>
         </is>
       </c>
       <c r="G32">

--- a/jogos_2026-09-16.xlsx
+++ b/jogos_2026-09-16.xlsx
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Teleoptik</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="G15">
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G16">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Teleoptik</t>
         </is>
       </c>
       <c r="G17">

--- a/jogos_2026-09-16.xlsx
+++ b/jogos_2026-09-16.xlsx
@@ -8753,12 +8753,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Temouchent</t>
         </is>
       </c>
       <c r="G52">
@@ -8916,12 +8916,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Temouchent</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G53">
@@ -9079,12 +9079,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G54">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G55">
@@ -9405,12 +9405,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G56">
@@ -9568,12 +9568,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>JS El Biar</t>
         </is>
       </c>
       <c r="G57">
@@ -9731,12 +9731,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>JS El Biar</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G58">

--- a/jogos_2026-09-16.xlsx
+++ b/jogos_2026-09-16.xlsx
@@ -961,64 +961,64 @@
         </is>
       </c>
       <c r="N4">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="O4">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="P4">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="Q4">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="R4">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="S4">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="T4">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="U4">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="V4">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="W4">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X4">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y4">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z4">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AA4">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AB4">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AC4">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AD4">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AE4">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF4">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG4">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AK4">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1613,64 +1613,64 @@
         </is>
       </c>
       <c r="N8">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="O8">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="P8">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Q8">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="R8">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="S8">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T8">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="U8">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="V8">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W8">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y8">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z8">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AA8">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AB8">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC8">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AD8">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AE8">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF8">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AG8">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK8">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1776,64 +1776,64 @@
         </is>
       </c>
       <c r="N9">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="O9">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P9">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="Q9">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="R9">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="S9">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T9">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U9">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="V9">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="W9">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y9">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z9">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA9">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AB9">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC9">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="AD9">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE9">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF9">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG9">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AK9">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -5697,55 +5697,55 @@
         <v>0</v>
       </c>
       <c r="Q33">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R33">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S33">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="T33">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="U33">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="V33">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W33">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X33">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y33">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z33">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AA33">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AB33">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC33">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AD33">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE33">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF33">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG33">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AK33">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5851,64 +5851,64 @@
         </is>
       </c>
       <c r="N34">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="O34">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="P34">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Q34">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="R34">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="S34">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T34">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U34">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="V34">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W34">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X34">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y34">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z34">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA34">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB34">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC34">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AD34">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE34">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF34">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG34">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK34">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AL34">
         <v>0</v>

--- a/jogos_2026-09-16.xlsx
+++ b/jogos_2026-09-16.xlsx
@@ -929,12 +929,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Olympic El Qanah</t>
         </is>
       </c>
       <c r="G4">
@@ -961,64 +961,64 @@
         </is>
       </c>
       <c r="N4">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="O4">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="P4">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="Q4">
-        <v>3.71</v>
+        <v>0</v>
       </c>
       <c r="R4">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="S4">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="T4">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="U4">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="V4">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="W4">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X4">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="Y4">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="Z4">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="AA4">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="AB4">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AC4">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="AD4">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AE4">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AF4">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG4">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AK4">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1092,12 +1092,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="G5">
@@ -1124,64 +1124,64 @@
         </is>
       </c>
       <c r="N5">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="O5">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="P5">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="Q5">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="R5">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="S5">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="T5">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="U5">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="V5">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="W5">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X5">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y5">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z5">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AA5">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AB5">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AC5">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AD5">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AE5">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF5">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG5">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AK5">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1403,12 +1403,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="G7">
@@ -1554,7 +1554,7 @@
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>2026-09-16 12:00:00</t>
+          <t>2026-09-16 11:00:00</t>
         </is>
       </c>
     </row>
@@ -1566,12 +1566,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Spartak Moskva</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="G8">
@@ -1613,64 +1613,64 @@
         </is>
       </c>
       <c r="N8">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="O8">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="P8">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Q8">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="R8">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="S8">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="T8">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="U8">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="V8">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="W8">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X8">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y8">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="Z8">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AA8">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AB8">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AC8">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AD8">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AE8">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AF8">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AG8">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AK8">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1717,7 +1717,7 @@
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>2026-09-16 12:30:00</t>
+          <t>2026-09-16 12:00:00</t>
         </is>
       </c>
     </row>
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Rodina Moskva</t>
+          <t>Spartak Moskva</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rubin Kazan</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="G9">
@@ -1776,64 +1776,64 @@
         </is>
       </c>
       <c r="N9">
-        <v>3.17</v>
+        <v>1.33</v>
       </c>
       <c r="O9">
-        <v>3.3</v>
+        <v>4.8</v>
       </c>
       <c r="P9">
-        <v>2.29</v>
+        <v>10</v>
       </c>
       <c r="Q9">
-        <v>3.85</v>
+        <v>1.85</v>
       </c>
       <c r="R9">
-        <v>2.04</v>
+        <v>2.32</v>
       </c>
       <c r="S9">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="T9">
-        <v>2.7</v>
+        <v>2.85</v>
       </c>
       <c r="U9">
-        <v>3.14</v>
+        <v>2.81</v>
       </c>
       <c r="V9">
-        <v>1.34</v>
+        <v>1.41</v>
       </c>
       <c r="W9">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="X9">
         <v>1.01</v>
       </c>
       <c r="Y9">
-        <v>1.32</v>
+        <v>1.27</v>
       </c>
       <c r="Z9">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="AA9">
-        <v>2.12</v>
+        <v>1.91</v>
       </c>
       <c r="AB9">
-        <v>1.79</v>
+        <v>1.91</v>
       </c>
       <c r="AC9">
-        <v>3.68</v>
+        <v>3.05</v>
       </c>
       <c r="AD9">
-        <v>1.22</v>
+        <v>1.31</v>
       </c>
       <c r="AE9">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="AF9">
-        <v>1.83</v>
+        <v>2.32</v>
       </c>
       <c r="AG9">
-        <v>1.89</v>
+        <v>1.54</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.65</v>
+        <v>1.21</v>
       </c>
       <c r="AK9">
-        <v>1.38</v>
+        <v>3.34</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1892,27 +1892,27 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Rodina Moskva</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Rubin Kazan</t>
         </is>
       </c>
       <c r="G10">
@@ -1939,64 +1939,64 @@
         </is>
       </c>
       <c r="N10">
-        <v>2.88</v>
+        <v>3.17</v>
       </c>
       <c r="O10">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="P10">
-        <v>2.25</v>
+        <v>2.29</v>
       </c>
       <c r="Q10">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="R10">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="S10">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T10">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U10">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="V10">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="W10">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y10">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z10">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA10">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AB10">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC10">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="AD10">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE10">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF10">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG10">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AK10">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2043,7 +2043,7 @@
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>2026-09-16 12:45:00</t>
+          <t>2026-09-16 12:30:00</t>
         </is>
       </c>
     </row>
@@ -2055,27 +2055,27 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="G11">
@@ -2098,68 +2098,68 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N11">
-        <v>5.25</v>
+        <v>2.88</v>
       </c>
       <c r="O11">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="P11">
-        <v>1.94</v>
+        <v>2.25</v>
       </c>
       <c r="Q11">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="R11">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="S11">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="T11">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="U11">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="V11">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="W11">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X11">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y11">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="Z11">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="AA11">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB11">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC11">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AD11">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AE11">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF11">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG11">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AK11">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2206,7 +2206,7 @@
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>2026-09-16 13:00:00</t>
+          <t>2026-09-16 12:45:00</t>
         </is>
       </c>
     </row>
@@ -2223,22 +2223,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="G12">
@@ -2261,68 +2261,68 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N12">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="O12">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P12">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="Q12">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="R12">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S12">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="T12">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="U12">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="V12">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="W12">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X12">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y12">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="Z12">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AA12">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB12">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC12">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AD12">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE12">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF12">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG12">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK12">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2386,7 +2386,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="G13">
@@ -2424,68 +2424,68 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N13">
-        <v>1.23</v>
+        <v>1.61</v>
       </c>
       <c r="O13">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="P13">
-        <v>8.5</v>
+        <v>4.53</v>
       </c>
       <c r="Q13">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="R13">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="S13">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="T13">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="U13">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="V13">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="W13">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="X13">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y13">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Z13">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="AA13">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AB13">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AC13">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD13">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AE13">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AF13">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AG13">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AK13">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2549,22 +2549,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>CSKA Sofia</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="G14">
@@ -2591,64 +2591,64 @@
         </is>
       </c>
       <c r="N14">
-        <v>4.6</v>
+        <v>1.23</v>
       </c>
       <c r="O14">
-        <v>3.9</v>
+        <v>5.5</v>
       </c>
       <c r="P14">
-        <v>1.55</v>
+        <v>8.5</v>
       </c>
       <c r="Q14">
-        <v>5.07</v>
+        <v>1.62</v>
       </c>
       <c r="R14">
-        <v>2.43</v>
+        <v>2.95</v>
       </c>
       <c r="S14">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="T14">
-        <v>3.1</v>
+        <v>4</v>
       </c>
       <c r="U14">
-        <v>2.63</v>
+        <v>2.1</v>
       </c>
       <c r="V14">
-        <v>1.47</v>
+        <v>1.68</v>
       </c>
       <c r="W14">
+        <v>1.17</v>
+      </c>
+      <c r="X14">
+        <v>1.02</v>
+      </c>
+      <c r="Y14">
         <v>1.08</v>
       </c>
-      <c r="X14">
-        <v>1.04</v>
-      </c>
-      <c r="Y14">
-        <v>1.24</v>
-      </c>
       <c r="Z14">
-        <v>3.72</v>
+        <v>5.75</v>
       </c>
       <c r="AA14">
-        <v>1.75</v>
+        <v>1.43</v>
       </c>
       <c r="AB14">
-        <v>2.05</v>
+        <v>2.75</v>
       </c>
       <c r="AC14">
-        <v>2.75</v>
+        <v>2</v>
       </c>
       <c r="AD14">
-        <v>1.4</v>
+        <v>1.61</v>
       </c>
       <c r="AE14">
-        <v>1.15</v>
+        <v>1.27</v>
       </c>
       <c r="AF14">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="AG14">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.25</v>
+        <v>1.08</v>
       </c>
       <c r="AK14">
-        <v>1.17</v>
+        <v>3.42</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2712,7 +2712,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>CSKA Sofia</t>
         </is>
       </c>
       <c r="G15">
@@ -2750,68 +2750,68 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N15">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="O15">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="P15">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Q15">
-        <v>0</v>
+        <v>5.07</v>
       </c>
       <c r="R15">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="S15">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T15">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U15">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="V15">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="W15">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X15">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y15">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z15">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="AA15">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB15">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC15">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AD15">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE15">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF15">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AG15">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK15">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="G16">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Teleoptik</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G17">
@@ -3196,12 +3196,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Grosseto</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Teleoptik</t>
         </is>
       </c>
       <c r="G18">
@@ -3347,7 +3347,7 @@
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>2026-09-16 13:30:00</t>
+          <t>2026-09-16 13:00:00</t>
         </is>
       </c>
     </row>
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Grosseto</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="G19">
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Ostia Mare Lidocalcio</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="G20">
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Ostia Mare Lidocalcio</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G21">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Sambenedettese</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="G22">
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Sambenedettese</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="G23">
@@ -4174,12 +4174,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="G24">
@@ -4325,7 +4325,7 @@
       </c>
       <c r="AU24" t="inlineStr">
         <is>
-          <t>2026-09-16 14:00:00</t>
+          <t>2026-09-16 13:30:00</t>
         </is>
       </c>
     </row>
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="G25">
@@ -4505,7 +4505,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="G26">
@@ -4543,68 +4543,68 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N26">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="O26">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="P26">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="Q26">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="R26">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="S26">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="T26">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="U26">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="V26">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="W26">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="X26">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y26">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="Z26">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="AA26">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AB26">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="AC26">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="AD26">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AE26">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AF26">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AG26">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AK26">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Servette</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="G27">
@@ -4710,34 +4710,34 @@
         </is>
       </c>
       <c r="N27">
-        <v>2.72</v>
+        <v>2.01</v>
       </c>
       <c r="O27">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="P27">
-        <v>2.2</v>
+        <v>3.52</v>
       </c>
       <c r="Q27">
-        <v>3.05</v>
+        <v>2.47</v>
       </c>
       <c r="R27">
-        <v>2.29</v>
+        <v>2.4</v>
       </c>
       <c r="S27">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="T27">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="U27">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="V27">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="W27">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="X27">
         <v>1.02</v>
@@ -4746,28 +4746,28 @@
         <v>1.11</v>
       </c>
       <c r="Z27">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="AA27">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AB27">
-        <v>2.53</v>
+        <v>2.39</v>
       </c>
       <c r="AC27">
-        <v>2.25</v>
+        <v>2.26</v>
       </c>
       <c r="AD27">
         <v>1.62</v>
       </c>
       <c r="AE27">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AF27">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="AG27">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>1.57</v>
+        <v>1.33</v>
       </c>
       <c r="AK27">
-        <v>1.41</v>
+        <v>1.74</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4831,7 +4831,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Preußen Münster</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Saarbrucken</t>
+          <t>Servette</t>
         </is>
       </c>
       <c r="G28">
@@ -4869,68 +4869,68 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N28">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="O28">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P28">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q28">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="R28">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="S28">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="T28">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U28">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="V28">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="W28">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X28">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y28">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z28">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA28">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB28">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="AC28">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD28">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AE28">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF28">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AG28">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AK28">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Hansa Rostock</t>
+          <t>Preußen Münster</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Saarbrucken</t>
         </is>
       </c>
       <c r="G29">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Fortuna Köln</t>
+          <t>Hansa Rostock</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Wehen Wiesbaden</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="G30">
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Waldhof Mannheim</t>
+          <t>Fortuna Köln</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rot-Weiss Essen</t>
+          <t>Wehen Wiesbaden</t>
         </is>
       </c>
       <c r="G31">
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Ingolstadt</t>
+          <t>Waldhof Mannheim</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Hoffenheim II</t>
+          <t>Rot-Weiss Essen</t>
         </is>
       </c>
       <c r="G32">
@@ -5646,7 +5646,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>Ingolstadt</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Hoffenheim II</t>
         </is>
       </c>
       <c r="G33">
@@ -5697,55 +5697,55 @@
         <v>0</v>
       </c>
       <c r="Q33">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="R33">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="S33">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="T33">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="U33">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="V33">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="W33">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X33">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Y33">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="Z33">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="AA33">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AB33">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC33">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="AD33">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AE33">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AF33">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG33">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AK33">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="G34">
@@ -5851,80 +5851,80 @@
         </is>
       </c>
       <c r="N34">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="O34">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="P34">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="Q34">
-        <v>1.91</v>
+        <v>2.9</v>
       </c>
       <c r="R34">
-        <v>2.57</v>
+        <v>2.1</v>
       </c>
       <c r="S34">
-        <v>1.3</v>
+        <v>1.42</v>
       </c>
       <c r="T34">
-        <v>3.2</v>
+        <v>2.65</v>
       </c>
       <c r="U34">
-        <v>2.49</v>
+        <v>2.88</v>
       </c>
       <c r="V34">
+        <v>1.36</v>
+      </c>
+      <c r="W34">
+        <v>1.07</v>
+      </c>
+      <c r="X34">
+        <v>1.08</v>
+      </c>
+      <c r="Y34">
+        <v>1.38</v>
+      </c>
+      <c r="Z34">
+        <v>2.65</v>
+      </c>
+      <c r="AA34">
+        <v>2.28</v>
+      </c>
+      <c r="AB34">
+        <v>1.6</v>
+      </c>
+      <c r="AC34">
+        <v>3.7</v>
+      </c>
+      <c r="AD34">
+        <v>1.22</v>
+      </c>
+      <c r="AE34">
+        <v>1.06</v>
+      </c>
+      <c r="AF34">
+        <v>1.9</v>
+      </c>
+      <c r="AG34">
+        <v>1.83</v>
+      </c>
+      <c r="AH34" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI34" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ34">
+        <v>1.4</v>
+      </c>
+      <c r="AK34">
         <v>1.5</v>
-      </c>
-      <c r="W34">
-        <v>1.11</v>
-      </c>
-      <c r="X34">
-        <v>1.01</v>
-      </c>
-      <c r="Y34">
-        <v>1.22</v>
-      </c>
-      <c r="Z34">
-        <v>4</v>
-      </c>
-      <c r="AA34">
-        <v>1.72</v>
-      </c>
-      <c r="AB34">
-        <v>2.1</v>
-      </c>
-      <c r="AC34">
-        <v>2.8</v>
-      </c>
-      <c r="AD34">
-        <v>1.38</v>
-      </c>
-      <c r="AE34">
-        <v>1.15</v>
-      </c>
-      <c r="AF34">
-        <v>1.85</v>
-      </c>
-      <c r="AG34">
-        <v>1.85</v>
-      </c>
-      <c r="AH34" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI34" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ34">
-        <v>1.22</v>
-      </c>
-      <c r="AK34">
-        <v>2.5</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -5972,22 +5972,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="G35">
@@ -6014,64 +6014,64 @@
         </is>
       </c>
       <c r="N35">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="O35">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="P35">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Q35">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="R35">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="S35">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T35">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U35">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="V35">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W35">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X35">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y35">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z35">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA35">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB35">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC35">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AD35">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE35">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF35">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG35">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK35">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6130,27 +6130,27 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Lokomotiv Moskva</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Krylya Sovetov</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="G36">
@@ -6177,19 +6177,19 @@
         </is>
       </c>
       <c r="N36">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="O36">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P36">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q36">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="R36">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="S36">
         <v>0</v>
@@ -6198,10 +6198,10 @@
         <v>0</v>
       </c>
       <c r="U36">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="V36">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="W36">
         <v>0</v>
@@ -6210,31 +6210,31 @@
         <v>0</v>
       </c>
       <c r="Y36">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z36">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AA36">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AB36">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC36">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AD36">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE36">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF36">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AG36">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK36">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6281,7 +6281,7 @@
       </c>
       <c r="AU36" t="inlineStr">
         <is>
-          <t>2026-09-16 14:45:00</t>
+          <t>2026-09-16 14:00:00</t>
         </is>
       </c>
     </row>
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Baltika</t>
+          <t>Lokomotiv Moskva</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Zenit</t>
+          <t>Krylya Sovetov</t>
         </is>
       </c>
       <c r="G37">
@@ -6456,27 +6456,27 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Baltika</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Zenit</t>
         </is>
       </c>
       <c r="G38">
@@ -6499,68 +6499,68 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N38">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="O38">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="P38">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="Q38">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="R38">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="S38">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="T38">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="U38">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="V38">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="W38">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X38">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="Y38">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="Z38">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AA38">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AB38">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AC38">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="AD38">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AE38">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AF38">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AG38">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AK38">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6607,7 +6607,7 @@
       </c>
       <c r="AU38" t="inlineStr">
         <is>
-          <t>2026-09-16 15:00:00</t>
+          <t>2026-09-16 14:45:00</t>
         </is>
       </c>
     </row>
@@ -6624,22 +6624,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Metalac GM</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G39">
@@ -6662,68 +6662,68 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N39">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="O39">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="P39">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="Q39">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="R39">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="S39">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="T39">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="U39">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V39">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="W39">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X39">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Y39">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Z39">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AA39">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AB39">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AC39">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AD39">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AE39">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF39">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AG39">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK39">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6782,12 +6782,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>Metalac GM</t>
         </is>
       </c>
       <c r="G40">
@@ -6933,7 +6933,7 @@
       </c>
       <c r="AU40" t="inlineStr">
         <is>
-          <t>2026-09-16 16:00:00</t>
+          <t>2026-09-16 15:00:00</t>
         </is>
       </c>
     </row>
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="G41">
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vado</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="G42">
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Pescara</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Gubbio</t>
+          <t>Vado</t>
         </is>
       </c>
       <c r="G43">
@@ -7439,22 +7439,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Guabirá</t>
+          <t>Pescara</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>Gubbio</t>
         </is>
       </c>
       <c r="G44">
@@ -7597,27 +7597,27 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Guabirá</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="G45">
@@ -7748,7 +7748,7 @@
       </c>
       <c r="AU45" t="inlineStr">
         <is>
-          <t>2026-09-16 16:30:00</t>
+          <t>2026-09-16 16:00:00</t>
         </is>
       </c>
     </row>
@@ -7775,12 +7775,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Levante UD</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="G46">
@@ -7923,27 +7923,27 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>Levante UD</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Huachipato</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="G47">
@@ -7970,64 +7970,64 @@
         </is>
       </c>
       <c r="N47">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="O47">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="P47">
-        <v>6.54</v>
+        <v>0</v>
       </c>
       <c r="Q47">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="R47">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="S47">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="T47">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="U47">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="V47">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="W47">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X47">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y47">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Z47">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AA47">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB47">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="AC47">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AD47">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AE47">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AF47">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG47">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -8040,10 +8040,10 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AK47">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8074,7 +8074,7 @@
       </c>
       <c r="AU47" t="inlineStr">
         <is>
-          <t>2026-09-16 18:00:00</t>
+          <t>2026-09-16 16:30:00</t>
         </is>
       </c>
     </row>
@@ -8086,12 +8086,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -8101,12 +8101,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>Coquimbo Unido</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Sporting JAX</t>
+          <t>Huachipato</t>
         </is>
       </c>
       <c r="G48">
@@ -8133,64 +8133,64 @@
         </is>
       </c>
       <c r="N48">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="O48">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="P48">
-        <v>0</v>
+        <v>6.54</v>
       </c>
       <c r="Q48">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="R48">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S48">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T48">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U48">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="V48">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W48">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X48">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y48">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z48">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AA48">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB48">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AC48">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AD48">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE48">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF48">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG48">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8203,10 +8203,10 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AK48">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8237,7 +8237,7 @@
       </c>
       <c r="AU48" t="inlineStr">
         <is>
-          <t>2026-09-16 19:00:00</t>
+          <t>2026-09-16 18:00:00</t>
         </is>
       </c>
     </row>
@@ -8249,12 +8249,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Sporting JAX</t>
         </is>
       </c>
       <c r="G49">
@@ -8292,68 +8292,68 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N49">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="O49">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="P49">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Q49">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="R49">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="S49">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="T49">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="U49">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="V49">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="W49">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X49">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y49">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z49">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AA49">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB49">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC49">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AD49">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AE49">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AF49">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG49">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8366,10 +8366,10 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AK49">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -8400,7 +8400,7 @@
       </c>
       <c r="AU49" t="inlineStr">
         <is>
-          <t>2026-09-16 19:30:00</t>
+          <t>2026-09-16 19:00:00</t>
         </is>
       </c>
     </row>
@@ -8417,7 +8417,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Club Always Ready</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="G50">
@@ -8455,68 +8455,68 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N50">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="O50">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P50">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q50">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="R50">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="S50">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T50">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="U50">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="V50">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W50">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X50">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y50">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z50">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AA50">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB50">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC50">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AD50">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE50">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF50">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG50">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK50">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8575,12 +8575,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>Club Always Ready</t>
         </is>
       </c>
       <c r="G51">
@@ -8726,7 +8726,7 @@
       </c>
       <c r="AU51" t="inlineStr">
         <is>
-          <t>2026-09-16 21:00:00</t>
+          <t>2026-09-16 19:30:00</t>
         </is>
       </c>
     </row>

--- a/jogos_2026-09-16.xlsx
+++ b/jogos_2026-09-16.xlsx
@@ -4384,64 +4384,64 @@
         </is>
       </c>
       <c r="N25">
-        <v>0</v>
+        <v>5.39</v>
       </c>
       <c r="O25">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P25">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Q25">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="R25">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="S25">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="T25">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="U25">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="V25">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W25">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X25">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y25">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="Z25">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AA25">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AB25">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC25">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AD25">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE25">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF25">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG25">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AK25">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4547,64 +4547,64 @@
         </is>
       </c>
       <c r="N26">
-        <v>0</v>
+        <v>7.95</v>
       </c>
       <c r="O26">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="P26">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Q26">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="R26">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S26">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="T26">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="U26">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="V26">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="W26">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X26">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y26">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="Z26">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AA26">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB26">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC26">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AD26">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE26">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF26">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AG26">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK26">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -5036,64 +5036,64 @@
         </is>
       </c>
       <c r="N29">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O29">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P29">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="Q29">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="R29">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S29">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="T29">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="U29">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="V29">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="W29">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X29">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y29">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z29">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AA29">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AB29">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AC29">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AD29">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE29">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF29">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AG29">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK29">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5199,64 +5199,64 @@
         </is>
       </c>
       <c r="N30">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="O30">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="P30">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="Q30">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="R30">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S30">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="T30">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="U30">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="V30">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="W30">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X30">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y30">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Z30">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="AA30">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AB30">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AC30">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD30">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AE30">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AF30">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AG30">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK30">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5525,64 +5525,64 @@
         </is>
       </c>
       <c r="N32">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O32">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P32">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Q32">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="R32">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S32">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T32">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U32">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="V32">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="W32">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X32">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y32">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Z32">
-        <v>0</v>
+        <v>5.45</v>
       </c>
       <c r="AA32">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AB32">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AC32">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AD32">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AE32">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AF32">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AG32">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK32">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5688,64 +5688,64 @@
         </is>
       </c>
       <c r="N33">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="O33">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="P33">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="Q33">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="R33">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="S33">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="T33">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="U33">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="V33">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="W33">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="X33">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y33">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Z33">
-        <v>0</v>
+        <v>5.85</v>
       </c>
       <c r="AA33">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AB33">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AC33">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AD33">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AE33">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AF33">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AG33">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK33">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -6340,64 +6340,64 @@
         </is>
       </c>
       <c r="N37">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="O37">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="P37">
-        <v>0</v>
+        <v>4.28</v>
       </c>
       <c r="Q37">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="R37">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="S37">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T37">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="U37">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="V37">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W37">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X37">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y37">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z37">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="AA37">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AB37">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AC37">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="AD37">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE37">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF37">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG37">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK37">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6503,64 +6503,64 @@
         </is>
       </c>
       <c r="N38">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="O38">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="P38">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Q38">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="R38">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="S38">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="T38">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="U38">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="V38">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="W38">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X38">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y38">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z38">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AA38">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB38">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AC38">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="AD38">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE38">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF38">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG38">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AK38">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AL38">
         <v>0</v>

--- a/jogos_2026-09-16.xlsx
+++ b/jogos_2026-09-16.xlsx
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Preußen Münster</t>
+          <t>Fortuna Köln</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Saarbrucken</t>
+          <t>Wehen Wiesbaden</t>
         </is>
       </c>
       <c r="G29">
@@ -5036,64 +5036,64 @@
         </is>
       </c>
       <c r="N29">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O29">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="P29">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="Q29">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="R29">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S29">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="T29">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="U29">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="V29">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="W29">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="X29">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y29">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="Z29">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="AA29">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AB29">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="AC29">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="AD29">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AE29">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AF29">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AG29">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AK29">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Hansa Rostock</t>
+          <t>Waldhof Mannheim</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Rot-Weiss Essen</t>
         </is>
       </c>
       <c r="G30">
@@ -5199,64 +5199,64 @@
         </is>
       </c>
       <c r="N30">
-        <v>1.59</v>
+        <v>2.6</v>
       </c>
       <c r="O30">
-        <v>4.3</v>
+        <v>3.75</v>
       </c>
       <c r="P30">
-        <v>4.5</v>
+        <v>2.35</v>
       </c>
       <c r="Q30">
-        <v>1.91</v>
+        <v>2.88</v>
       </c>
       <c r="R30">
-        <v>2.7</v>
+        <v>2.38</v>
       </c>
       <c r="S30">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="T30">
-        <v>4.55</v>
+        <v>4</v>
       </c>
       <c r="U30">
-        <v>1.89</v>
+        <v>2.08</v>
       </c>
       <c r="V30">
-        <v>1.81</v>
+        <v>1.66</v>
       </c>
       <c r="W30">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="X30">
         <v>1.01</v>
       </c>
       <c r="Y30">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="Z30">
-        <v>6.7</v>
+        <v>5.45</v>
       </c>
       <c r="AA30">
-        <v>1.3</v>
+        <v>1.39</v>
       </c>
       <c r="AB30">
-        <v>2.97</v>
+        <v>2.59</v>
       </c>
       <c r="AC30">
-        <v>1.85</v>
+        <v>2.06</v>
       </c>
       <c r="AD30">
-        <v>1.85</v>
+        <v>1.68</v>
       </c>
       <c r="AE30">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="AF30">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="AG30">
-        <v>2.77</v>
+        <v>2.81</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="AK30">
-        <v>2.16</v>
+        <v>1.44</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Fortuna Köln</t>
+          <t>Ingolstadt</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Wehen Wiesbaden</t>
+          <t>Hoffenheim II</t>
         </is>
       </c>
       <c r="G31">
@@ -5362,64 +5362,64 @@
         </is>
       </c>
       <c r="N31">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="O31">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="P31">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="Q31">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="R31">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="S31">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="T31">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="U31">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="V31">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="W31">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="X31">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y31">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Z31">
-        <v>0</v>
+        <v>5.85</v>
       </c>
       <c r="AA31">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AB31">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AC31">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AD31">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AE31">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AF31">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AG31">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK31">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Waldhof Mannheim</t>
+          <t>Hansa Rostock</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rot-Weiss Essen</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="G32">
@@ -5525,64 +5525,64 @@
         </is>
       </c>
       <c r="N32">
-        <v>2.6</v>
+        <v>1.59</v>
       </c>
       <c r="O32">
-        <v>3.75</v>
+        <v>4.3</v>
       </c>
       <c r="P32">
-        <v>2.35</v>
+        <v>4.5</v>
       </c>
       <c r="Q32">
-        <v>2.88</v>
+        <v>1.91</v>
       </c>
       <c r="R32">
-        <v>2.38</v>
+        <v>2.7</v>
       </c>
       <c r="S32">
+        <v>1.13</v>
+      </c>
+      <c r="T32">
+        <v>4.55</v>
+      </c>
+      <c r="U32">
+        <v>1.89</v>
+      </c>
+      <c r="V32">
+        <v>1.81</v>
+      </c>
+      <c r="W32">
         <v>1.2</v>
-      </c>
-      <c r="T32">
-        <v>4</v>
-      </c>
-      <c r="U32">
-        <v>2.08</v>
-      </c>
-      <c r="V32">
-        <v>1.66</v>
-      </c>
-      <c r="W32">
-        <v>1.14</v>
       </c>
       <c r="X32">
         <v>1.01</v>
       </c>
       <c r="Y32">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="Z32">
-        <v>5.45</v>
+        <v>6.7</v>
       </c>
       <c r="AA32">
-        <v>1.39</v>
+        <v>1.3</v>
       </c>
       <c r="AB32">
-        <v>2.59</v>
+        <v>2.97</v>
       </c>
       <c r="AC32">
-        <v>2.06</v>
+        <v>1.85</v>
       </c>
       <c r="AD32">
-        <v>1.68</v>
+        <v>1.85</v>
       </c>
       <c r="AE32">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="AF32">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="AG32">
-        <v>2.81</v>
+        <v>2.77</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="AK32">
-        <v>1.44</v>
+        <v>2.16</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Ingolstadt</t>
+          <t>Preußen Münster</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Hoffenheim II</t>
+          <t>Saarbrucken</t>
         </is>
       </c>
       <c r="G33">
@@ -5688,64 +5688,64 @@
         </is>
       </c>
       <c r="N33">
-        <v>1.74</v>
+        <v>2.55</v>
       </c>
       <c r="O33">
-        <v>4.1</v>
+        <v>3.6</v>
       </c>
       <c r="P33">
-        <v>3.8</v>
+        <v>2.46</v>
       </c>
       <c r="Q33">
-        <v>2.1</v>
+        <v>2.93</v>
       </c>
       <c r="R33">
-        <v>2.63</v>
+        <v>2.3</v>
       </c>
       <c r="S33">
-        <v>1.17</v>
+        <v>1.24</v>
       </c>
       <c r="T33">
-        <v>4.5</v>
+        <v>3.48</v>
       </c>
       <c r="U33">
-        <v>1.92</v>
+        <v>2.23</v>
       </c>
       <c r="V33">
-        <v>1.78</v>
+        <v>1.55</v>
       </c>
       <c r="W33">
-        <v>1.21</v>
+        <v>1.12</v>
       </c>
       <c r="X33">
         <v>1.01</v>
       </c>
       <c r="Y33">
-        <v>1.07</v>
+        <v>1.14</v>
       </c>
       <c r="Z33">
-        <v>5.85</v>
+        <v>4.33</v>
       </c>
       <c r="AA33">
-        <v>1.33</v>
+        <v>1.59</v>
       </c>
       <c r="AB33">
-        <v>2.83</v>
+        <v>2.21</v>
       </c>
       <c r="AC33">
-        <v>1.9</v>
+        <v>2.43</v>
       </c>
       <c r="AD33">
-        <v>1.8</v>
+        <v>1.44</v>
       </c>
       <c r="AE33">
-        <v>1.31</v>
+        <v>1.15</v>
       </c>
       <c r="AF33">
-        <v>1.39</v>
+        <v>1.49</v>
       </c>
       <c r="AG33">
-        <v>2.73</v>
+        <v>2.42</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AK33">
-        <v>2</v>
+        <v>1.44</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -7807,64 +7807,64 @@
         </is>
       </c>
       <c r="N46">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="O46">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="P46">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="Q46">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="R46">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="S46">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="T46">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="U46">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="V46">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="W46">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="X46">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y46">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Z46">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AA46">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AB46">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AC46">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AD46">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AE46">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AF46">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG46">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7877,10 +7877,10 @@
         </is>
       </c>
       <c r="AJ46">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AK46">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -7970,64 +7970,64 @@
         </is>
       </c>
       <c r="N47">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O47">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P47">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="Q47">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="R47">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="S47">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T47">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U47">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="V47">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W47">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X47">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y47">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z47">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AA47">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB47">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC47">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AD47">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE47">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF47">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG47">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -8040,10 +8040,10 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AK47">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8412,12 +8412,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Club Always Ready</t>
         </is>
       </c>
       <c r="G50">
@@ -8455,68 +8455,68 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N50">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="O50">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="P50">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Q50">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="R50">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="S50">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="T50">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="U50">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="V50">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="W50">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X50">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y50">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z50">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AA50">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB50">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC50">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AD50">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AE50">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AF50">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG50">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AK50">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8563,7 +8563,7 @@
       </c>
       <c r="AU50" t="inlineStr">
         <is>
-          <t>2026-09-16 19:30:00</t>
+          <t>2026-09-16 19:00:00</t>
         </is>
       </c>
     </row>
@@ -8580,7 +8580,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Club Always Ready</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="G51">
@@ -8622,64 +8622,64 @@
         </is>
       </c>
       <c r="N51">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="O51">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P51">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q51">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="R51">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="S51">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T51">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="U51">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="V51">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W51">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X51">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y51">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z51">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AA51">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB51">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC51">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AD51">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE51">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF51">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG51">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8692,10 +8692,10 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK51">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AL51">
         <v>0</v>

--- a/jogos_2026-09-16.xlsx
+++ b/jogos_2026-09-16.xlsx
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Sambenedettese</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="G22">
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Sambenedettese</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="G23">
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="G24">
